--- a/excel/template.xlsx
+++ b/excel/template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\ATPU-DG\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F10C9B-44FE-497A-93CE-99327B613B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4EC7F17-2AC5-4C9E-B348-3A733117430B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4905" yWindow="1110" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hlavni" sheetId="13" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="816" uniqueCount="294">
   <si>
     <t>Ústav:</t>
   </si>
@@ -922,28 +922,7 @@
     <t>Verze: 14.10.2019</t>
   </si>
   <si>
-    <t>AP7SU</t>
-  </si>
-  <si>
-    <t>AP6UI</t>
-  </si>
-  <si>
-    <t>AP7SC</t>
-  </si>
-  <si>
-    <t>AK0DA</t>
-  </si>
-  <si>
-    <t>AP0DA</t>
-  </si>
-  <si>
     <t>Rok</t>
-  </si>
-  <si>
-    <t>AP9EV</t>
-  </si>
-  <si>
-    <t>AE9EV</t>
   </si>
   <si>
     <t>Staré hodnoty</t>
@@ -1869,7 +1848,7 @@
     <xf numFmtId="0" fontId="15" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="219">
+  <cellXfs count="218">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2186,10 +2165,6 @@
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="47" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2210,6 +2185,269 @@
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="2" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="2" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="7" borderId="40" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="38" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="7" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="50" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="7" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="4" fillId="7" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2294,269 +2532,6 @@
     <xf numFmtId="9" fontId="4" fillId="7" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="7" borderId="25" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="4" fillId="7" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="15" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="16" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="49" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="50" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="7" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="7" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="40" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="36" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="4" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="2" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="2" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="2" borderId="23" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="44" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="38" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="7" borderId="40" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="44" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="38" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="40" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="44" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="39" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="36" xfId="5" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="56" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="5" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Bad" xfId="5" builtinId="27"/>
@@ -2564,7 +2539,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="normální 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="normální_UV_nove" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="3" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2852,723 +2827,723 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AH129"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="21.42578125" style="2" customWidth="1"/>
-    <col min="2" max="13" width="7.42578125" style="1" customWidth="1"/>
-    <col min="14" max="17" width="7.28515625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="8.42578125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="7.42578125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="6.42578125" style="1" customWidth="1"/>
-    <col min="21" max="21" width="2.7109375" style="2" customWidth="1"/>
-    <col min="22" max="22" width="33.85546875" style="2" customWidth="1"/>
-    <col min="23" max="23" width="2.85546875" style="2" customWidth="1"/>
+    <col min="1" max="1" width="21.44140625" style="2" customWidth="1"/>
+    <col min="2" max="13" width="7.44140625" style="1" customWidth="1"/>
+    <col min="14" max="17" width="7.33203125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="8.44140625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="7.44140625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="6.44140625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="2.6640625" style="2" customWidth="1"/>
+    <col min="22" max="22" width="33.88671875" style="2" customWidth="1"/>
+    <col min="23" max="23" width="2.88671875" style="2" customWidth="1"/>
     <col min="24" max="25" width="9" style="2" hidden="1" customWidth="1"/>
-    <col min="26" max="27" width="9.140625" style="2" hidden="1" customWidth="1"/>
+    <col min="26" max="27" width="9.109375" style="2" hidden="1" customWidth="1"/>
     <col min="28" max="28" width="12" style="2" hidden="1" customWidth="1"/>
-    <col min="29" max="30" width="9.140625" style="2" hidden="1" customWidth="1"/>
-    <col min="31" max="31" width="10.42578125" style="98" customWidth="1"/>
-    <col min="32" max="34" width="8.85546875" style="98"/>
-    <col min="35" max="255" width="8.85546875" style="2"/>
-    <col min="256" max="256" width="14.7109375" style="2" customWidth="1"/>
-    <col min="257" max="257" width="5.140625" style="2" customWidth="1"/>
-    <col min="258" max="264" width="4.140625" style="2" customWidth="1"/>
-    <col min="265" max="267" width="3.7109375" style="2" customWidth="1"/>
-    <col min="268" max="270" width="4.140625" style="2" customWidth="1"/>
-    <col min="271" max="272" width="4.7109375" style="2" customWidth="1"/>
-    <col min="273" max="275" width="5.140625" style="2" customWidth="1"/>
-    <col min="276" max="276" width="2.7109375" style="2" customWidth="1"/>
-    <col min="277" max="277" width="15.7109375" style="2" customWidth="1"/>
-    <col min="278" max="511" width="8.85546875" style="2"/>
-    <col min="512" max="512" width="14.7109375" style="2" customWidth="1"/>
-    <col min="513" max="513" width="5.140625" style="2" customWidth="1"/>
-    <col min="514" max="520" width="4.140625" style="2" customWidth="1"/>
-    <col min="521" max="523" width="3.7109375" style="2" customWidth="1"/>
-    <col min="524" max="526" width="4.140625" style="2" customWidth="1"/>
-    <col min="527" max="528" width="4.7109375" style="2" customWidth="1"/>
-    <col min="529" max="531" width="5.140625" style="2" customWidth="1"/>
-    <col min="532" max="532" width="2.7109375" style="2" customWidth="1"/>
-    <col min="533" max="533" width="15.7109375" style="2" customWidth="1"/>
-    <col min="534" max="767" width="8.85546875" style="2"/>
-    <col min="768" max="768" width="14.7109375" style="2" customWidth="1"/>
-    <col min="769" max="769" width="5.140625" style="2" customWidth="1"/>
-    <col min="770" max="776" width="4.140625" style="2" customWidth="1"/>
-    <col min="777" max="779" width="3.7109375" style="2" customWidth="1"/>
-    <col min="780" max="782" width="4.140625" style="2" customWidth="1"/>
-    <col min="783" max="784" width="4.7109375" style="2" customWidth="1"/>
-    <col min="785" max="787" width="5.140625" style="2" customWidth="1"/>
-    <col min="788" max="788" width="2.7109375" style="2" customWidth="1"/>
-    <col min="789" max="789" width="15.7109375" style="2" customWidth="1"/>
-    <col min="790" max="1023" width="8.85546875" style="2"/>
-    <col min="1024" max="1024" width="14.7109375" style="2" customWidth="1"/>
-    <col min="1025" max="1025" width="5.140625" style="2" customWidth="1"/>
-    <col min="1026" max="1032" width="4.140625" style="2" customWidth="1"/>
-    <col min="1033" max="1035" width="3.7109375" style="2" customWidth="1"/>
-    <col min="1036" max="1038" width="4.140625" style="2" customWidth="1"/>
-    <col min="1039" max="1040" width="4.7109375" style="2" customWidth="1"/>
-    <col min="1041" max="1043" width="5.140625" style="2" customWidth="1"/>
-    <col min="1044" max="1044" width="2.7109375" style="2" customWidth="1"/>
-    <col min="1045" max="1045" width="15.7109375" style="2" customWidth="1"/>
-    <col min="1046" max="1279" width="8.85546875" style="2"/>
-    <col min="1280" max="1280" width="14.7109375" style="2" customWidth="1"/>
-    <col min="1281" max="1281" width="5.140625" style="2" customWidth="1"/>
-    <col min="1282" max="1288" width="4.140625" style="2" customWidth="1"/>
-    <col min="1289" max="1291" width="3.7109375" style="2" customWidth="1"/>
-    <col min="1292" max="1294" width="4.140625" style="2" customWidth="1"/>
-    <col min="1295" max="1296" width="4.7109375" style="2" customWidth="1"/>
-    <col min="1297" max="1299" width="5.140625" style="2" customWidth="1"/>
-    <col min="1300" max="1300" width="2.7109375" style="2" customWidth="1"/>
-    <col min="1301" max="1301" width="15.7109375" style="2" customWidth="1"/>
-    <col min="1302" max="1535" width="8.85546875" style="2"/>
-    <col min="1536" max="1536" width="14.7109375" style="2" customWidth="1"/>
-    <col min="1537" max="1537" width="5.140625" style="2" customWidth="1"/>
-    <col min="1538" max="1544" width="4.140625" style="2" customWidth="1"/>
-    <col min="1545" max="1547" width="3.7109375" style="2" customWidth="1"/>
-    <col min="1548" max="1550" width="4.140625" style="2" customWidth="1"/>
-    <col min="1551" max="1552" width="4.7109375" style="2" customWidth="1"/>
-    <col min="1553" max="1555" width="5.140625" style="2" customWidth="1"/>
-    <col min="1556" max="1556" width="2.7109375" style="2" customWidth="1"/>
-    <col min="1557" max="1557" width="15.7109375" style="2" customWidth="1"/>
-    <col min="1558" max="1791" width="8.85546875" style="2"/>
-    <col min="1792" max="1792" width="14.7109375" style="2" customWidth="1"/>
-    <col min="1793" max="1793" width="5.140625" style="2" customWidth="1"/>
-    <col min="1794" max="1800" width="4.140625" style="2" customWidth="1"/>
-    <col min="1801" max="1803" width="3.7109375" style="2" customWidth="1"/>
-    <col min="1804" max="1806" width="4.140625" style="2" customWidth="1"/>
-    <col min="1807" max="1808" width="4.7109375" style="2" customWidth="1"/>
-    <col min="1809" max="1811" width="5.140625" style="2" customWidth="1"/>
-    <col min="1812" max="1812" width="2.7109375" style="2" customWidth="1"/>
-    <col min="1813" max="1813" width="15.7109375" style="2" customWidth="1"/>
-    <col min="1814" max="2047" width="8.85546875" style="2"/>
-    <col min="2048" max="2048" width="14.7109375" style="2" customWidth="1"/>
-    <col min="2049" max="2049" width="5.140625" style="2" customWidth="1"/>
-    <col min="2050" max="2056" width="4.140625" style="2" customWidth="1"/>
-    <col min="2057" max="2059" width="3.7109375" style="2" customWidth="1"/>
-    <col min="2060" max="2062" width="4.140625" style="2" customWidth="1"/>
-    <col min="2063" max="2064" width="4.7109375" style="2" customWidth="1"/>
-    <col min="2065" max="2067" width="5.140625" style="2" customWidth="1"/>
-    <col min="2068" max="2068" width="2.7109375" style="2" customWidth="1"/>
-    <col min="2069" max="2069" width="15.7109375" style="2" customWidth="1"/>
-    <col min="2070" max="2303" width="8.85546875" style="2"/>
-    <col min="2304" max="2304" width="14.7109375" style="2" customWidth="1"/>
-    <col min="2305" max="2305" width="5.140625" style="2" customWidth="1"/>
-    <col min="2306" max="2312" width="4.140625" style="2" customWidth="1"/>
-    <col min="2313" max="2315" width="3.7109375" style="2" customWidth="1"/>
-    <col min="2316" max="2318" width="4.140625" style="2" customWidth="1"/>
-    <col min="2319" max="2320" width="4.7109375" style="2" customWidth="1"/>
-    <col min="2321" max="2323" width="5.140625" style="2" customWidth="1"/>
-    <col min="2324" max="2324" width="2.7109375" style="2" customWidth="1"/>
-    <col min="2325" max="2325" width="15.7109375" style="2" customWidth="1"/>
-    <col min="2326" max="2559" width="8.85546875" style="2"/>
-    <col min="2560" max="2560" width="14.7109375" style="2" customWidth="1"/>
-    <col min="2561" max="2561" width="5.140625" style="2" customWidth="1"/>
-    <col min="2562" max="2568" width="4.140625" style="2" customWidth="1"/>
-    <col min="2569" max="2571" width="3.7109375" style="2" customWidth="1"/>
-    <col min="2572" max="2574" width="4.140625" style="2" customWidth="1"/>
-    <col min="2575" max="2576" width="4.7109375" style="2" customWidth="1"/>
-    <col min="2577" max="2579" width="5.140625" style="2" customWidth="1"/>
-    <col min="2580" max="2580" width="2.7109375" style="2" customWidth="1"/>
-    <col min="2581" max="2581" width="15.7109375" style="2" customWidth="1"/>
-    <col min="2582" max="2815" width="8.85546875" style="2"/>
-    <col min="2816" max="2816" width="14.7109375" style="2" customWidth="1"/>
-    <col min="2817" max="2817" width="5.140625" style="2" customWidth="1"/>
-    <col min="2818" max="2824" width="4.140625" style="2" customWidth="1"/>
-    <col min="2825" max="2827" width="3.7109375" style="2" customWidth="1"/>
-    <col min="2828" max="2830" width="4.140625" style="2" customWidth="1"/>
-    <col min="2831" max="2832" width="4.7109375" style="2" customWidth="1"/>
-    <col min="2833" max="2835" width="5.140625" style="2" customWidth="1"/>
-    <col min="2836" max="2836" width="2.7109375" style="2" customWidth="1"/>
-    <col min="2837" max="2837" width="15.7109375" style="2" customWidth="1"/>
-    <col min="2838" max="3071" width="8.85546875" style="2"/>
-    <col min="3072" max="3072" width="14.7109375" style="2" customWidth="1"/>
-    <col min="3073" max="3073" width="5.140625" style="2" customWidth="1"/>
-    <col min="3074" max="3080" width="4.140625" style="2" customWidth="1"/>
-    <col min="3081" max="3083" width="3.7109375" style="2" customWidth="1"/>
-    <col min="3084" max="3086" width="4.140625" style="2" customWidth="1"/>
-    <col min="3087" max="3088" width="4.7109375" style="2" customWidth="1"/>
-    <col min="3089" max="3091" width="5.140625" style="2" customWidth="1"/>
-    <col min="3092" max="3092" width="2.7109375" style="2" customWidth="1"/>
-    <col min="3093" max="3093" width="15.7109375" style="2" customWidth="1"/>
-    <col min="3094" max="3327" width="8.85546875" style="2"/>
-    <col min="3328" max="3328" width="14.7109375" style="2" customWidth="1"/>
-    <col min="3329" max="3329" width="5.140625" style="2" customWidth="1"/>
-    <col min="3330" max="3336" width="4.140625" style="2" customWidth="1"/>
-    <col min="3337" max="3339" width="3.7109375" style="2" customWidth="1"/>
-    <col min="3340" max="3342" width="4.140625" style="2" customWidth="1"/>
-    <col min="3343" max="3344" width="4.7109375" style="2" customWidth="1"/>
-    <col min="3345" max="3347" width="5.140625" style="2" customWidth="1"/>
-    <col min="3348" max="3348" width="2.7109375" style="2" customWidth="1"/>
-    <col min="3349" max="3349" width="15.7109375" style="2" customWidth="1"/>
-    <col min="3350" max="3583" width="8.85546875" style="2"/>
-    <col min="3584" max="3584" width="14.7109375" style="2" customWidth="1"/>
-    <col min="3585" max="3585" width="5.140625" style="2" customWidth="1"/>
-    <col min="3586" max="3592" width="4.140625" style="2" customWidth="1"/>
-    <col min="3593" max="3595" width="3.7109375" style="2" customWidth="1"/>
-    <col min="3596" max="3598" width="4.140625" style="2" customWidth="1"/>
-    <col min="3599" max="3600" width="4.7109375" style="2" customWidth="1"/>
-    <col min="3601" max="3603" width="5.140625" style="2" customWidth="1"/>
-    <col min="3604" max="3604" width="2.7109375" style="2" customWidth="1"/>
-    <col min="3605" max="3605" width="15.7109375" style="2" customWidth="1"/>
-    <col min="3606" max="3839" width="8.85546875" style="2"/>
-    <col min="3840" max="3840" width="14.7109375" style="2" customWidth="1"/>
-    <col min="3841" max="3841" width="5.140625" style="2" customWidth="1"/>
-    <col min="3842" max="3848" width="4.140625" style="2" customWidth="1"/>
-    <col min="3849" max="3851" width="3.7109375" style="2" customWidth="1"/>
-    <col min="3852" max="3854" width="4.140625" style="2" customWidth="1"/>
-    <col min="3855" max="3856" width="4.7109375" style="2" customWidth="1"/>
-    <col min="3857" max="3859" width="5.140625" style="2" customWidth="1"/>
-    <col min="3860" max="3860" width="2.7109375" style="2" customWidth="1"/>
-    <col min="3861" max="3861" width="15.7109375" style="2" customWidth="1"/>
-    <col min="3862" max="4095" width="8.85546875" style="2"/>
-    <col min="4096" max="4096" width="14.7109375" style="2" customWidth="1"/>
-    <col min="4097" max="4097" width="5.140625" style="2" customWidth="1"/>
-    <col min="4098" max="4104" width="4.140625" style="2" customWidth="1"/>
-    <col min="4105" max="4107" width="3.7109375" style="2" customWidth="1"/>
-    <col min="4108" max="4110" width="4.140625" style="2" customWidth="1"/>
-    <col min="4111" max="4112" width="4.7109375" style="2" customWidth="1"/>
-    <col min="4113" max="4115" width="5.140625" style="2" customWidth="1"/>
-    <col min="4116" max="4116" width="2.7109375" style="2" customWidth="1"/>
-    <col min="4117" max="4117" width="15.7109375" style="2" customWidth="1"/>
-    <col min="4118" max="4351" width="8.85546875" style="2"/>
-    <col min="4352" max="4352" width="14.7109375" style="2" customWidth="1"/>
-    <col min="4353" max="4353" width="5.140625" style="2" customWidth="1"/>
-    <col min="4354" max="4360" width="4.140625" style="2" customWidth="1"/>
-    <col min="4361" max="4363" width="3.7109375" style="2" customWidth="1"/>
-    <col min="4364" max="4366" width="4.140625" style="2" customWidth="1"/>
-    <col min="4367" max="4368" width="4.7109375" style="2" customWidth="1"/>
-    <col min="4369" max="4371" width="5.140625" style="2" customWidth="1"/>
-    <col min="4372" max="4372" width="2.7109375" style="2" customWidth="1"/>
-    <col min="4373" max="4373" width="15.7109375" style="2" customWidth="1"/>
-    <col min="4374" max="4607" width="8.85546875" style="2"/>
-    <col min="4608" max="4608" width="14.7109375" style="2" customWidth="1"/>
-    <col min="4609" max="4609" width="5.140625" style="2" customWidth="1"/>
-    <col min="4610" max="4616" width="4.140625" style="2" customWidth="1"/>
-    <col min="4617" max="4619" width="3.7109375" style="2" customWidth="1"/>
-    <col min="4620" max="4622" width="4.140625" style="2" customWidth="1"/>
-    <col min="4623" max="4624" width="4.7109375" style="2" customWidth="1"/>
-    <col min="4625" max="4627" width="5.140625" style="2" customWidth="1"/>
-    <col min="4628" max="4628" width="2.7109375" style="2" customWidth="1"/>
-    <col min="4629" max="4629" width="15.7109375" style="2" customWidth="1"/>
-    <col min="4630" max="4863" width="8.85546875" style="2"/>
-    <col min="4864" max="4864" width="14.7109375" style="2" customWidth="1"/>
-    <col min="4865" max="4865" width="5.140625" style="2" customWidth="1"/>
-    <col min="4866" max="4872" width="4.140625" style="2" customWidth="1"/>
-    <col min="4873" max="4875" width="3.7109375" style="2" customWidth="1"/>
-    <col min="4876" max="4878" width="4.140625" style="2" customWidth="1"/>
-    <col min="4879" max="4880" width="4.7109375" style="2" customWidth="1"/>
-    <col min="4881" max="4883" width="5.140625" style="2" customWidth="1"/>
-    <col min="4884" max="4884" width="2.7109375" style="2" customWidth="1"/>
-    <col min="4885" max="4885" width="15.7109375" style="2" customWidth="1"/>
-    <col min="4886" max="5119" width="8.85546875" style="2"/>
-    <col min="5120" max="5120" width="14.7109375" style="2" customWidth="1"/>
-    <col min="5121" max="5121" width="5.140625" style="2" customWidth="1"/>
-    <col min="5122" max="5128" width="4.140625" style="2" customWidth="1"/>
-    <col min="5129" max="5131" width="3.7109375" style="2" customWidth="1"/>
-    <col min="5132" max="5134" width="4.140625" style="2" customWidth="1"/>
-    <col min="5135" max="5136" width="4.7109375" style="2" customWidth="1"/>
-    <col min="5137" max="5139" width="5.140625" style="2" customWidth="1"/>
-    <col min="5140" max="5140" width="2.7109375" style="2" customWidth="1"/>
-    <col min="5141" max="5141" width="15.7109375" style="2" customWidth="1"/>
-    <col min="5142" max="5375" width="8.85546875" style="2"/>
-    <col min="5376" max="5376" width="14.7109375" style="2" customWidth="1"/>
-    <col min="5377" max="5377" width="5.140625" style="2" customWidth="1"/>
-    <col min="5378" max="5384" width="4.140625" style="2" customWidth="1"/>
-    <col min="5385" max="5387" width="3.7109375" style="2" customWidth="1"/>
-    <col min="5388" max="5390" width="4.140625" style="2" customWidth="1"/>
-    <col min="5391" max="5392" width="4.7109375" style="2" customWidth="1"/>
-    <col min="5393" max="5395" width="5.140625" style="2" customWidth="1"/>
-    <col min="5396" max="5396" width="2.7109375" style="2" customWidth="1"/>
-    <col min="5397" max="5397" width="15.7109375" style="2" customWidth="1"/>
-    <col min="5398" max="5631" width="8.85546875" style="2"/>
-    <col min="5632" max="5632" width="14.7109375" style="2" customWidth="1"/>
-    <col min="5633" max="5633" width="5.140625" style="2" customWidth="1"/>
-    <col min="5634" max="5640" width="4.140625" style="2" customWidth="1"/>
-    <col min="5641" max="5643" width="3.7109375" style="2" customWidth="1"/>
-    <col min="5644" max="5646" width="4.140625" style="2" customWidth="1"/>
-    <col min="5647" max="5648" width="4.7109375" style="2" customWidth="1"/>
-    <col min="5649" max="5651" width="5.140625" style="2" customWidth="1"/>
-    <col min="5652" max="5652" width="2.7109375" style="2" customWidth="1"/>
-    <col min="5653" max="5653" width="15.7109375" style="2" customWidth="1"/>
-    <col min="5654" max="5887" width="8.85546875" style="2"/>
-    <col min="5888" max="5888" width="14.7109375" style="2" customWidth="1"/>
-    <col min="5889" max="5889" width="5.140625" style="2" customWidth="1"/>
-    <col min="5890" max="5896" width="4.140625" style="2" customWidth="1"/>
-    <col min="5897" max="5899" width="3.7109375" style="2" customWidth="1"/>
-    <col min="5900" max="5902" width="4.140625" style="2" customWidth="1"/>
-    <col min="5903" max="5904" width="4.7109375" style="2" customWidth="1"/>
-    <col min="5905" max="5907" width="5.140625" style="2" customWidth="1"/>
-    <col min="5908" max="5908" width="2.7109375" style="2" customWidth="1"/>
-    <col min="5909" max="5909" width="15.7109375" style="2" customWidth="1"/>
-    <col min="5910" max="6143" width="8.85546875" style="2"/>
-    <col min="6144" max="6144" width="14.7109375" style="2" customWidth="1"/>
-    <col min="6145" max="6145" width="5.140625" style="2" customWidth="1"/>
-    <col min="6146" max="6152" width="4.140625" style="2" customWidth="1"/>
-    <col min="6153" max="6155" width="3.7109375" style="2" customWidth="1"/>
-    <col min="6156" max="6158" width="4.140625" style="2" customWidth="1"/>
-    <col min="6159" max="6160" width="4.7109375" style="2" customWidth="1"/>
-    <col min="6161" max="6163" width="5.140625" style="2" customWidth="1"/>
-    <col min="6164" max="6164" width="2.7109375" style="2" customWidth="1"/>
-    <col min="6165" max="6165" width="15.7109375" style="2" customWidth="1"/>
-    <col min="6166" max="6399" width="8.85546875" style="2"/>
-    <col min="6400" max="6400" width="14.7109375" style="2" customWidth="1"/>
-    <col min="6401" max="6401" width="5.140625" style="2" customWidth="1"/>
-    <col min="6402" max="6408" width="4.140625" style="2" customWidth="1"/>
-    <col min="6409" max="6411" width="3.7109375" style="2" customWidth="1"/>
-    <col min="6412" max="6414" width="4.140625" style="2" customWidth="1"/>
-    <col min="6415" max="6416" width="4.7109375" style="2" customWidth="1"/>
-    <col min="6417" max="6419" width="5.140625" style="2" customWidth="1"/>
-    <col min="6420" max="6420" width="2.7109375" style="2" customWidth="1"/>
-    <col min="6421" max="6421" width="15.7109375" style="2" customWidth="1"/>
-    <col min="6422" max="6655" width="8.85546875" style="2"/>
-    <col min="6656" max="6656" width="14.7109375" style="2" customWidth="1"/>
-    <col min="6657" max="6657" width="5.140625" style="2" customWidth="1"/>
-    <col min="6658" max="6664" width="4.140625" style="2" customWidth="1"/>
-    <col min="6665" max="6667" width="3.7109375" style="2" customWidth="1"/>
-    <col min="6668" max="6670" width="4.140625" style="2" customWidth="1"/>
-    <col min="6671" max="6672" width="4.7109375" style="2" customWidth="1"/>
-    <col min="6673" max="6675" width="5.140625" style="2" customWidth="1"/>
-    <col min="6676" max="6676" width="2.7109375" style="2" customWidth="1"/>
-    <col min="6677" max="6677" width="15.7109375" style="2" customWidth="1"/>
-    <col min="6678" max="6911" width="8.85546875" style="2"/>
-    <col min="6912" max="6912" width="14.7109375" style="2" customWidth="1"/>
-    <col min="6913" max="6913" width="5.140625" style="2" customWidth="1"/>
-    <col min="6914" max="6920" width="4.140625" style="2" customWidth="1"/>
-    <col min="6921" max="6923" width="3.7109375" style="2" customWidth="1"/>
-    <col min="6924" max="6926" width="4.140625" style="2" customWidth="1"/>
-    <col min="6927" max="6928" width="4.7109375" style="2" customWidth="1"/>
-    <col min="6929" max="6931" width="5.140625" style="2" customWidth="1"/>
-    <col min="6932" max="6932" width="2.7109375" style="2" customWidth="1"/>
-    <col min="6933" max="6933" width="15.7109375" style="2" customWidth="1"/>
-    <col min="6934" max="7167" width="8.85546875" style="2"/>
-    <col min="7168" max="7168" width="14.7109375" style="2" customWidth="1"/>
-    <col min="7169" max="7169" width="5.140625" style="2" customWidth="1"/>
-    <col min="7170" max="7176" width="4.140625" style="2" customWidth="1"/>
-    <col min="7177" max="7179" width="3.7109375" style="2" customWidth="1"/>
-    <col min="7180" max="7182" width="4.140625" style="2" customWidth="1"/>
-    <col min="7183" max="7184" width="4.7109375" style="2" customWidth="1"/>
-    <col min="7185" max="7187" width="5.140625" style="2" customWidth="1"/>
-    <col min="7188" max="7188" width="2.7109375" style="2" customWidth="1"/>
-    <col min="7189" max="7189" width="15.7109375" style="2" customWidth="1"/>
-    <col min="7190" max="7423" width="8.85546875" style="2"/>
-    <col min="7424" max="7424" width="14.7109375" style="2" customWidth="1"/>
-    <col min="7425" max="7425" width="5.140625" style="2" customWidth="1"/>
-    <col min="7426" max="7432" width="4.140625" style="2" customWidth="1"/>
-    <col min="7433" max="7435" width="3.7109375" style="2" customWidth="1"/>
-    <col min="7436" max="7438" width="4.140625" style="2" customWidth="1"/>
-    <col min="7439" max="7440" width="4.7109375" style="2" customWidth="1"/>
-    <col min="7441" max="7443" width="5.140625" style="2" customWidth="1"/>
-    <col min="7444" max="7444" width="2.7109375" style="2" customWidth="1"/>
-    <col min="7445" max="7445" width="15.7109375" style="2" customWidth="1"/>
-    <col min="7446" max="7679" width="8.85546875" style="2"/>
-    <col min="7680" max="7680" width="14.7109375" style="2" customWidth="1"/>
-    <col min="7681" max="7681" width="5.140625" style="2" customWidth="1"/>
-    <col min="7682" max="7688" width="4.140625" style="2" customWidth="1"/>
-    <col min="7689" max="7691" width="3.7109375" style="2" customWidth="1"/>
-    <col min="7692" max="7694" width="4.140625" style="2" customWidth="1"/>
-    <col min="7695" max="7696" width="4.7109375" style="2" customWidth="1"/>
-    <col min="7697" max="7699" width="5.140625" style="2" customWidth="1"/>
-    <col min="7700" max="7700" width="2.7109375" style="2" customWidth="1"/>
-    <col min="7701" max="7701" width="15.7109375" style="2" customWidth="1"/>
-    <col min="7702" max="7935" width="8.85546875" style="2"/>
-    <col min="7936" max="7936" width="14.7109375" style="2" customWidth="1"/>
-    <col min="7937" max="7937" width="5.140625" style="2" customWidth="1"/>
-    <col min="7938" max="7944" width="4.140625" style="2" customWidth="1"/>
-    <col min="7945" max="7947" width="3.7109375" style="2" customWidth="1"/>
-    <col min="7948" max="7950" width="4.140625" style="2" customWidth="1"/>
-    <col min="7951" max="7952" width="4.7109375" style="2" customWidth="1"/>
-    <col min="7953" max="7955" width="5.140625" style="2" customWidth="1"/>
-    <col min="7956" max="7956" width="2.7109375" style="2" customWidth="1"/>
-    <col min="7957" max="7957" width="15.7109375" style="2" customWidth="1"/>
-    <col min="7958" max="8191" width="8.85546875" style="2"/>
-    <col min="8192" max="8192" width="14.7109375" style="2" customWidth="1"/>
-    <col min="8193" max="8193" width="5.140625" style="2" customWidth="1"/>
-    <col min="8194" max="8200" width="4.140625" style="2" customWidth="1"/>
-    <col min="8201" max="8203" width="3.7109375" style="2" customWidth="1"/>
-    <col min="8204" max="8206" width="4.140625" style="2" customWidth="1"/>
-    <col min="8207" max="8208" width="4.7109375" style="2" customWidth="1"/>
-    <col min="8209" max="8211" width="5.140625" style="2" customWidth="1"/>
-    <col min="8212" max="8212" width="2.7109375" style="2" customWidth="1"/>
-    <col min="8213" max="8213" width="15.7109375" style="2" customWidth="1"/>
-    <col min="8214" max="8447" width="8.85546875" style="2"/>
-    <col min="8448" max="8448" width="14.7109375" style="2" customWidth="1"/>
-    <col min="8449" max="8449" width="5.140625" style="2" customWidth="1"/>
-    <col min="8450" max="8456" width="4.140625" style="2" customWidth="1"/>
-    <col min="8457" max="8459" width="3.7109375" style="2" customWidth="1"/>
-    <col min="8460" max="8462" width="4.140625" style="2" customWidth="1"/>
-    <col min="8463" max="8464" width="4.7109375" style="2" customWidth="1"/>
-    <col min="8465" max="8467" width="5.140625" style="2" customWidth="1"/>
-    <col min="8468" max="8468" width="2.7109375" style="2" customWidth="1"/>
-    <col min="8469" max="8469" width="15.7109375" style="2" customWidth="1"/>
-    <col min="8470" max="8703" width="8.85546875" style="2"/>
-    <col min="8704" max="8704" width="14.7109375" style="2" customWidth="1"/>
-    <col min="8705" max="8705" width="5.140625" style="2" customWidth="1"/>
-    <col min="8706" max="8712" width="4.140625" style="2" customWidth="1"/>
-    <col min="8713" max="8715" width="3.7109375" style="2" customWidth="1"/>
-    <col min="8716" max="8718" width="4.140625" style="2" customWidth="1"/>
-    <col min="8719" max="8720" width="4.7109375" style="2" customWidth="1"/>
-    <col min="8721" max="8723" width="5.140625" style="2" customWidth="1"/>
-    <col min="8724" max="8724" width="2.7109375" style="2" customWidth="1"/>
-    <col min="8725" max="8725" width="15.7109375" style="2" customWidth="1"/>
-    <col min="8726" max="8959" width="8.85546875" style="2"/>
-    <col min="8960" max="8960" width="14.7109375" style="2" customWidth="1"/>
-    <col min="8961" max="8961" width="5.140625" style="2" customWidth="1"/>
-    <col min="8962" max="8968" width="4.140625" style="2" customWidth="1"/>
-    <col min="8969" max="8971" width="3.7109375" style="2" customWidth="1"/>
-    <col min="8972" max="8974" width="4.140625" style="2" customWidth="1"/>
-    <col min="8975" max="8976" width="4.7109375" style="2" customWidth="1"/>
-    <col min="8977" max="8979" width="5.140625" style="2" customWidth="1"/>
-    <col min="8980" max="8980" width="2.7109375" style="2" customWidth="1"/>
-    <col min="8981" max="8981" width="15.7109375" style="2" customWidth="1"/>
-    <col min="8982" max="9215" width="8.85546875" style="2"/>
-    <col min="9216" max="9216" width="14.7109375" style="2" customWidth="1"/>
-    <col min="9217" max="9217" width="5.140625" style="2" customWidth="1"/>
-    <col min="9218" max="9224" width="4.140625" style="2" customWidth="1"/>
-    <col min="9225" max="9227" width="3.7109375" style="2" customWidth="1"/>
-    <col min="9228" max="9230" width="4.140625" style="2" customWidth="1"/>
-    <col min="9231" max="9232" width="4.7109375" style="2" customWidth="1"/>
-    <col min="9233" max="9235" width="5.140625" style="2" customWidth="1"/>
-    <col min="9236" max="9236" width="2.7109375" style="2" customWidth="1"/>
-    <col min="9237" max="9237" width="15.7109375" style="2" customWidth="1"/>
-    <col min="9238" max="9471" width="8.85546875" style="2"/>
-    <col min="9472" max="9472" width="14.7109375" style="2" customWidth="1"/>
-    <col min="9473" max="9473" width="5.140625" style="2" customWidth="1"/>
-    <col min="9474" max="9480" width="4.140625" style="2" customWidth="1"/>
-    <col min="9481" max="9483" width="3.7109375" style="2" customWidth="1"/>
-    <col min="9484" max="9486" width="4.140625" style="2" customWidth="1"/>
-    <col min="9487" max="9488" width="4.7109375" style="2" customWidth="1"/>
-    <col min="9489" max="9491" width="5.140625" style="2" customWidth="1"/>
-    <col min="9492" max="9492" width="2.7109375" style="2" customWidth="1"/>
-    <col min="9493" max="9493" width="15.7109375" style="2" customWidth="1"/>
-    <col min="9494" max="9727" width="8.85546875" style="2"/>
-    <col min="9728" max="9728" width="14.7109375" style="2" customWidth="1"/>
-    <col min="9729" max="9729" width="5.140625" style="2" customWidth="1"/>
-    <col min="9730" max="9736" width="4.140625" style="2" customWidth="1"/>
-    <col min="9737" max="9739" width="3.7109375" style="2" customWidth="1"/>
-    <col min="9740" max="9742" width="4.140625" style="2" customWidth="1"/>
-    <col min="9743" max="9744" width="4.7109375" style="2" customWidth="1"/>
-    <col min="9745" max="9747" width="5.140625" style="2" customWidth="1"/>
-    <col min="9748" max="9748" width="2.7109375" style="2" customWidth="1"/>
-    <col min="9749" max="9749" width="15.7109375" style="2" customWidth="1"/>
-    <col min="9750" max="9983" width="8.85546875" style="2"/>
-    <col min="9984" max="9984" width="14.7109375" style="2" customWidth="1"/>
-    <col min="9985" max="9985" width="5.140625" style="2" customWidth="1"/>
-    <col min="9986" max="9992" width="4.140625" style="2" customWidth="1"/>
-    <col min="9993" max="9995" width="3.7109375" style="2" customWidth="1"/>
-    <col min="9996" max="9998" width="4.140625" style="2" customWidth="1"/>
-    <col min="9999" max="10000" width="4.7109375" style="2" customWidth="1"/>
-    <col min="10001" max="10003" width="5.140625" style="2" customWidth="1"/>
-    <col min="10004" max="10004" width="2.7109375" style="2" customWidth="1"/>
-    <col min="10005" max="10005" width="15.7109375" style="2" customWidth="1"/>
-    <col min="10006" max="10239" width="8.85546875" style="2"/>
-    <col min="10240" max="10240" width="14.7109375" style="2" customWidth="1"/>
-    <col min="10241" max="10241" width="5.140625" style="2" customWidth="1"/>
-    <col min="10242" max="10248" width="4.140625" style="2" customWidth="1"/>
-    <col min="10249" max="10251" width="3.7109375" style="2" customWidth="1"/>
-    <col min="10252" max="10254" width="4.140625" style="2" customWidth="1"/>
-    <col min="10255" max="10256" width="4.7109375" style="2" customWidth="1"/>
-    <col min="10257" max="10259" width="5.140625" style="2" customWidth="1"/>
-    <col min="10260" max="10260" width="2.7109375" style="2" customWidth="1"/>
-    <col min="10261" max="10261" width="15.7109375" style="2" customWidth="1"/>
-    <col min="10262" max="10495" width="8.85546875" style="2"/>
-    <col min="10496" max="10496" width="14.7109375" style="2" customWidth="1"/>
-    <col min="10497" max="10497" width="5.140625" style="2" customWidth="1"/>
-    <col min="10498" max="10504" width="4.140625" style="2" customWidth="1"/>
-    <col min="10505" max="10507" width="3.7109375" style="2" customWidth="1"/>
-    <col min="10508" max="10510" width="4.140625" style="2" customWidth="1"/>
-    <col min="10511" max="10512" width="4.7109375" style="2" customWidth="1"/>
-    <col min="10513" max="10515" width="5.140625" style="2" customWidth="1"/>
-    <col min="10516" max="10516" width="2.7109375" style="2" customWidth="1"/>
-    <col min="10517" max="10517" width="15.7109375" style="2" customWidth="1"/>
-    <col min="10518" max="10751" width="8.85546875" style="2"/>
-    <col min="10752" max="10752" width="14.7109375" style="2" customWidth="1"/>
-    <col min="10753" max="10753" width="5.140625" style="2" customWidth="1"/>
-    <col min="10754" max="10760" width="4.140625" style="2" customWidth="1"/>
-    <col min="10761" max="10763" width="3.7109375" style="2" customWidth="1"/>
-    <col min="10764" max="10766" width="4.140625" style="2" customWidth="1"/>
-    <col min="10767" max="10768" width="4.7109375" style="2" customWidth="1"/>
-    <col min="10769" max="10771" width="5.140625" style="2" customWidth="1"/>
-    <col min="10772" max="10772" width="2.7109375" style="2" customWidth="1"/>
-    <col min="10773" max="10773" width="15.7109375" style="2" customWidth="1"/>
-    <col min="10774" max="11007" width="8.85546875" style="2"/>
-    <col min="11008" max="11008" width="14.7109375" style="2" customWidth="1"/>
-    <col min="11009" max="11009" width="5.140625" style="2" customWidth="1"/>
-    <col min="11010" max="11016" width="4.140625" style="2" customWidth="1"/>
-    <col min="11017" max="11019" width="3.7109375" style="2" customWidth="1"/>
-    <col min="11020" max="11022" width="4.140625" style="2" customWidth="1"/>
-    <col min="11023" max="11024" width="4.7109375" style="2" customWidth="1"/>
-    <col min="11025" max="11027" width="5.140625" style="2" customWidth="1"/>
-    <col min="11028" max="11028" width="2.7109375" style="2" customWidth="1"/>
-    <col min="11029" max="11029" width="15.7109375" style="2" customWidth="1"/>
-    <col min="11030" max="11263" width="8.85546875" style="2"/>
-    <col min="11264" max="11264" width="14.7109375" style="2" customWidth="1"/>
-    <col min="11265" max="11265" width="5.140625" style="2" customWidth="1"/>
-    <col min="11266" max="11272" width="4.140625" style="2" customWidth="1"/>
-    <col min="11273" max="11275" width="3.7109375" style="2" customWidth="1"/>
-    <col min="11276" max="11278" width="4.140625" style="2" customWidth="1"/>
-    <col min="11279" max="11280" width="4.7109375" style="2" customWidth="1"/>
-    <col min="11281" max="11283" width="5.140625" style="2" customWidth="1"/>
-    <col min="11284" max="11284" width="2.7109375" style="2" customWidth="1"/>
-    <col min="11285" max="11285" width="15.7109375" style="2" customWidth="1"/>
-    <col min="11286" max="11519" width="8.85546875" style="2"/>
-    <col min="11520" max="11520" width="14.7109375" style="2" customWidth="1"/>
-    <col min="11521" max="11521" width="5.140625" style="2" customWidth="1"/>
-    <col min="11522" max="11528" width="4.140625" style="2" customWidth="1"/>
-    <col min="11529" max="11531" width="3.7109375" style="2" customWidth="1"/>
-    <col min="11532" max="11534" width="4.140625" style="2" customWidth="1"/>
-    <col min="11535" max="11536" width="4.7109375" style="2" customWidth="1"/>
-    <col min="11537" max="11539" width="5.140625" style="2" customWidth="1"/>
-    <col min="11540" max="11540" width="2.7109375" style="2" customWidth="1"/>
-    <col min="11541" max="11541" width="15.7109375" style="2" customWidth="1"/>
-    <col min="11542" max="11775" width="8.85546875" style="2"/>
-    <col min="11776" max="11776" width="14.7109375" style="2" customWidth="1"/>
-    <col min="11777" max="11777" width="5.140625" style="2" customWidth="1"/>
-    <col min="11778" max="11784" width="4.140625" style="2" customWidth="1"/>
-    <col min="11785" max="11787" width="3.7109375" style="2" customWidth="1"/>
-    <col min="11788" max="11790" width="4.140625" style="2" customWidth="1"/>
-    <col min="11791" max="11792" width="4.7109375" style="2" customWidth="1"/>
-    <col min="11793" max="11795" width="5.140625" style="2" customWidth="1"/>
-    <col min="11796" max="11796" width="2.7109375" style="2" customWidth="1"/>
-    <col min="11797" max="11797" width="15.7109375" style="2" customWidth="1"/>
-    <col min="11798" max="12031" width="8.85546875" style="2"/>
-    <col min="12032" max="12032" width="14.7109375" style="2" customWidth="1"/>
-    <col min="12033" max="12033" width="5.140625" style="2" customWidth="1"/>
-    <col min="12034" max="12040" width="4.140625" style="2" customWidth="1"/>
-    <col min="12041" max="12043" width="3.7109375" style="2" customWidth="1"/>
-    <col min="12044" max="12046" width="4.140625" style="2" customWidth="1"/>
-    <col min="12047" max="12048" width="4.7109375" style="2" customWidth="1"/>
-    <col min="12049" max="12051" width="5.140625" style="2" customWidth="1"/>
-    <col min="12052" max="12052" width="2.7109375" style="2" customWidth="1"/>
-    <col min="12053" max="12053" width="15.7109375" style="2" customWidth="1"/>
-    <col min="12054" max="12287" width="8.85546875" style="2"/>
-    <col min="12288" max="12288" width="14.7109375" style="2" customWidth="1"/>
-    <col min="12289" max="12289" width="5.140625" style="2" customWidth="1"/>
-    <col min="12290" max="12296" width="4.140625" style="2" customWidth="1"/>
-    <col min="12297" max="12299" width="3.7109375" style="2" customWidth="1"/>
-    <col min="12300" max="12302" width="4.140625" style="2" customWidth="1"/>
-    <col min="12303" max="12304" width="4.7109375" style="2" customWidth="1"/>
-    <col min="12305" max="12307" width="5.140625" style="2" customWidth="1"/>
-    <col min="12308" max="12308" width="2.7109375" style="2" customWidth="1"/>
-    <col min="12309" max="12309" width="15.7109375" style="2" customWidth="1"/>
-    <col min="12310" max="12543" width="8.85546875" style="2"/>
-    <col min="12544" max="12544" width="14.7109375" style="2" customWidth="1"/>
-    <col min="12545" max="12545" width="5.140625" style="2" customWidth="1"/>
-    <col min="12546" max="12552" width="4.140625" style="2" customWidth="1"/>
-    <col min="12553" max="12555" width="3.7109375" style="2" customWidth="1"/>
-    <col min="12556" max="12558" width="4.140625" style="2" customWidth="1"/>
-    <col min="12559" max="12560" width="4.7109375" style="2" customWidth="1"/>
-    <col min="12561" max="12563" width="5.140625" style="2" customWidth="1"/>
-    <col min="12564" max="12564" width="2.7109375" style="2" customWidth="1"/>
-    <col min="12565" max="12565" width="15.7109375" style="2" customWidth="1"/>
-    <col min="12566" max="12799" width="8.85546875" style="2"/>
-    <col min="12800" max="12800" width="14.7109375" style="2" customWidth="1"/>
-    <col min="12801" max="12801" width="5.140625" style="2" customWidth="1"/>
-    <col min="12802" max="12808" width="4.140625" style="2" customWidth="1"/>
-    <col min="12809" max="12811" width="3.7109375" style="2" customWidth="1"/>
-    <col min="12812" max="12814" width="4.140625" style="2" customWidth="1"/>
-    <col min="12815" max="12816" width="4.7109375" style="2" customWidth="1"/>
-    <col min="12817" max="12819" width="5.140625" style="2" customWidth="1"/>
-    <col min="12820" max="12820" width="2.7109375" style="2" customWidth="1"/>
-    <col min="12821" max="12821" width="15.7109375" style="2" customWidth="1"/>
-    <col min="12822" max="13055" width="8.85546875" style="2"/>
-    <col min="13056" max="13056" width="14.7109375" style="2" customWidth="1"/>
-    <col min="13057" max="13057" width="5.140625" style="2" customWidth="1"/>
-    <col min="13058" max="13064" width="4.140625" style="2" customWidth="1"/>
-    <col min="13065" max="13067" width="3.7109375" style="2" customWidth="1"/>
-    <col min="13068" max="13070" width="4.140625" style="2" customWidth="1"/>
-    <col min="13071" max="13072" width="4.7109375" style="2" customWidth="1"/>
-    <col min="13073" max="13075" width="5.140625" style="2" customWidth="1"/>
-    <col min="13076" max="13076" width="2.7109375" style="2" customWidth="1"/>
-    <col min="13077" max="13077" width="15.7109375" style="2" customWidth="1"/>
-    <col min="13078" max="13311" width="8.85546875" style="2"/>
-    <col min="13312" max="13312" width="14.7109375" style="2" customWidth="1"/>
-    <col min="13313" max="13313" width="5.140625" style="2" customWidth="1"/>
-    <col min="13314" max="13320" width="4.140625" style="2" customWidth="1"/>
-    <col min="13321" max="13323" width="3.7109375" style="2" customWidth="1"/>
-    <col min="13324" max="13326" width="4.140625" style="2" customWidth="1"/>
-    <col min="13327" max="13328" width="4.7109375" style="2" customWidth="1"/>
-    <col min="13329" max="13331" width="5.140625" style="2" customWidth="1"/>
-    <col min="13332" max="13332" width="2.7109375" style="2" customWidth="1"/>
-    <col min="13333" max="13333" width="15.7109375" style="2" customWidth="1"/>
-    <col min="13334" max="13567" width="8.85546875" style="2"/>
-    <col min="13568" max="13568" width="14.7109375" style="2" customWidth="1"/>
-    <col min="13569" max="13569" width="5.140625" style="2" customWidth="1"/>
-    <col min="13570" max="13576" width="4.140625" style="2" customWidth="1"/>
-    <col min="13577" max="13579" width="3.7109375" style="2" customWidth="1"/>
-    <col min="13580" max="13582" width="4.140625" style="2" customWidth="1"/>
-    <col min="13583" max="13584" width="4.7109375" style="2" customWidth="1"/>
-    <col min="13585" max="13587" width="5.140625" style="2" customWidth="1"/>
-    <col min="13588" max="13588" width="2.7109375" style="2" customWidth="1"/>
-    <col min="13589" max="13589" width="15.7109375" style="2" customWidth="1"/>
-    <col min="13590" max="13823" width="8.85546875" style="2"/>
-    <col min="13824" max="13824" width="14.7109375" style="2" customWidth="1"/>
-    <col min="13825" max="13825" width="5.140625" style="2" customWidth="1"/>
-    <col min="13826" max="13832" width="4.140625" style="2" customWidth="1"/>
-    <col min="13833" max="13835" width="3.7109375" style="2" customWidth="1"/>
-    <col min="13836" max="13838" width="4.140625" style="2" customWidth="1"/>
-    <col min="13839" max="13840" width="4.7109375" style="2" customWidth="1"/>
-    <col min="13841" max="13843" width="5.140625" style="2" customWidth="1"/>
-    <col min="13844" max="13844" width="2.7109375" style="2" customWidth="1"/>
-    <col min="13845" max="13845" width="15.7109375" style="2" customWidth="1"/>
-    <col min="13846" max="14079" width="8.85546875" style="2"/>
-    <col min="14080" max="14080" width="14.7109375" style="2" customWidth="1"/>
-    <col min="14081" max="14081" width="5.140625" style="2" customWidth="1"/>
-    <col min="14082" max="14088" width="4.140625" style="2" customWidth="1"/>
-    <col min="14089" max="14091" width="3.7109375" style="2" customWidth="1"/>
-    <col min="14092" max="14094" width="4.140625" style="2" customWidth="1"/>
-    <col min="14095" max="14096" width="4.7109375" style="2" customWidth="1"/>
-    <col min="14097" max="14099" width="5.140625" style="2" customWidth="1"/>
-    <col min="14100" max="14100" width="2.7109375" style="2" customWidth="1"/>
-    <col min="14101" max="14101" width="15.7109375" style="2" customWidth="1"/>
-    <col min="14102" max="14335" width="8.85546875" style="2"/>
-    <col min="14336" max="14336" width="14.7109375" style="2" customWidth="1"/>
-    <col min="14337" max="14337" width="5.140625" style="2" customWidth="1"/>
-    <col min="14338" max="14344" width="4.140625" style="2" customWidth="1"/>
-    <col min="14345" max="14347" width="3.7109375" style="2" customWidth="1"/>
-    <col min="14348" max="14350" width="4.140625" style="2" customWidth="1"/>
-    <col min="14351" max="14352" width="4.7109375" style="2" customWidth="1"/>
-    <col min="14353" max="14355" width="5.140625" style="2" customWidth="1"/>
-    <col min="14356" max="14356" width="2.7109375" style="2" customWidth="1"/>
-    <col min="14357" max="14357" width="15.7109375" style="2" customWidth="1"/>
-    <col min="14358" max="14591" width="8.85546875" style="2"/>
-    <col min="14592" max="14592" width="14.7109375" style="2" customWidth="1"/>
-    <col min="14593" max="14593" width="5.140625" style="2" customWidth="1"/>
-    <col min="14594" max="14600" width="4.140625" style="2" customWidth="1"/>
-    <col min="14601" max="14603" width="3.7109375" style="2" customWidth="1"/>
-    <col min="14604" max="14606" width="4.140625" style="2" customWidth="1"/>
-    <col min="14607" max="14608" width="4.7109375" style="2" customWidth="1"/>
-    <col min="14609" max="14611" width="5.140625" style="2" customWidth="1"/>
-    <col min="14612" max="14612" width="2.7109375" style="2" customWidth="1"/>
-    <col min="14613" max="14613" width="15.7109375" style="2" customWidth="1"/>
-    <col min="14614" max="14847" width="8.85546875" style="2"/>
-    <col min="14848" max="14848" width="14.7109375" style="2" customWidth="1"/>
-    <col min="14849" max="14849" width="5.140625" style="2" customWidth="1"/>
-    <col min="14850" max="14856" width="4.140625" style="2" customWidth="1"/>
-    <col min="14857" max="14859" width="3.7109375" style="2" customWidth="1"/>
-    <col min="14860" max="14862" width="4.140625" style="2" customWidth="1"/>
-    <col min="14863" max="14864" width="4.7109375" style="2" customWidth="1"/>
-    <col min="14865" max="14867" width="5.140625" style="2" customWidth="1"/>
-    <col min="14868" max="14868" width="2.7109375" style="2" customWidth="1"/>
-    <col min="14869" max="14869" width="15.7109375" style="2" customWidth="1"/>
-    <col min="14870" max="15103" width="8.85546875" style="2"/>
-    <col min="15104" max="15104" width="14.7109375" style="2" customWidth="1"/>
-    <col min="15105" max="15105" width="5.140625" style="2" customWidth="1"/>
-    <col min="15106" max="15112" width="4.140625" style="2" customWidth="1"/>
-    <col min="15113" max="15115" width="3.7109375" style="2" customWidth="1"/>
-    <col min="15116" max="15118" width="4.140625" style="2" customWidth="1"/>
-    <col min="15119" max="15120" width="4.7109375" style="2" customWidth="1"/>
-    <col min="15121" max="15123" width="5.140625" style="2" customWidth="1"/>
-    <col min="15124" max="15124" width="2.7109375" style="2" customWidth="1"/>
-    <col min="15125" max="15125" width="15.7109375" style="2" customWidth="1"/>
-    <col min="15126" max="15359" width="8.85546875" style="2"/>
-    <col min="15360" max="15360" width="14.7109375" style="2" customWidth="1"/>
-    <col min="15361" max="15361" width="5.140625" style="2" customWidth="1"/>
-    <col min="15362" max="15368" width="4.140625" style="2" customWidth="1"/>
-    <col min="15369" max="15371" width="3.7109375" style="2" customWidth="1"/>
-    <col min="15372" max="15374" width="4.140625" style="2" customWidth="1"/>
-    <col min="15375" max="15376" width="4.7109375" style="2" customWidth="1"/>
-    <col min="15377" max="15379" width="5.140625" style="2" customWidth="1"/>
-    <col min="15380" max="15380" width="2.7109375" style="2" customWidth="1"/>
-    <col min="15381" max="15381" width="15.7109375" style="2" customWidth="1"/>
-    <col min="15382" max="15615" width="8.85546875" style="2"/>
-    <col min="15616" max="15616" width="14.7109375" style="2" customWidth="1"/>
-    <col min="15617" max="15617" width="5.140625" style="2" customWidth="1"/>
-    <col min="15618" max="15624" width="4.140625" style="2" customWidth="1"/>
-    <col min="15625" max="15627" width="3.7109375" style="2" customWidth="1"/>
-    <col min="15628" max="15630" width="4.140625" style="2" customWidth="1"/>
-    <col min="15631" max="15632" width="4.7109375" style="2" customWidth="1"/>
-    <col min="15633" max="15635" width="5.140625" style="2" customWidth="1"/>
-    <col min="15636" max="15636" width="2.7109375" style="2" customWidth="1"/>
-    <col min="15637" max="15637" width="15.7109375" style="2" customWidth="1"/>
-    <col min="15638" max="15871" width="8.85546875" style="2"/>
-    <col min="15872" max="15872" width="14.7109375" style="2" customWidth="1"/>
-    <col min="15873" max="15873" width="5.140625" style="2" customWidth="1"/>
-    <col min="15874" max="15880" width="4.140625" style="2" customWidth="1"/>
-    <col min="15881" max="15883" width="3.7109375" style="2" customWidth="1"/>
-    <col min="15884" max="15886" width="4.140625" style="2" customWidth="1"/>
-    <col min="15887" max="15888" width="4.7109375" style="2" customWidth="1"/>
-    <col min="15889" max="15891" width="5.140625" style="2" customWidth="1"/>
-    <col min="15892" max="15892" width="2.7109375" style="2" customWidth="1"/>
-    <col min="15893" max="15893" width="15.7109375" style="2" customWidth="1"/>
-    <col min="15894" max="16127" width="8.85546875" style="2"/>
-    <col min="16128" max="16128" width="14.7109375" style="2" customWidth="1"/>
-    <col min="16129" max="16129" width="5.140625" style="2" customWidth="1"/>
-    <col min="16130" max="16136" width="4.140625" style="2" customWidth="1"/>
-    <col min="16137" max="16139" width="3.7109375" style="2" customWidth="1"/>
-    <col min="16140" max="16142" width="4.140625" style="2" customWidth="1"/>
-    <col min="16143" max="16144" width="4.7109375" style="2" customWidth="1"/>
-    <col min="16145" max="16147" width="5.140625" style="2" customWidth="1"/>
-    <col min="16148" max="16148" width="2.7109375" style="2" customWidth="1"/>
-    <col min="16149" max="16149" width="15.7109375" style="2" customWidth="1"/>
-    <col min="16150" max="16384" width="8.85546875" style="2"/>
+    <col min="29" max="30" width="9.109375" style="2" hidden="1" customWidth="1"/>
+    <col min="31" max="31" width="10.44140625" style="98" customWidth="1"/>
+    <col min="32" max="34" width="8.88671875" style="98"/>
+    <col min="35" max="255" width="8.88671875" style="2"/>
+    <col min="256" max="256" width="14.6640625" style="2" customWidth="1"/>
+    <col min="257" max="257" width="5.109375" style="2" customWidth="1"/>
+    <col min="258" max="264" width="4.109375" style="2" customWidth="1"/>
+    <col min="265" max="267" width="3.6640625" style="2" customWidth="1"/>
+    <col min="268" max="270" width="4.109375" style="2" customWidth="1"/>
+    <col min="271" max="272" width="4.6640625" style="2" customWidth="1"/>
+    <col min="273" max="275" width="5.109375" style="2" customWidth="1"/>
+    <col min="276" max="276" width="2.6640625" style="2" customWidth="1"/>
+    <col min="277" max="277" width="15.6640625" style="2" customWidth="1"/>
+    <col min="278" max="511" width="8.88671875" style="2"/>
+    <col min="512" max="512" width="14.6640625" style="2" customWidth="1"/>
+    <col min="513" max="513" width="5.109375" style="2" customWidth="1"/>
+    <col min="514" max="520" width="4.109375" style="2" customWidth="1"/>
+    <col min="521" max="523" width="3.6640625" style="2" customWidth="1"/>
+    <col min="524" max="526" width="4.109375" style="2" customWidth="1"/>
+    <col min="527" max="528" width="4.6640625" style="2" customWidth="1"/>
+    <col min="529" max="531" width="5.109375" style="2" customWidth="1"/>
+    <col min="532" max="532" width="2.6640625" style="2" customWidth="1"/>
+    <col min="533" max="533" width="15.6640625" style="2" customWidth="1"/>
+    <col min="534" max="767" width="8.88671875" style="2"/>
+    <col min="768" max="768" width="14.6640625" style="2" customWidth="1"/>
+    <col min="769" max="769" width="5.109375" style="2" customWidth="1"/>
+    <col min="770" max="776" width="4.109375" style="2" customWidth="1"/>
+    <col min="777" max="779" width="3.6640625" style="2" customWidth="1"/>
+    <col min="780" max="782" width="4.109375" style="2" customWidth="1"/>
+    <col min="783" max="784" width="4.6640625" style="2" customWidth="1"/>
+    <col min="785" max="787" width="5.109375" style="2" customWidth="1"/>
+    <col min="788" max="788" width="2.6640625" style="2" customWidth="1"/>
+    <col min="789" max="789" width="15.6640625" style="2" customWidth="1"/>
+    <col min="790" max="1023" width="8.88671875" style="2"/>
+    <col min="1024" max="1024" width="14.6640625" style="2" customWidth="1"/>
+    <col min="1025" max="1025" width="5.109375" style="2" customWidth="1"/>
+    <col min="1026" max="1032" width="4.109375" style="2" customWidth="1"/>
+    <col min="1033" max="1035" width="3.6640625" style="2" customWidth="1"/>
+    <col min="1036" max="1038" width="4.109375" style="2" customWidth="1"/>
+    <col min="1039" max="1040" width="4.6640625" style="2" customWidth="1"/>
+    <col min="1041" max="1043" width="5.109375" style="2" customWidth="1"/>
+    <col min="1044" max="1044" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1045" max="1045" width="15.6640625" style="2" customWidth="1"/>
+    <col min="1046" max="1279" width="8.88671875" style="2"/>
+    <col min="1280" max="1280" width="14.6640625" style="2" customWidth="1"/>
+    <col min="1281" max="1281" width="5.109375" style="2" customWidth="1"/>
+    <col min="1282" max="1288" width="4.109375" style="2" customWidth="1"/>
+    <col min="1289" max="1291" width="3.6640625" style="2" customWidth="1"/>
+    <col min="1292" max="1294" width="4.109375" style="2" customWidth="1"/>
+    <col min="1295" max="1296" width="4.6640625" style="2" customWidth="1"/>
+    <col min="1297" max="1299" width="5.109375" style="2" customWidth="1"/>
+    <col min="1300" max="1300" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1301" max="1301" width="15.6640625" style="2" customWidth="1"/>
+    <col min="1302" max="1535" width="8.88671875" style="2"/>
+    <col min="1536" max="1536" width="14.6640625" style="2" customWidth="1"/>
+    <col min="1537" max="1537" width="5.109375" style="2" customWidth="1"/>
+    <col min="1538" max="1544" width="4.109375" style="2" customWidth="1"/>
+    <col min="1545" max="1547" width="3.6640625" style="2" customWidth="1"/>
+    <col min="1548" max="1550" width="4.109375" style="2" customWidth="1"/>
+    <col min="1551" max="1552" width="4.6640625" style="2" customWidth="1"/>
+    <col min="1553" max="1555" width="5.109375" style="2" customWidth="1"/>
+    <col min="1556" max="1556" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1557" max="1557" width="15.6640625" style="2" customWidth="1"/>
+    <col min="1558" max="1791" width="8.88671875" style="2"/>
+    <col min="1792" max="1792" width="14.6640625" style="2" customWidth="1"/>
+    <col min="1793" max="1793" width="5.109375" style="2" customWidth="1"/>
+    <col min="1794" max="1800" width="4.109375" style="2" customWidth="1"/>
+    <col min="1801" max="1803" width="3.6640625" style="2" customWidth="1"/>
+    <col min="1804" max="1806" width="4.109375" style="2" customWidth="1"/>
+    <col min="1807" max="1808" width="4.6640625" style="2" customWidth="1"/>
+    <col min="1809" max="1811" width="5.109375" style="2" customWidth="1"/>
+    <col min="1812" max="1812" width="2.6640625" style="2" customWidth="1"/>
+    <col min="1813" max="1813" width="15.6640625" style="2" customWidth="1"/>
+    <col min="1814" max="2047" width="8.88671875" style="2"/>
+    <col min="2048" max="2048" width="14.6640625" style="2" customWidth="1"/>
+    <col min="2049" max="2049" width="5.109375" style="2" customWidth="1"/>
+    <col min="2050" max="2056" width="4.109375" style="2" customWidth="1"/>
+    <col min="2057" max="2059" width="3.6640625" style="2" customWidth="1"/>
+    <col min="2060" max="2062" width="4.109375" style="2" customWidth="1"/>
+    <col min="2063" max="2064" width="4.6640625" style="2" customWidth="1"/>
+    <col min="2065" max="2067" width="5.109375" style="2" customWidth="1"/>
+    <col min="2068" max="2068" width="2.6640625" style="2" customWidth="1"/>
+    <col min="2069" max="2069" width="15.6640625" style="2" customWidth="1"/>
+    <col min="2070" max="2303" width="8.88671875" style="2"/>
+    <col min="2304" max="2304" width="14.6640625" style="2" customWidth="1"/>
+    <col min="2305" max="2305" width="5.109375" style="2" customWidth="1"/>
+    <col min="2306" max="2312" width="4.109375" style="2" customWidth="1"/>
+    <col min="2313" max="2315" width="3.6640625" style="2" customWidth="1"/>
+    <col min="2316" max="2318" width="4.109375" style="2" customWidth="1"/>
+    <col min="2319" max="2320" width="4.6640625" style="2" customWidth="1"/>
+    <col min="2321" max="2323" width="5.109375" style="2" customWidth="1"/>
+    <col min="2324" max="2324" width="2.6640625" style="2" customWidth="1"/>
+    <col min="2325" max="2325" width="15.6640625" style="2" customWidth="1"/>
+    <col min="2326" max="2559" width="8.88671875" style="2"/>
+    <col min="2560" max="2560" width="14.6640625" style="2" customWidth="1"/>
+    <col min="2561" max="2561" width="5.109375" style="2" customWidth="1"/>
+    <col min="2562" max="2568" width="4.109375" style="2" customWidth="1"/>
+    <col min="2569" max="2571" width="3.6640625" style="2" customWidth="1"/>
+    <col min="2572" max="2574" width="4.109375" style="2" customWidth="1"/>
+    <col min="2575" max="2576" width="4.6640625" style="2" customWidth="1"/>
+    <col min="2577" max="2579" width="5.109375" style="2" customWidth="1"/>
+    <col min="2580" max="2580" width="2.6640625" style="2" customWidth="1"/>
+    <col min="2581" max="2581" width="15.6640625" style="2" customWidth="1"/>
+    <col min="2582" max="2815" width="8.88671875" style="2"/>
+    <col min="2816" max="2816" width="14.6640625" style="2" customWidth="1"/>
+    <col min="2817" max="2817" width="5.109375" style="2" customWidth="1"/>
+    <col min="2818" max="2824" width="4.109375" style="2" customWidth="1"/>
+    <col min="2825" max="2827" width="3.6640625" style="2" customWidth="1"/>
+    <col min="2828" max="2830" width="4.109375" style="2" customWidth="1"/>
+    <col min="2831" max="2832" width="4.6640625" style="2" customWidth="1"/>
+    <col min="2833" max="2835" width="5.109375" style="2" customWidth="1"/>
+    <col min="2836" max="2836" width="2.6640625" style="2" customWidth="1"/>
+    <col min="2837" max="2837" width="15.6640625" style="2" customWidth="1"/>
+    <col min="2838" max="3071" width="8.88671875" style="2"/>
+    <col min="3072" max="3072" width="14.6640625" style="2" customWidth="1"/>
+    <col min="3073" max="3073" width="5.109375" style="2" customWidth="1"/>
+    <col min="3074" max="3080" width="4.109375" style="2" customWidth="1"/>
+    <col min="3081" max="3083" width="3.6640625" style="2" customWidth="1"/>
+    <col min="3084" max="3086" width="4.109375" style="2" customWidth="1"/>
+    <col min="3087" max="3088" width="4.6640625" style="2" customWidth="1"/>
+    <col min="3089" max="3091" width="5.109375" style="2" customWidth="1"/>
+    <col min="3092" max="3092" width="2.6640625" style="2" customWidth="1"/>
+    <col min="3093" max="3093" width="15.6640625" style="2" customWidth="1"/>
+    <col min="3094" max="3327" width="8.88671875" style="2"/>
+    <col min="3328" max="3328" width="14.6640625" style="2" customWidth="1"/>
+    <col min="3329" max="3329" width="5.109375" style="2" customWidth="1"/>
+    <col min="3330" max="3336" width="4.109375" style="2" customWidth="1"/>
+    <col min="3337" max="3339" width="3.6640625" style="2" customWidth="1"/>
+    <col min="3340" max="3342" width="4.109375" style="2" customWidth="1"/>
+    <col min="3343" max="3344" width="4.6640625" style="2" customWidth="1"/>
+    <col min="3345" max="3347" width="5.109375" style="2" customWidth="1"/>
+    <col min="3348" max="3348" width="2.6640625" style="2" customWidth="1"/>
+    <col min="3349" max="3349" width="15.6640625" style="2" customWidth="1"/>
+    <col min="3350" max="3583" width="8.88671875" style="2"/>
+    <col min="3584" max="3584" width="14.6640625" style="2" customWidth="1"/>
+    <col min="3585" max="3585" width="5.109375" style="2" customWidth="1"/>
+    <col min="3586" max="3592" width="4.109375" style="2" customWidth="1"/>
+    <col min="3593" max="3595" width="3.6640625" style="2" customWidth="1"/>
+    <col min="3596" max="3598" width="4.109375" style="2" customWidth="1"/>
+    <col min="3599" max="3600" width="4.6640625" style="2" customWidth="1"/>
+    <col min="3601" max="3603" width="5.109375" style="2" customWidth="1"/>
+    <col min="3604" max="3604" width="2.6640625" style="2" customWidth="1"/>
+    <col min="3605" max="3605" width="15.6640625" style="2" customWidth="1"/>
+    <col min="3606" max="3839" width="8.88671875" style="2"/>
+    <col min="3840" max="3840" width="14.6640625" style="2" customWidth="1"/>
+    <col min="3841" max="3841" width="5.109375" style="2" customWidth="1"/>
+    <col min="3842" max="3848" width="4.109375" style="2" customWidth="1"/>
+    <col min="3849" max="3851" width="3.6640625" style="2" customWidth="1"/>
+    <col min="3852" max="3854" width="4.109375" style="2" customWidth="1"/>
+    <col min="3855" max="3856" width="4.6640625" style="2" customWidth="1"/>
+    <col min="3857" max="3859" width="5.109375" style="2" customWidth="1"/>
+    <col min="3860" max="3860" width="2.6640625" style="2" customWidth="1"/>
+    <col min="3861" max="3861" width="15.6640625" style="2" customWidth="1"/>
+    <col min="3862" max="4095" width="8.88671875" style="2"/>
+    <col min="4096" max="4096" width="14.6640625" style="2" customWidth="1"/>
+    <col min="4097" max="4097" width="5.109375" style="2" customWidth="1"/>
+    <col min="4098" max="4104" width="4.109375" style="2" customWidth="1"/>
+    <col min="4105" max="4107" width="3.6640625" style="2" customWidth="1"/>
+    <col min="4108" max="4110" width="4.109375" style="2" customWidth="1"/>
+    <col min="4111" max="4112" width="4.6640625" style="2" customWidth="1"/>
+    <col min="4113" max="4115" width="5.109375" style="2" customWidth="1"/>
+    <col min="4116" max="4116" width="2.6640625" style="2" customWidth="1"/>
+    <col min="4117" max="4117" width="15.6640625" style="2" customWidth="1"/>
+    <col min="4118" max="4351" width="8.88671875" style="2"/>
+    <col min="4352" max="4352" width="14.6640625" style="2" customWidth="1"/>
+    <col min="4353" max="4353" width="5.109375" style="2" customWidth="1"/>
+    <col min="4354" max="4360" width="4.109375" style="2" customWidth="1"/>
+    <col min="4361" max="4363" width="3.6640625" style="2" customWidth="1"/>
+    <col min="4364" max="4366" width="4.109375" style="2" customWidth="1"/>
+    <col min="4367" max="4368" width="4.6640625" style="2" customWidth="1"/>
+    <col min="4369" max="4371" width="5.109375" style="2" customWidth="1"/>
+    <col min="4372" max="4372" width="2.6640625" style="2" customWidth="1"/>
+    <col min="4373" max="4373" width="15.6640625" style="2" customWidth="1"/>
+    <col min="4374" max="4607" width="8.88671875" style="2"/>
+    <col min="4608" max="4608" width="14.6640625" style="2" customWidth="1"/>
+    <col min="4609" max="4609" width="5.109375" style="2" customWidth="1"/>
+    <col min="4610" max="4616" width="4.109375" style="2" customWidth="1"/>
+    <col min="4617" max="4619" width="3.6640625" style="2" customWidth="1"/>
+    <col min="4620" max="4622" width="4.109375" style="2" customWidth="1"/>
+    <col min="4623" max="4624" width="4.6640625" style="2" customWidth="1"/>
+    <col min="4625" max="4627" width="5.109375" style="2" customWidth="1"/>
+    <col min="4628" max="4628" width="2.6640625" style="2" customWidth="1"/>
+    <col min="4629" max="4629" width="15.6640625" style="2" customWidth="1"/>
+    <col min="4630" max="4863" width="8.88671875" style="2"/>
+    <col min="4864" max="4864" width="14.6640625" style="2" customWidth="1"/>
+    <col min="4865" max="4865" width="5.109375" style="2" customWidth="1"/>
+    <col min="4866" max="4872" width="4.109375" style="2" customWidth="1"/>
+    <col min="4873" max="4875" width="3.6640625" style="2" customWidth="1"/>
+    <col min="4876" max="4878" width="4.109375" style="2" customWidth="1"/>
+    <col min="4879" max="4880" width="4.6640625" style="2" customWidth="1"/>
+    <col min="4881" max="4883" width="5.109375" style="2" customWidth="1"/>
+    <col min="4884" max="4884" width="2.6640625" style="2" customWidth="1"/>
+    <col min="4885" max="4885" width="15.6640625" style="2" customWidth="1"/>
+    <col min="4886" max="5119" width="8.88671875" style="2"/>
+    <col min="5120" max="5120" width="14.6640625" style="2" customWidth="1"/>
+    <col min="5121" max="5121" width="5.109375" style="2" customWidth="1"/>
+    <col min="5122" max="5128" width="4.109375" style="2" customWidth="1"/>
+    <col min="5129" max="5131" width="3.6640625" style="2" customWidth="1"/>
+    <col min="5132" max="5134" width="4.109375" style="2" customWidth="1"/>
+    <col min="5135" max="5136" width="4.6640625" style="2" customWidth="1"/>
+    <col min="5137" max="5139" width="5.109375" style="2" customWidth="1"/>
+    <col min="5140" max="5140" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5141" max="5141" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5142" max="5375" width="8.88671875" style="2"/>
+    <col min="5376" max="5376" width="14.6640625" style="2" customWidth="1"/>
+    <col min="5377" max="5377" width="5.109375" style="2" customWidth="1"/>
+    <col min="5378" max="5384" width="4.109375" style="2" customWidth="1"/>
+    <col min="5385" max="5387" width="3.6640625" style="2" customWidth="1"/>
+    <col min="5388" max="5390" width="4.109375" style="2" customWidth="1"/>
+    <col min="5391" max="5392" width="4.6640625" style="2" customWidth="1"/>
+    <col min="5393" max="5395" width="5.109375" style="2" customWidth="1"/>
+    <col min="5396" max="5396" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5397" max="5397" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5398" max="5631" width="8.88671875" style="2"/>
+    <col min="5632" max="5632" width="14.6640625" style="2" customWidth="1"/>
+    <col min="5633" max="5633" width="5.109375" style="2" customWidth="1"/>
+    <col min="5634" max="5640" width="4.109375" style="2" customWidth="1"/>
+    <col min="5641" max="5643" width="3.6640625" style="2" customWidth="1"/>
+    <col min="5644" max="5646" width="4.109375" style="2" customWidth="1"/>
+    <col min="5647" max="5648" width="4.6640625" style="2" customWidth="1"/>
+    <col min="5649" max="5651" width="5.109375" style="2" customWidth="1"/>
+    <col min="5652" max="5652" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5653" max="5653" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5654" max="5887" width="8.88671875" style="2"/>
+    <col min="5888" max="5888" width="14.6640625" style="2" customWidth="1"/>
+    <col min="5889" max="5889" width="5.109375" style="2" customWidth="1"/>
+    <col min="5890" max="5896" width="4.109375" style="2" customWidth="1"/>
+    <col min="5897" max="5899" width="3.6640625" style="2" customWidth="1"/>
+    <col min="5900" max="5902" width="4.109375" style="2" customWidth="1"/>
+    <col min="5903" max="5904" width="4.6640625" style="2" customWidth="1"/>
+    <col min="5905" max="5907" width="5.109375" style="2" customWidth="1"/>
+    <col min="5908" max="5908" width="2.6640625" style="2" customWidth="1"/>
+    <col min="5909" max="5909" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5910" max="6143" width="8.88671875" style="2"/>
+    <col min="6144" max="6144" width="14.6640625" style="2" customWidth="1"/>
+    <col min="6145" max="6145" width="5.109375" style="2" customWidth="1"/>
+    <col min="6146" max="6152" width="4.109375" style="2" customWidth="1"/>
+    <col min="6153" max="6155" width="3.6640625" style="2" customWidth="1"/>
+    <col min="6156" max="6158" width="4.109375" style="2" customWidth="1"/>
+    <col min="6159" max="6160" width="4.6640625" style="2" customWidth="1"/>
+    <col min="6161" max="6163" width="5.109375" style="2" customWidth="1"/>
+    <col min="6164" max="6164" width="2.6640625" style="2" customWidth="1"/>
+    <col min="6165" max="6165" width="15.6640625" style="2" customWidth="1"/>
+    <col min="6166" max="6399" width="8.88671875" style="2"/>
+    <col min="6400" max="6400" width="14.6640625" style="2" customWidth="1"/>
+    <col min="6401" max="6401" width="5.109375" style="2" customWidth="1"/>
+    <col min="6402" max="6408" width="4.109375" style="2" customWidth="1"/>
+    <col min="6409" max="6411" width="3.6640625" style="2" customWidth="1"/>
+    <col min="6412" max="6414" width="4.109375" style="2" customWidth="1"/>
+    <col min="6415" max="6416" width="4.6640625" style="2" customWidth="1"/>
+    <col min="6417" max="6419" width="5.109375" style="2" customWidth="1"/>
+    <col min="6420" max="6420" width="2.6640625" style="2" customWidth="1"/>
+    <col min="6421" max="6421" width="15.6640625" style="2" customWidth="1"/>
+    <col min="6422" max="6655" width="8.88671875" style="2"/>
+    <col min="6656" max="6656" width="14.6640625" style="2" customWidth="1"/>
+    <col min="6657" max="6657" width="5.109375" style="2" customWidth="1"/>
+    <col min="6658" max="6664" width="4.109375" style="2" customWidth="1"/>
+    <col min="6665" max="6667" width="3.6640625" style="2" customWidth="1"/>
+    <col min="6668" max="6670" width="4.109375" style="2" customWidth="1"/>
+    <col min="6671" max="6672" width="4.6640625" style="2" customWidth="1"/>
+    <col min="6673" max="6675" width="5.109375" style="2" customWidth="1"/>
+    <col min="6676" max="6676" width="2.6640625" style="2" customWidth="1"/>
+    <col min="6677" max="6677" width="15.6640625" style="2" customWidth="1"/>
+    <col min="6678" max="6911" width="8.88671875" style="2"/>
+    <col min="6912" max="6912" width="14.6640625" style="2" customWidth="1"/>
+    <col min="6913" max="6913" width="5.109375" style="2" customWidth="1"/>
+    <col min="6914" max="6920" width="4.109375" style="2" customWidth="1"/>
+    <col min="6921" max="6923" width="3.6640625" style="2" customWidth="1"/>
+    <col min="6924" max="6926" width="4.109375" style="2" customWidth="1"/>
+    <col min="6927" max="6928" width="4.6640625" style="2" customWidth="1"/>
+    <col min="6929" max="6931" width="5.109375" style="2" customWidth="1"/>
+    <col min="6932" max="6932" width="2.6640625" style="2" customWidth="1"/>
+    <col min="6933" max="6933" width="15.6640625" style="2" customWidth="1"/>
+    <col min="6934" max="7167" width="8.88671875" style="2"/>
+    <col min="7168" max="7168" width="14.6640625" style="2" customWidth="1"/>
+    <col min="7169" max="7169" width="5.109375" style="2" customWidth="1"/>
+    <col min="7170" max="7176" width="4.109375" style="2" customWidth="1"/>
+    <col min="7177" max="7179" width="3.6640625" style="2" customWidth="1"/>
+    <col min="7180" max="7182" width="4.109375" style="2" customWidth="1"/>
+    <col min="7183" max="7184" width="4.6640625" style="2" customWidth="1"/>
+    <col min="7185" max="7187" width="5.109375" style="2" customWidth="1"/>
+    <col min="7188" max="7188" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7189" max="7189" width="15.6640625" style="2" customWidth="1"/>
+    <col min="7190" max="7423" width="8.88671875" style="2"/>
+    <col min="7424" max="7424" width="14.6640625" style="2" customWidth="1"/>
+    <col min="7425" max="7425" width="5.109375" style="2" customWidth="1"/>
+    <col min="7426" max="7432" width="4.109375" style="2" customWidth="1"/>
+    <col min="7433" max="7435" width="3.6640625" style="2" customWidth="1"/>
+    <col min="7436" max="7438" width="4.109375" style="2" customWidth="1"/>
+    <col min="7439" max="7440" width="4.6640625" style="2" customWidth="1"/>
+    <col min="7441" max="7443" width="5.109375" style="2" customWidth="1"/>
+    <col min="7444" max="7444" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7445" max="7445" width="15.6640625" style="2" customWidth="1"/>
+    <col min="7446" max="7679" width="8.88671875" style="2"/>
+    <col min="7680" max="7680" width="14.6640625" style="2" customWidth="1"/>
+    <col min="7681" max="7681" width="5.109375" style="2" customWidth="1"/>
+    <col min="7682" max="7688" width="4.109375" style="2" customWidth="1"/>
+    <col min="7689" max="7691" width="3.6640625" style="2" customWidth="1"/>
+    <col min="7692" max="7694" width="4.109375" style="2" customWidth="1"/>
+    <col min="7695" max="7696" width="4.6640625" style="2" customWidth="1"/>
+    <col min="7697" max="7699" width="5.109375" style="2" customWidth="1"/>
+    <col min="7700" max="7700" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7701" max="7701" width="15.6640625" style="2" customWidth="1"/>
+    <col min="7702" max="7935" width="8.88671875" style="2"/>
+    <col min="7936" max="7936" width="14.6640625" style="2" customWidth="1"/>
+    <col min="7937" max="7937" width="5.109375" style="2" customWidth="1"/>
+    <col min="7938" max="7944" width="4.109375" style="2" customWidth="1"/>
+    <col min="7945" max="7947" width="3.6640625" style="2" customWidth="1"/>
+    <col min="7948" max="7950" width="4.109375" style="2" customWidth="1"/>
+    <col min="7951" max="7952" width="4.6640625" style="2" customWidth="1"/>
+    <col min="7953" max="7955" width="5.109375" style="2" customWidth="1"/>
+    <col min="7956" max="7956" width="2.6640625" style="2" customWidth="1"/>
+    <col min="7957" max="7957" width="15.6640625" style="2" customWidth="1"/>
+    <col min="7958" max="8191" width="8.88671875" style="2"/>
+    <col min="8192" max="8192" width="14.6640625" style="2" customWidth="1"/>
+    <col min="8193" max="8193" width="5.109375" style="2" customWidth="1"/>
+    <col min="8194" max="8200" width="4.109375" style="2" customWidth="1"/>
+    <col min="8201" max="8203" width="3.6640625" style="2" customWidth="1"/>
+    <col min="8204" max="8206" width="4.109375" style="2" customWidth="1"/>
+    <col min="8207" max="8208" width="4.6640625" style="2" customWidth="1"/>
+    <col min="8209" max="8211" width="5.109375" style="2" customWidth="1"/>
+    <col min="8212" max="8212" width="2.6640625" style="2" customWidth="1"/>
+    <col min="8213" max="8213" width="15.6640625" style="2" customWidth="1"/>
+    <col min="8214" max="8447" width="8.88671875" style="2"/>
+    <col min="8448" max="8448" width="14.6640625" style="2" customWidth="1"/>
+    <col min="8449" max="8449" width="5.109375" style="2" customWidth="1"/>
+    <col min="8450" max="8456" width="4.109375" style="2" customWidth="1"/>
+    <col min="8457" max="8459" width="3.6640625" style="2" customWidth="1"/>
+    <col min="8460" max="8462" width="4.109375" style="2" customWidth="1"/>
+    <col min="8463" max="8464" width="4.6640625" style="2" customWidth="1"/>
+    <col min="8465" max="8467" width="5.109375" style="2" customWidth="1"/>
+    <col min="8468" max="8468" width="2.6640625" style="2" customWidth="1"/>
+    <col min="8469" max="8469" width="15.6640625" style="2" customWidth="1"/>
+    <col min="8470" max="8703" width="8.88671875" style="2"/>
+    <col min="8704" max="8704" width="14.6640625" style="2" customWidth="1"/>
+    <col min="8705" max="8705" width="5.109375" style="2" customWidth="1"/>
+    <col min="8706" max="8712" width="4.109375" style="2" customWidth="1"/>
+    <col min="8713" max="8715" width="3.6640625" style="2" customWidth="1"/>
+    <col min="8716" max="8718" width="4.109375" style="2" customWidth="1"/>
+    <col min="8719" max="8720" width="4.6640625" style="2" customWidth="1"/>
+    <col min="8721" max="8723" width="5.109375" style="2" customWidth="1"/>
+    <col min="8724" max="8724" width="2.6640625" style="2" customWidth="1"/>
+    <col min="8725" max="8725" width="15.6640625" style="2" customWidth="1"/>
+    <col min="8726" max="8959" width="8.88671875" style="2"/>
+    <col min="8960" max="8960" width="14.6640625" style="2" customWidth="1"/>
+    <col min="8961" max="8961" width="5.109375" style="2" customWidth="1"/>
+    <col min="8962" max="8968" width="4.109375" style="2" customWidth="1"/>
+    <col min="8969" max="8971" width="3.6640625" style="2" customWidth="1"/>
+    <col min="8972" max="8974" width="4.109375" style="2" customWidth="1"/>
+    <col min="8975" max="8976" width="4.6640625" style="2" customWidth="1"/>
+    <col min="8977" max="8979" width="5.109375" style="2" customWidth="1"/>
+    <col min="8980" max="8980" width="2.6640625" style="2" customWidth="1"/>
+    <col min="8981" max="8981" width="15.6640625" style="2" customWidth="1"/>
+    <col min="8982" max="9215" width="8.88671875" style="2"/>
+    <col min="9216" max="9216" width="14.6640625" style="2" customWidth="1"/>
+    <col min="9217" max="9217" width="5.109375" style="2" customWidth="1"/>
+    <col min="9218" max="9224" width="4.109375" style="2" customWidth="1"/>
+    <col min="9225" max="9227" width="3.6640625" style="2" customWidth="1"/>
+    <col min="9228" max="9230" width="4.109375" style="2" customWidth="1"/>
+    <col min="9231" max="9232" width="4.6640625" style="2" customWidth="1"/>
+    <col min="9233" max="9235" width="5.109375" style="2" customWidth="1"/>
+    <col min="9236" max="9236" width="2.6640625" style="2" customWidth="1"/>
+    <col min="9237" max="9237" width="15.6640625" style="2" customWidth="1"/>
+    <col min="9238" max="9471" width="8.88671875" style="2"/>
+    <col min="9472" max="9472" width="14.6640625" style="2" customWidth="1"/>
+    <col min="9473" max="9473" width="5.109375" style="2" customWidth="1"/>
+    <col min="9474" max="9480" width="4.109375" style="2" customWidth="1"/>
+    <col min="9481" max="9483" width="3.6640625" style="2" customWidth="1"/>
+    <col min="9484" max="9486" width="4.109375" style="2" customWidth="1"/>
+    <col min="9487" max="9488" width="4.6640625" style="2" customWidth="1"/>
+    <col min="9489" max="9491" width="5.109375" style="2" customWidth="1"/>
+    <col min="9492" max="9492" width="2.6640625" style="2" customWidth="1"/>
+    <col min="9493" max="9493" width="15.6640625" style="2" customWidth="1"/>
+    <col min="9494" max="9727" width="8.88671875" style="2"/>
+    <col min="9728" max="9728" width="14.6640625" style="2" customWidth="1"/>
+    <col min="9729" max="9729" width="5.109375" style="2" customWidth="1"/>
+    <col min="9730" max="9736" width="4.109375" style="2" customWidth="1"/>
+    <col min="9737" max="9739" width="3.6640625" style="2" customWidth="1"/>
+    <col min="9740" max="9742" width="4.109375" style="2" customWidth="1"/>
+    <col min="9743" max="9744" width="4.6640625" style="2" customWidth="1"/>
+    <col min="9745" max="9747" width="5.109375" style="2" customWidth="1"/>
+    <col min="9748" max="9748" width="2.6640625" style="2" customWidth="1"/>
+    <col min="9749" max="9749" width="15.6640625" style="2" customWidth="1"/>
+    <col min="9750" max="9983" width="8.88671875" style="2"/>
+    <col min="9984" max="9984" width="14.6640625" style="2" customWidth="1"/>
+    <col min="9985" max="9985" width="5.109375" style="2" customWidth="1"/>
+    <col min="9986" max="9992" width="4.109375" style="2" customWidth="1"/>
+    <col min="9993" max="9995" width="3.6640625" style="2" customWidth="1"/>
+    <col min="9996" max="9998" width="4.109375" style="2" customWidth="1"/>
+    <col min="9999" max="10000" width="4.6640625" style="2" customWidth="1"/>
+    <col min="10001" max="10003" width="5.109375" style="2" customWidth="1"/>
+    <col min="10004" max="10004" width="2.6640625" style="2" customWidth="1"/>
+    <col min="10005" max="10005" width="15.6640625" style="2" customWidth="1"/>
+    <col min="10006" max="10239" width="8.88671875" style="2"/>
+    <col min="10240" max="10240" width="14.6640625" style="2" customWidth="1"/>
+    <col min="10241" max="10241" width="5.109375" style="2" customWidth="1"/>
+    <col min="10242" max="10248" width="4.109375" style="2" customWidth="1"/>
+    <col min="10249" max="10251" width="3.6640625" style="2" customWidth="1"/>
+    <col min="10252" max="10254" width="4.109375" style="2" customWidth="1"/>
+    <col min="10255" max="10256" width="4.6640625" style="2" customWidth="1"/>
+    <col min="10257" max="10259" width="5.109375" style="2" customWidth="1"/>
+    <col min="10260" max="10260" width="2.6640625" style="2" customWidth="1"/>
+    <col min="10261" max="10261" width="15.6640625" style="2" customWidth="1"/>
+    <col min="10262" max="10495" width="8.88671875" style="2"/>
+    <col min="10496" max="10496" width="14.6640625" style="2" customWidth="1"/>
+    <col min="10497" max="10497" width="5.109375" style="2" customWidth="1"/>
+    <col min="10498" max="10504" width="4.109375" style="2" customWidth="1"/>
+    <col min="10505" max="10507" width="3.6640625" style="2" customWidth="1"/>
+    <col min="10508" max="10510" width="4.109375" style="2" customWidth="1"/>
+    <col min="10511" max="10512" width="4.6640625" style="2" customWidth="1"/>
+    <col min="10513" max="10515" width="5.109375" style="2" customWidth="1"/>
+    <col min="10516" max="10516" width="2.6640625" style="2" customWidth="1"/>
+    <col min="10517" max="10517" width="15.6640625" style="2" customWidth="1"/>
+    <col min="10518" max="10751" width="8.88671875" style="2"/>
+    <col min="10752" max="10752" width="14.6640625" style="2" customWidth="1"/>
+    <col min="10753" max="10753" width="5.109375" style="2" customWidth="1"/>
+    <col min="10754" max="10760" width="4.109375" style="2" customWidth="1"/>
+    <col min="10761" max="10763" width="3.6640625" style="2" customWidth="1"/>
+    <col min="10764" max="10766" width="4.109375" style="2" customWidth="1"/>
+    <col min="10767" max="10768" width="4.6640625" style="2" customWidth="1"/>
+    <col min="10769" max="10771" width="5.109375" style="2" customWidth="1"/>
+    <col min="10772" max="10772" width="2.6640625" style="2" customWidth="1"/>
+    <col min="10773" max="10773" width="15.6640625" style="2" customWidth="1"/>
+    <col min="10774" max="11007" width="8.88671875" style="2"/>
+    <col min="11008" max="11008" width="14.6640625" style="2" customWidth="1"/>
+    <col min="11009" max="11009" width="5.109375" style="2" customWidth="1"/>
+    <col min="11010" max="11016" width="4.109375" style="2" customWidth="1"/>
+    <col min="11017" max="11019" width="3.6640625" style="2" customWidth="1"/>
+    <col min="11020" max="11022" width="4.109375" style="2" customWidth="1"/>
+    <col min="11023" max="11024" width="4.6640625" style="2" customWidth="1"/>
+    <col min="11025" max="11027" width="5.109375" style="2" customWidth="1"/>
+    <col min="11028" max="11028" width="2.6640625" style="2" customWidth="1"/>
+    <col min="11029" max="11029" width="15.6640625" style="2" customWidth="1"/>
+    <col min="11030" max="11263" width="8.88671875" style="2"/>
+    <col min="11264" max="11264" width="14.6640625" style="2" customWidth="1"/>
+    <col min="11265" max="11265" width="5.109375" style="2" customWidth="1"/>
+    <col min="11266" max="11272" width="4.109375" style="2" customWidth="1"/>
+    <col min="11273" max="11275" width="3.6640625" style="2" customWidth="1"/>
+    <col min="11276" max="11278" width="4.109375" style="2" customWidth="1"/>
+    <col min="11279" max="11280" width="4.6640625" style="2" customWidth="1"/>
+    <col min="11281" max="11283" width="5.109375" style="2" customWidth="1"/>
+    <col min="11284" max="11284" width="2.6640625" style="2" customWidth="1"/>
+    <col min="11285" max="11285" width="15.6640625" style="2" customWidth="1"/>
+    <col min="11286" max="11519" width="8.88671875" style="2"/>
+    <col min="11520" max="11520" width="14.6640625" style="2" customWidth="1"/>
+    <col min="11521" max="11521" width="5.109375" style="2" customWidth="1"/>
+    <col min="11522" max="11528" width="4.109375" style="2" customWidth="1"/>
+    <col min="11529" max="11531" width="3.6640625" style="2" customWidth="1"/>
+    <col min="11532" max="11534" width="4.109375" style="2" customWidth="1"/>
+    <col min="11535" max="11536" width="4.6640625" style="2" customWidth="1"/>
+    <col min="11537" max="11539" width="5.109375" style="2" customWidth="1"/>
+    <col min="11540" max="11540" width="2.6640625" style="2" customWidth="1"/>
+    <col min="11541" max="11541" width="15.6640625" style="2" customWidth="1"/>
+    <col min="11542" max="11775" width="8.88671875" style="2"/>
+    <col min="11776" max="11776" width="14.6640625" style="2" customWidth="1"/>
+    <col min="11777" max="11777" width="5.109375" style="2" customWidth="1"/>
+    <col min="11778" max="11784" width="4.109375" style="2" customWidth="1"/>
+    <col min="11785" max="11787" width="3.6640625" style="2" customWidth="1"/>
+    <col min="11788" max="11790" width="4.109375" style="2" customWidth="1"/>
+    <col min="11791" max="11792" width="4.6640625" style="2" customWidth="1"/>
+    <col min="11793" max="11795" width="5.109375" style="2" customWidth="1"/>
+    <col min="11796" max="11796" width="2.6640625" style="2" customWidth="1"/>
+    <col min="11797" max="11797" width="15.6640625" style="2" customWidth="1"/>
+    <col min="11798" max="12031" width="8.88671875" style="2"/>
+    <col min="12032" max="12032" width="14.6640625" style="2" customWidth="1"/>
+    <col min="12033" max="12033" width="5.109375" style="2" customWidth="1"/>
+    <col min="12034" max="12040" width="4.109375" style="2" customWidth="1"/>
+    <col min="12041" max="12043" width="3.6640625" style="2" customWidth="1"/>
+    <col min="12044" max="12046" width="4.109375" style="2" customWidth="1"/>
+    <col min="12047" max="12048" width="4.6640625" style="2" customWidth="1"/>
+    <col min="12049" max="12051" width="5.109375" style="2" customWidth="1"/>
+    <col min="12052" max="12052" width="2.6640625" style="2" customWidth="1"/>
+    <col min="12053" max="12053" width="15.6640625" style="2" customWidth="1"/>
+    <col min="12054" max="12287" width="8.88671875" style="2"/>
+    <col min="12288" max="12288" width="14.6640625" style="2" customWidth="1"/>
+    <col min="12289" max="12289" width="5.109375" style="2" customWidth="1"/>
+    <col min="12290" max="12296" width="4.109375" style="2" customWidth="1"/>
+    <col min="12297" max="12299" width="3.6640625" style="2" customWidth="1"/>
+    <col min="12300" max="12302" width="4.109375" style="2" customWidth="1"/>
+    <col min="12303" max="12304" width="4.6640625" style="2" customWidth="1"/>
+    <col min="12305" max="12307" width="5.109375" style="2" customWidth="1"/>
+    <col min="12308" max="12308" width="2.6640625" style="2" customWidth="1"/>
+    <col min="12309" max="12309" width="15.6640625" style="2" customWidth="1"/>
+    <col min="12310" max="12543" width="8.88671875" style="2"/>
+    <col min="12544" max="12544" width="14.6640625" style="2" customWidth="1"/>
+    <col min="12545" max="12545" width="5.109375" style="2" customWidth="1"/>
+    <col min="12546" max="12552" width="4.109375" style="2" customWidth="1"/>
+    <col min="12553" max="12555" width="3.6640625" style="2" customWidth="1"/>
+    <col min="12556" max="12558" width="4.109375" style="2" customWidth="1"/>
+    <col min="12559" max="12560" width="4.6640625" style="2" customWidth="1"/>
+    <col min="12561" max="12563" width="5.109375" style="2" customWidth="1"/>
+    <col min="12564" max="12564" width="2.6640625" style="2" customWidth="1"/>
+    <col min="12565" max="12565" width="15.6640625" style="2" customWidth="1"/>
+    <col min="12566" max="12799" width="8.88671875" style="2"/>
+    <col min="12800" max="12800" width="14.6640625" style="2" customWidth="1"/>
+    <col min="12801" max="12801" width="5.109375" style="2" customWidth="1"/>
+    <col min="12802" max="12808" width="4.109375" style="2" customWidth="1"/>
+    <col min="12809" max="12811" width="3.6640625" style="2" customWidth="1"/>
+    <col min="12812" max="12814" width="4.109375" style="2" customWidth="1"/>
+    <col min="12815" max="12816" width="4.6640625" style="2" customWidth="1"/>
+    <col min="12817" max="12819" width="5.109375" style="2" customWidth="1"/>
+    <col min="12820" max="12820" width="2.6640625" style="2" customWidth="1"/>
+    <col min="12821" max="12821" width="15.6640625" style="2" customWidth="1"/>
+    <col min="12822" max="13055" width="8.88671875" style="2"/>
+    <col min="13056" max="13056" width="14.6640625" style="2" customWidth="1"/>
+    <col min="13057" max="13057" width="5.109375" style="2" customWidth="1"/>
+    <col min="13058" max="13064" width="4.109375" style="2" customWidth="1"/>
+    <col min="13065" max="13067" width="3.6640625" style="2" customWidth="1"/>
+    <col min="13068" max="13070" width="4.109375" style="2" customWidth="1"/>
+    <col min="13071" max="13072" width="4.6640625" style="2" customWidth="1"/>
+    <col min="13073" max="13075" width="5.109375" style="2" customWidth="1"/>
+    <col min="13076" max="13076" width="2.6640625" style="2" customWidth="1"/>
+    <col min="13077" max="13077" width="15.6640625" style="2" customWidth="1"/>
+    <col min="13078" max="13311" width="8.88671875" style="2"/>
+    <col min="13312" max="13312" width="14.6640625" style="2" customWidth="1"/>
+    <col min="13313" max="13313" width="5.109375" style="2" customWidth="1"/>
+    <col min="13314" max="13320" width="4.109375" style="2" customWidth="1"/>
+    <col min="13321" max="13323" width="3.6640625" style="2" customWidth="1"/>
+    <col min="13324" max="13326" width="4.109375" style="2" customWidth="1"/>
+    <col min="13327" max="13328" width="4.6640625" style="2" customWidth="1"/>
+    <col min="13329" max="13331" width="5.109375" style="2" customWidth="1"/>
+    <col min="13332" max="13332" width="2.6640625" style="2" customWidth="1"/>
+    <col min="13333" max="13333" width="15.6640625" style="2" customWidth="1"/>
+    <col min="13334" max="13567" width="8.88671875" style="2"/>
+    <col min="13568" max="13568" width="14.6640625" style="2" customWidth="1"/>
+    <col min="13569" max="13569" width="5.109375" style="2" customWidth="1"/>
+    <col min="13570" max="13576" width="4.109375" style="2" customWidth="1"/>
+    <col min="13577" max="13579" width="3.6640625" style="2" customWidth="1"/>
+    <col min="13580" max="13582" width="4.109375" style="2" customWidth="1"/>
+    <col min="13583" max="13584" width="4.6640625" style="2" customWidth="1"/>
+    <col min="13585" max="13587" width="5.109375" style="2" customWidth="1"/>
+    <col min="13588" max="13588" width="2.6640625" style="2" customWidth="1"/>
+    <col min="13589" max="13589" width="15.6640625" style="2" customWidth="1"/>
+    <col min="13590" max="13823" width="8.88671875" style="2"/>
+    <col min="13824" max="13824" width="14.6640625" style="2" customWidth="1"/>
+    <col min="13825" max="13825" width="5.109375" style="2" customWidth="1"/>
+    <col min="13826" max="13832" width="4.109375" style="2" customWidth="1"/>
+    <col min="13833" max="13835" width="3.6640625" style="2" customWidth="1"/>
+    <col min="13836" max="13838" width="4.109375" style="2" customWidth="1"/>
+    <col min="13839" max="13840" width="4.6640625" style="2" customWidth="1"/>
+    <col min="13841" max="13843" width="5.109375" style="2" customWidth="1"/>
+    <col min="13844" max="13844" width="2.6640625" style="2" customWidth="1"/>
+    <col min="13845" max="13845" width="15.6640625" style="2" customWidth="1"/>
+    <col min="13846" max="14079" width="8.88671875" style="2"/>
+    <col min="14080" max="14080" width="14.6640625" style="2" customWidth="1"/>
+    <col min="14081" max="14081" width="5.109375" style="2" customWidth="1"/>
+    <col min="14082" max="14088" width="4.109375" style="2" customWidth="1"/>
+    <col min="14089" max="14091" width="3.6640625" style="2" customWidth="1"/>
+    <col min="14092" max="14094" width="4.109375" style="2" customWidth="1"/>
+    <col min="14095" max="14096" width="4.6640625" style="2" customWidth="1"/>
+    <col min="14097" max="14099" width="5.109375" style="2" customWidth="1"/>
+    <col min="14100" max="14100" width="2.6640625" style="2" customWidth="1"/>
+    <col min="14101" max="14101" width="15.6640625" style="2" customWidth="1"/>
+    <col min="14102" max="14335" width="8.88671875" style="2"/>
+    <col min="14336" max="14336" width="14.6640625" style="2" customWidth="1"/>
+    <col min="14337" max="14337" width="5.109375" style="2" customWidth="1"/>
+    <col min="14338" max="14344" width="4.109375" style="2" customWidth="1"/>
+    <col min="14345" max="14347" width="3.6640625" style="2" customWidth="1"/>
+    <col min="14348" max="14350" width="4.109375" style="2" customWidth="1"/>
+    <col min="14351" max="14352" width="4.6640625" style="2" customWidth="1"/>
+    <col min="14353" max="14355" width="5.109375" style="2" customWidth="1"/>
+    <col min="14356" max="14356" width="2.6640625" style="2" customWidth="1"/>
+    <col min="14357" max="14357" width="15.6640625" style="2" customWidth="1"/>
+    <col min="14358" max="14591" width="8.88671875" style="2"/>
+    <col min="14592" max="14592" width="14.6640625" style="2" customWidth="1"/>
+    <col min="14593" max="14593" width="5.109375" style="2" customWidth="1"/>
+    <col min="14594" max="14600" width="4.109375" style="2" customWidth="1"/>
+    <col min="14601" max="14603" width="3.6640625" style="2" customWidth="1"/>
+    <col min="14604" max="14606" width="4.109375" style="2" customWidth="1"/>
+    <col min="14607" max="14608" width="4.6640625" style="2" customWidth="1"/>
+    <col min="14609" max="14611" width="5.109375" style="2" customWidth="1"/>
+    <col min="14612" max="14612" width="2.6640625" style="2" customWidth="1"/>
+    <col min="14613" max="14613" width="15.6640625" style="2" customWidth="1"/>
+    <col min="14614" max="14847" width="8.88671875" style="2"/>
+    <col min="14848" max="14848" width="14.6640625" style="2" customWidth="1"/>
+    <col min="14849" max="14849" width="5.109375" style="2" customWidth="1"/>
+    <col min="14850" max="14856" width="4.109375" style="2" customWidth="1"/>
+    <col min="14857" max="14859" width="3.6640625" style="2" customWidth="1"/>
+    <col min="14860" max="14862" width="4.109375" style="2" customWidth="1"/>
+    <col min="14863" max="14864" width="4.6640625" style="2" customWidth="1"/>
+    <col min="14865" max="14867" width="5.109375" style="2" customWidth="1"/>
+    <col min="14868" max="14868" width="2.6640625" style="2" customWidth="1"/>
+    <col min="14869" max="14869" width="15.6640625" style="2" customWidth="1"/>
+    <col min="14870" max="15103" width="8.88671875" style="2"/>
+    <col min="15104" max="15104" width="14.6640625" style="2" customWidth="1"/>
+    <col min="15105" max="15105" width="5.109375" style="2" customWidth="1"/>
+    <col min="15106" max="15112" width="4.109375" style="2" customWidth="1"/>
+    <col min="15113" max="15115" width="3.6640625" style="2" customWidth="1"/>
+    <col min="15116" max="15118" width="4.109375" style="2" customWidth="1"/>
+    <col min="15119" max="15120" width="4.6640625" style="2" customWidth="1"/>
+    <col min="15121" max="15123" width="5.109375" style="2" customWidth="1"/>
+    <col min="15124" max="15124" width="2.6640625" style="2" customWidth="1"/>
+    <col min="15125" max="15125" width="15.6640625" style="2" customWidth="1"/>
+    <col min="15126" max="15359" width="8.88671875" style="2"/>
+    <col min="15360" max="15360" width="14.6640625" style="2" customWidth="1"/>
+    <col min="15361" max="15361" width="5.109375" style="2" customWidth="1"/>
+    <col min="15362" max="15368" width="4.109375" style="2" customWidth="1"/>
+    <col min="15369" max="15371" width="3.6640625" style="2" customWidth="1"/>
+    <col min="15372" max="15374" width="4.109375" style="2" customWidth="1"/>
+    <col min="15375" max="15376" width="4.6640625" style="2" customWidth="1"/>
+    <col min="15377" max="15379" width="5.109375" style="2" customWidth="1"/>
+    <col min="15380" max="15380" width="2.6640625" style="2" customWidth="1"/>
+    <col min="15381" max="15381" width="15.6640625" style="2" customWidth="1"/>
+    <col min="15382" max="15615" width="8.88671875" style="2"/>
+    <col min="15616" max="15616" width="14.6640625" style="2" customWidth="1"/>
+    <col min="15617" max="15617" width="5.109375" style="2" customWidth="1"/>
+    <col min="15618" max="15624" width="4.109375" style="2" customWidth="1"/>
+    <col min="15625" max="15627" width="3.6640625" style="2" customWidth="1"/>
+    <col min="15628" max="15630" width="4.109375" style="2" customWidth="1"/>
+    <col min="15631" max="15632" width="4.6640625" style="2" customWidth="1"/>
+    <col min="15633" max="15635" width="5.109375" style="2" customWidth="1"/>
+    <col min="15636" max="15636" width="2.6640625" style="2" customWidth="1"/>
+    <col min="15637" max="15637" width="15.6640625" style="2" customWidth="1"/>
+    <col min="15638" max="15871" width="8.88671875" style="2"/>
+    <col min="15872" max="15872" width="14.6640625" style="2" customWidth="1"/>
+    <col min="15873" max="15873" width="5.109375" style="2" customWidth="1"/>
+    <col min="15874" max="15880" width="4.109375" style="2" customWidth="1"/>
+    <col min="15881" max="15883" width="3.6640625" style="2" customWidth="1"/>
+    <col min="15884" max="15886" width="4.109375" style="2" customWidth="1"/>
+    <col min="15887" max="15888" width="4.6640625" style="2" customWidth="1"/>
+    <col min="15889" max="15891" width="5.109375" style="2" customWidth="1"/>
+    <col min="15892" max="15892" width="2.6640625" style="2" customWidth="1"/>
+    <col min="15893" max="15893" width="15.6640625" style="2" customWidth="1"/>
+    <col min="15894" max="16127" width="8.88671875" style="2"/>
+    <col min="16128" max="16128" width="14.6640625" style="2" customWidth="1"/>
+    <col min="16129" max="16129" width="5.109375" style="2" customWidth="1"/>
+    <col min="16130" max="16136" width="4.109375" style="2" customWidth="1"/>
+    <col min="16137" max="16139" width="3.6640625" style="2" customWidth="1"/>
+    <col min="16140" max="16142" width="4.109375" style="2" customWidth="1"/>
+    <col min="16143" max="16144" width="4.6640625" style="2" customWidth="1"/>
+    <col min="16145" max="16147" width="5.109375" style="2" customWidth="1"/>
+    <col min="16148" max="16148" width="2.6640625" style="2" customWidth="1"/>
+    <col min="16149" max="16149" width="15.6640625" style="2" customWidth="1"/>
+    <col min="16150" max="16384" width="8.88671875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="24.75" customHeight="1" thickBot="1">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="192" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="108"/>
-      <c r="J1" s="108"/>
-      <c r="K1" s="108"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="107"/>
-      <c r="Q1" s="107"/>
-      <c r="R1" s="107"/>
-      <c r="S1" s="107"/>
-      <c r="T1" s="109"/>
+      <c r="B1" s="193"/>
+      <c r="C1" s="193"/>
+      <c r="D1" s="193"/>
+      <c r="E1" s="193"/>
+      <c r="F1" s="193"/>
+      <c r="G1" s="193"/>
+      <c r="H1" s="193"/>
+      <c r="I1" s="194"/>
+      <c r="J1" s="194"/>
+      <c r="K1" s="194"/>
+      <c r="L1" s="193"/>
+      <c r="M1" s="193"/>
+      <c r="N1" s="193"/>
+      <c r="O1" s="193"/>
+      <c r="P1" s="193"/>
+      <c r="Q1" s="193"/>
+      <c r="R1" s="193"/>
+      <c r="S1" s="193"/>
+      <c r="T1" s="195"/>
       <c r="V1" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="X1" s="110" t="s">
+      <c r="X1" s="196" t="s">
         <v>6</v>
       </c>
-      <c r="Y1" s="111"/>
-      <c r="Z1" s="111"/>
-      <c r="AA1" s="111"/>
-      <c r="AB1" s="111"/>
-      <c r="AC1" s="111"/>
-      <c r="AD1" s="112"/>
+      <c r="Y1" s="197"/>
+      <c r="Z1" s="197"/>
+      <c r="AA1" s="197"/>
+      <c r="AB1" s="197"/>
+      <c r="AC1" s="197"/>
+      <c r="AD1" s="198"/>
     </row>
     <row r="2" spans="1:34" ht="20.100000000000001" customHeight="1" thickBot="1">
       <c r="A2" s="76" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="113" t="str">
+      <c r="B2" s="199" t="str">
         <f>CONCATENATE(Pomocný!B22," ")</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C2" s="114"/>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="115" t="s">
-        <v>0</v>
-      </c>
-      <c r="J2" s="116"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="118">
+      <c r="C2" s="200"/>
+      <c r="D2" s="200"/>
+      <c r="E2" s="200"/>
+      <c r="F2" s="200"/>
+      <c r="G2" s="200"/>
+      <c r="H2" s="200"/>
+      <c r="I2" s="201" t="s">
+        <v>0</v>
+      </c>
+      <c r="J2" s="202"/>
+      <c r="K2" s="203"/>
+      <c r="L2" s="204">
         <f>Pomocný!B21</f>
         <v>0</v>
       </c>
-      <c r="M2" s="119"/>
-      <c r="N2" s="119"/>
-      <c r="O2" s="119"/>
-      <c r="P2" s="119"/>
-      <c r="Q2" s="119"/>
-      <c r="R2" s="119"/>
-      <c r="S2" s="119"/>
-      <c r="T2" s="120"/>
+      <c r="M2" s="205"/>
+      <c r="N2" s="205"/>
+      <c r="O2" s="205"/>
+      <c r="P2" s="205"/>
+      <c r="Q2" s="205"/>
+      <c r="R2" s="205"/>
+      <c r="S2" s="205"/>
+      <c r="T2" s="206"/>
       <c r="V2" s="84"/>
       <c r="AE2" s="2"/>
       <c r="AF2" s="2"/>
@@ -3579,33 +3554,33 @@
       <c r="A3" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="121" t="str">
+      <c r="B3" s="207" t="str">
         <f>CONCATENATE(Pomocný!B19," ",Pomocný!B20)</f>
         <v xml:space="preserve"> </v>
       </c>
-      <c r="C3" s="121"/>
-      <c r="D3" s="121"/>
-      <c r="E3" s="121"/>
-      <c r="F3" s="121"/>
-      <c r="G3" s="121"/>
-      <c r="H3" s="121"/>
-      <c r="I3" s="122"/>
-      <c r="J3" s="122"/>
-      <c r="K3" s="122"/>
-      <c r="L3" s="122"/>
-      <c r="M3" s="122"/>
-      <c r="N3" s="123" t="s">
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="207"/>
+      <c r="H3" s="207"/>
+      <c r="I3" s="208"/>
+      <c r="J3" s="208"/>
+      <c r="K3" s="208"/>
+      <c r="L3" s="208"/>
+      <c r="M3" s="208"/>
+      <c r="N3" s="209" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="123"/>
-      <c r="P3" s="123"/>
-      <c r="Q3" s="123"/>
-      <c r="R3" s="124"/>
-      <c r="S3" s="125">
+      <c r="O3" s="209"/>
+      <c r="P3" s="209"/>
+      <c r="Q3" s="209"/>
+      <c r="R3" s="210"/>
+      <c r="S3" s="211">
         <f>Pomocný!B23</f>
         <v>0</v>
       </c>
-      <c r="T3" s="126"/>
+      <c r="T3" s="212"/>
       <c r="U3" s="69"/>
       <c r="V3" s="84"/>
       <c r="W3" s="69"/>
@@ -3623,32 +3598,32 @@
       <c r="A4" s="78" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="127"/>
-      <c r="C4" s="127"/>
-      <c r="D4" s="127"/>
-      <c r="E4" s="127"/>
-      <c r="F4" s="127"/>
-      <c r="G4" s="127"/>
-      <c r="H4" s="127"/>
-      <c r="I4" s="127"/>
-      <c r="J4" s="128" t="s">
+      <c r="B4" s="213"/>
+      <c r="C4" s="213"/>
+      <c r="D4" s="213"/>
+      <c r="E4" s="213"/>
+      <c r="F4" s="213"/>
+      <c r="G4" s="213"/>
+      <c r="H4" s="213"/>
+      <c r="I4" s="213"/>
+      <c r="J4" s="214" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="128"/>
-      <c r="L4" s="129"/>
-      <c r="M4" s="129"/>
-      <c r="N4" s="128" t="s">
+      <c r="K4" s="214"/>
+      <c r="L4" s="215"/>
+      <c r="M4" s="215"/>
+      <c r="N4" s="214" t="s">
         <v>18</v>
       </c>
-      <c r="O4" s="128"/>
-      <c r="P4" s="128"/>
-      <c r="Q4" s="128"/>
-      <c r="R4" s="128"/>
-      <c r="S4" s="130">
+      <c r="O4" s="214"/>
+      <c r="P4" s="214"/>
+      <c r="Q4" s="214"/>
+      <c r="R4" s="214"/>
+      <c r="S4" s="216">
         <f>S5/B5</f>
-        <v>0.15309999999999999</v>
-      </c>
-      <c r="T4" s="131"/>
+        <v>0</v>
+      </c>
+      <c r="T4" s="217"/>
       <c r="U4" s="70"/>
       <c r="V4" s="84"/>
       <c r="W4" s="69"/>
@@ -3678,41 +3653,41 @@
       <c r="A5" s="79" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="132">
+      <c r="B5" s="182">
         <f>$F$5*1000</f>
         <v>1000</v>
       </c>
-      <c r="C5" s="132"/>
-      <c r="D5" s="133" t="s">
+      <c r="C5" s="182"/>
+      <c r="D5" s="183" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="133"/>
+      <c r="E5" s="183"/>
       <c r="F5" s="42">
         <v>1</v>
       </c>
-      <c r="G5" s="134" t="s">
+      <c r="G5" s="184" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="135"/>
-      <c r="I5" s="135"/>
-      <c r="J5" s="135"/>
-      <c r="K5" s="135"/>
-      <c r="L5" s="136"/>
+      <c r="H5" s="185"/>
+      <c r="I5" s="185"/>
+      <c r="J5" s="185"/>
+      <c r="K5" s="185"/>
+      <c r="L5" s="186"/>
       <c r="M5" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="N5" s="133" t="s">
+      <c r="N5" s="183" t="s">
         <v>29</v>
       </c>
-      <c r="O5" s="133"/>
-      <c r="P5" s="133"/>
-      <c r="Q5" s="133"/>
-      <c r="R5" s="133"/>
-      <c r="S5" s="137">
+      <c r="O5" s="183"/>
+      <c r="P5" s="183"/>
+      <c r="Q5" s="183"/>
+      <c r="R5" s="183"/>
+      <c r="S5" s="187">
         <f>SUM(S6,S53,S93,S114)</f>
-        <v>153.1</v>
-      </c>
-      <c r="T5" s="138"/>
+        <v>0</v>
+      </c>
+      <c r="T5" s="188"/>
       <c r="U5" s="70"/>
       <c r="V5" s="84"/>
       <c r="W5" s="69"/>
@@ -3739,35 +3714,35 @@
       </c>
     </row>
     <row r="6" spans="1:34" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A6" s="147" t="s">
+      <c r="A6" s="145" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="148"/>
-      <c r="C6" s="148"/>
-      <c r="D6" s="148"/>
-      <c r="E6" s="148"/>
-      <c r="F6" s="148"/>
-      <c r="G6" s="148"/>
-      <c r="H6" s="148"/>
-      <c r="I6" s="148"/>
-      <c r="J6" s="148"/>
-      <c r="K6" s="148"/>
-      <c r="L6" s="148"/>
-      <c r="M6" s="148"/>
-      <c r="N6" s="148"/>
-      <c r="O6" s="148"/>
-      <c r="P6" s="148"/>
-      <c r="Q6" s="148"/>
+      <c r="B6" s="146"/>
+      <c r="C6" s="146"/>
+      <c r="D6" s="146"/>
+      <c r="E6" s="146"/>
+      <c r="F6" s="146"/>
+      <c r="G6" s="146"/>
+      <c r="H6" s="146"/>
+      <c r="I6" s="146"/>
+      <c r="J6" s="146"/>
+      <c r="K6" s="146"/>
+      <c r="L6" s="146"/>
+      <c r="M6" s="146"/>
+      <c r="N6" s="146"/>
+      <c r="O6" s="146"/>
+      <c r="P6" s="146"/>
+      <c r="Q6" s="146"/>
       <c r="R6" s="44" t="s">
         <v>37</v>
       </c>
       <c r="S6" s="26">
         <f>S39+S23+S7+S50</f>
-        <v>74.099999999999994</v>
+        <v>0</v>
       </c>
       <c r="T6" s="64">
         <f>S6/$B$5</f>
-        <v>7.4099999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="U6" s="70"/>
       <c r="V6" s="85"/>
@@ -3795,25 +3770,25 @@
       </c>
     </row>
     <row r="7" spans="1:34" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A7" s="139" t="s">
+      <c r="A7" s="137" t="s">
         <v>44</v>
       </c>
-      <c r="B7" s="140"/>
-      <c r="C7" s="140"/>
-      <c r="D7" s="140"/>
-      <c r="E7" s="140"/>
-      <c r="F7" s="140"/>
-      <c r="G7" s="140"/>
-      <c r="H7" s="140"/>
-      <c r="I7" s="140"/>
-      <c r="J7" s="140"/>
-      <c r="K7" s="140"/>
-      <c r="L7" s="140"/>
-      <c r="M7" s="140"/>
-      <c r="N7" s="140"/>
-      <c r="O7" s="140"/>
-      <c r="P7" s="140"/>
-      <c r="Q7" s="140"/>
+      <c r="B7" s="138"/>
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="138"/>
+      <c r="F7" s="138"/>
+      <c r="G7" s="138"/>
+      <c r="H7" s="138"/>
+      <c r="I7" s="138"/>
+      <c r="J7" s="138"/>
+      <c r="K7" s="138"/>
+      <c r="L7" s="138"/>
+      <c r="M7" s="138"/>
+      <c r="N7" s="138"/>
+      <c r="O7" s="138"/>
+      <c r="P7" s="138"/>
+      <c r="Q7" s="138"/>
       <c r="R7" s="43" t="s">
         <v>45</v>
       </c>
@@ -3855,28 +3830,28 @@
       <c r="AH7" s="97"/>
     </row>
     <row r="8" spans="1:34" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A8" s="141" t="s">
+      <c r="A8" s="139" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="142"/>
-      <c r="C8" s="142"/>
-      <c r="D8" s="142"/>
-      <c r="E8" s="142"/>
-      <c r="F8" s="142"/>
-      <c r="G8" s="142"/>
-      <c r="H8" s="142"/>
-      <c r="I8" s="142"/>
-      <c r="J8" s="142"/>
-      <c r="K8" s="142"/>
-      <c r="L8" s="142"/>
-      <c r="M8" s="142"/>
-      <c r="N8" s="142"/>
-      <c r="O8" s="142"/>
-      <c r="P8" s="142"/>
-      <c r="Q8" s="142"/>
-      <c r="R8" s="142"/>
-      <c r="S8" s="142"/>
-      <c r="T8" s="143"/>
+      <c r="B8" s="140"/>
+      <c r="C8" s="140"/>
+      <c r="D8" s="140"/>
+      <c r="E8" s="140"/>
+      <c r="F8" s="140"/>
+      <c r="G8" s="140"/>
+      <c r="H8" s="140"/>
+      <c r="I8" s="140"/>
+      <c r="J8" s="140"/>
+      <c r="K8" s="140"/>
+      <c r="L8" s="140"/>
+      <c r="M8" s="140"/>
+      <c r="N8" s="140"/>
+      <c r="O8" s="140"/>
+      <c r="P8" s="140"/>
+      <c r="Q8" s="140"/>
+      <c r="R8" s="140"/>
+      <c r="S8" s="140"/>
+      <c r="T8" s="159"/>
       <c r="U8" s="70"/>
       <c r="V8" s="85"/>
       <c r="W8" s="69"/>
@@ -3905,32 +3880,32 @@
       <c r="AH8" s="2"/>
     </row>
     <row r="9" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A9" s="149" t="s">
+      <c r="A9" s="174" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="150"/>
-      <c r="C9" s="149" t="s">
+      <c r="B9" s="175"/>
+      <c r="C9" s="174" t="s">
         <v>59</v>
       </c>
-      <c r="D9" s="150"/>
-      <c r="E9" s="151" t="s">
+      <c r="D9" s="175"/>
+      <c r="E9" s="176" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="152"/>
-      <c r="G9" s="152"/>
-      <c r="H9" s="153"/>
-      <c r="I9" s="151" t="s">
+      <c r="F9" s="177"/>
+      <c r="G9" s="177"/>
+      <c r="H9" s="178"/>
+      <c r="I9" s="176" t="s">
         <v>61</v>
       </c>
-      <c r="J9" s="152"/>
-      <c r="K9" s="152"/>
-      <c r="L9" s="154"/>
-      <c r="M9" s="155" t="s">
+      <c r="J9" s="177"/>
+      <c r="K9" s="177"/>
+      <c r="L9" s="179"/>
+      <c r="M9" s="180" t="s">
         <v>62</v>
       </c>
-      <c r="N9" s="156"/>
-      <c r="O9" s="156"/>
-      <c r="P9" s="150"/>
+      <c r="N9" s="181"/>
+      <c r="O9" s="181"/>
+      <c r="P9" s="175"/>
       <c r="Q9" s="14"/>
       <c r="R9" s="14"/>
       <c r="S9" s="14"/>
@@ -4041,7 +4016,7 @@
       <c r="AH10" s="1"/>
     </row>
     <row r="11" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A11" s="105"/>
+      <c r="A11" s="104"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
       <c r="D11" s="7"/>
@@ -4097,7 +4072,7 @@
       <c r="AH11" s="2"/>
     </row>
     <row r="12" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A12" s="105"/>
+      <c r="A12" s="104"/>
       <c r="B12" s="5"/>
       <c r="C12" s="6"/>
       <c r="D12" s="7"/>
@@ -4151,7 +4126,7 @@
       <c r="AH12" s="2"/>
     </row>
     <row r="13" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A13" s="105"/>
+      <c r="A13" s="104"/>
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
       <c r="D13" s="7"/>
@@ -4201,7 +4176,7 @@
       <c r="AH13" s="2"/>
     </row>
     <row r="14" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A14" s="105"/>
+      <c r="A14" s="104"/>
       <c r="B14" s="59"/>
       <c r="C14" s="11"/>
       <c r="D14" s="12"/>
@@ -4251,7 +4226,7 @@
       <c r="AH14" s="2"/>
     </row>
     <row r="15" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A15" s="105"/>
+      <c r="A15" s="104"/>
       <c r="B15" s="5"/>
       <c r="C15" s="6"/>
       <c r="D15" s="7"/>
@@ -4301,7 +4276,7 @@
       <c r="AH15" s="2"/>
     </row>
     <row r="16" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A16" s="105"/>
+      <c r="A16" s="104"/>
       <c r="B16" s="5"/>
       <c r="C16" s="6"/>
       <c r="D16" s="7"/>
@@ -4351,7 +4326,7 @@
       <c r="AH16" s="2"/>
     </row>
     <row r="17" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A17" s="105"/>
+      <c r="A17" s="104"/>
       <c r="B17" s="5"/>
       <c r="C17" s="6"/>
       <c r="D17" s="7"/>
@@ -4399,7 +4374,7 @@
       <c r="AH17" s="2"/>
     </row>
     <row r="18" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A18" s="218"/>
+      <c r="A18" s="109"/>
       <c r="B18" s="5"/>
       <c r="C18" s="11"/>
       <c r="D18" s="12"/>
@@ -4449,7 +4424,7 @@
       <c r="AH18" s="2"/>
     </row>
     <row r="19" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A19" s="104"/>
+      <c r="A19" s="103"/>
       <c r="B19" s="59"/>
       <c r="C19" s="11"/>
       <c r="D19" s="12"/>
@@ -4497,7 +4472,7 @@
       <c r="AH19" s="2"/>
     </row>
     <row r="20" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A20" s="214"/>
+      <c r="A20" s="105"/>
       <c r="B20" s="5"/>
       <c r="C20" s="6"/>
       <c r="D20" s="7"/>
@@ -4547,7 +4522,7 @@
       <c r="AH20" s="2"/>
     </row>
     <row r="21" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="215"/>
+      <c r="A21" s="106"/>
       <c r="B21" s="59"/>
       <c r="C21" s="11"/>
       <c r="D21" s="12"/>
@@ -4595,8 +4570,8 @@
       <c r="AH21" s="2"/>
     </row>
     <row r="22" spans="1:34" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A22" s="216"/>
-      <c r="B22" s="217"/>
+      <c r="A22" s="107"/>
+      <c r="B22" s="108"/>
       <c r="C22" s="11"/>
       <c r="D22" s="12"/>
       <c r="E22" s="11"/>
@@ -4643,35 +4618,35 @@
       <c r="AH22" s="2"/>
     </row>
     <row r="23" spans="1:34" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A23" s="139" t="s">
+      <c r="A23" s="137" t="s">
         <v>92</v>
       </c>
-      <c r="B23" s="140"/>
-      <c r="C23" s="140"/>
-      <c r="D23" s="140"/>
-      <c r="E23" s="140"/>
-      <c r="F23" s="140"/>
-      <c r="G23" s="140"/>
-      <c r="H23" s="140"/>
-      <c r="I23" s="140"/>
-      <c r="J23" s="140"/>
-      <c r="K23" s="140"/>
-      <c r="L23" s="140"/>
-      <c r="M23" s="140"/>
-      <c r="N23" s="140"/>
-      <c r="O23" s="140"/>
-      <c r="P23" s="140"/>
-      <c r="Q23" s="140"/>
+      <c r="B23" s="138"/>
+      <c r="C23" s="138"/>
+      <c r="D23" s="138"/>
+      <c r="E23" s="138"/>
+      <c r="F23" s="138"/>
+      <c r="G23" s="138"/>
+      <c r="H23" s="138"/>
+      <c r="I23" s="138"/>
+      <c r="J23" s="138"/>
+      <c r="K23" s="138"/>
+      <c r="L23" s="138"/>
+      <c r="M23" s="138"/>
+      <c r="N23" s="138"/>
+      <c r="O23" s="138"/>
+      <c r="P23" s="138"/>
+      <c r="Q23" s="138"/>
       <c r="R23" s="43" t="s">
         <v>93</v>
       </c>
       <c r="S23" s="30">
         <f>SUM(F27:I38)</f>
-        <v>46.599999999999994</v>
+        <v>0</v>
       </c>
       <c r="T23" s="57">
         <f>S23/$B$5</f>
-        <v>4.6599999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="U23" s="72"/>
       <c r="V23" s="84"/>
@@ -4689,28 +4664,28 @@
       <c r="AH23" s="2"/>
     </row>
     <row r="24" spans="1:34" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A24" s="141" t="s">
+      <c r="A24" s="139" t="s">
         <v>94</v>
       </c>
-      <c r="B24" s="142"/>
-      <c r="C24" s="142"/>
-      <c r="D24" s="142"/>
-      <c r="E24" s="142"/>
-      <c r="F24" s="142"/>
-      <c r="G24" s="142"/>
-      <c r="H24" s="142"/>
-      <c r="I24" s="142"/>
-      <c r="J24" s="142"/>
-      <c r="K24" s="142"/>
-      <c r="L24" s="142"/>
-      <c r="M24" s="142"/>
-      <c r="N24" s="142"/>
-      <c r="O24" s="142"/>
-      <c r="P24" s="142"/>
-      <c r="Q24" s="142"/>
-      <c r="R24" s="142"/>
-      <c r="S24" s="142"/>
-      <c r="T24" s="143"/>
+      <c r="B24" s="140"/>
+      <c r="C24" s="140"/>
+      <c r="D24" s="140"/>
+      <c r="E24" s="140"/>
+      <c r="F24" s="140"/>
+      <c r="G24" s="140"/>
+      <c r="H24" s="140"/>
+      <c r="I24" s="140"/>
+      <c r="J24" s="140"/>
+      <c r="K24" s="140"/>
+      <c r="L24" s="140"/>
+      <c r="M24" s="140"/>
+      <c r="N24" s="140"/>
+      <c r="O24" s="140"/>
+      <c r="P24" s="140"/>
+      <c r="Q24" s="140"/>
+      <c r="R24" s="140"/>
+      <c r="S24" s="140"/>
+      <c r="T24" s="159"/>
       <c r="U24" s="74"/>
       <c r="V24" s="84"/>
       <c r="W24" s="69"/>
@@ -4740,18 +4715,18 @@
       <c r="A25" s="53" t="s">
         <v>58</v>
       </c>
-      <c r="B25" s="144" t="s">
+      <c r="B25" s="189" t="s">
         <v>95</v>
       </c>
-      <c r="C25" s="145"/>
-      <c r="D25" s="145"/>
-      <c r="E25" s="146"/>
-      <c r="F25" s="144" t="s">
+      <c r="C25" s="190"/>
+      <c r="D25" s="190"/>
+      <c r="E25" s="191"/>
+      <c r="F25" s="189" t="s">
         <v>62</v>
       </c>
-      <c r="G25" s="145"/>
-      <c r="H25" s="145"/>
-      <c r="I25" s="146"/>
+      <c r="G25" s="190"/>
+      <c r="H25" s="190"/>
+      <c r="I25" s="191"/>
       <c r="J25" s="55"/>
       <c r="K25" s="55"/>
       <c r="L25" s="55"/>
@@ -4851,13 +4826,9 @@
       <c r="AH26" s="2"/>
     </row>
     <row r="27" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="103" t="s">
-        <v>290</v>
-      </c>
+      <c r="A27" s="102"/>
       <c r="B27" s="6"/>
-      <c r="C27" s="3">
-        <v>114</v>
-      </c>
+      <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="7"/>
       <c r="F27" s="8">
@@ -4866,7 +4837,7 @@
       </c>
       <c r="G27" s="9">
         <f>$C27*Pomocný!$D$12</f>
-        <v>22.8</v>
+        <v>0</v>
       </c>
       <c r="H27" s="9">
         <f>$D27*Pomocný!$E$12</f>
@@ -4903,13 +4874,9 @@
       <c r="AH27" s="2"/>
     </row>
     <row r="28" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="103" t="s">
-        <v>291</v>
-      </c>
+      <c r="A28" s="102"/>
       <c r="B28" s="6"/>
-      <c r="C28" s="3">
-        <v>30</v>
-      </c>
+      <c r="C28" s="3"/>
       <c r="D28" s="13"/>
       <c r="E28" s="12"/>
       <c r="F28" s="8">
@@ -4918,7 +4885,7 @@
       </c>
       <c r="G28" s="9">
         <f>$C28*Pomocný!$D$12</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H28" s="9">
         <f>$D28*Pomocný!$E$12</f>
@@ -4955,13 +4922,9 @@
       <c r="AH28" s="2"/>
     </row>
     <row r="29" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="103" t="s">
-        <v>289</v>
-      </c>
+      <c r="A29" s="102"/>
       <c r="B29" s="11"/>
-      <c r="C29" s="13">
-        <v>13</v>
-      </c>
+      <c r="C29" s="13"/>
       <c r="D29" s="13"/>
       <c r="E29" s="12"/>
       <c r="F29" s="8">
@@ -4970,7 +4933,7 @@
       </c>
       <c r="G29" s="9">
         <f>$C29*Pomocný!$D$12</f>
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="H29" s="9">
         <f>$D29*Pomocný!$E$12</f>
@@ -5007,13 +4970,9 @@
       <c r="AH29" s="2"/>
     </row>
     <row r="30" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="103" t="s">
-        <v>295</v>
-      </c>
+      <c r="A30" s="102"/>
       <c r="B30" s="6"/>
-      <c r="C30" s="3">
-        <v>31</v>
-      </c>
+      <c r="C30" s="3"/>
       <c r="D30" s="13"/>
       <c r="E30" s="7"/>
       <c r="F30" s="8">
@@ -5022,7 +4981,7 @@
       </c>
       <c r="G30" s="9">
         <f>$C30*Pomocný!$D$12</f>
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="H30" s="9">
         <f>$D30*Pomocný!$E$12</f>
@@ -5059,16 +5018,10 @@
       <c r="AH30" s="2"/>
     </row>
     <row r="31" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="105" t="s">
-        <v>293</v>
-      </c>
+      <c r="A31" s="104"/>
       <c r="B31" s="11"/>
-      <c r="C31" s="13">
-        <v>2</v>
-      </c>
-      <c r="D31" s="13">
-        <v>2</v>
-      </c>
+      <c r="C31" s="3"/>
+      <c r="D31" s="3"/>
       <c r="E31" s="7"/>
       <c r="F31" s="8">
         <f>$B31*Pomocný!$C$12</f>
@@ -5076,11 +5029,11 @@
       </c>
       <c r="G31" s="9">
         <f>$C31*Pomocný!$D$12</f>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="H31" s="9">
         <f>$D31*Pomocný!$E$12</f>
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="I31" s="10">
         <f>$E31*Pomocný!$F$12</f>
@@ -5117,16 +5070,10 @@
       <c r="AH31" s="2"/>
     </row>
     <row r="32" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A32" s="105" t="s">
-        <v>292</v>
-      </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="13">
-        <v>9</v>
-      </c>
-      <c r="D32" s="13">
-        <v>9</v>
-      </c>
+      <c r="A32" s="102"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="3"/>
+      <c r="D32" s="13"/>
       <c r="E32" s="7"/>
       <c r="F32" s="8">
         <f>$B32*Pomocný!$C$12</f>
@@ -5134,11 +5081,11 @@
       </c>
       <c r="G32" s="9">
         <f>$C32*Pomocný!$D$12</f>
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="H32" s="9">
         <f>$D32*Pomocný!$E$12</f>
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I32" s="10">
         <f>$E32*Pomocný!$F$12</f>
@@ -5175,12 +5122,10 @@
       <c r="AH32" s="2"/>
     </row>
     <row r="33" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A33" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="C33" s="1">
-        <v>12</v>
-      </c>
+      <c r="A33" s="102"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
       <c r="E33" s="7"/>
       <c r="F33" s="8">
         <f>$B33*Pomocný!$C$12</f>
@@ -5188,7 +5133,7 @@
       </c>
       <c r="G33" s="9">
         <f>$C33*Pomocný!$D$12</f>
-        <v>2.4000000000000004</v>
+        <v>0</v>
       </c>
       <c r="H33" s="9">
         <f>$D33*Pomocný!$E$12</f>
@@ -5225,6 +5170,10 @@
       <c r="AH33" s="2"/>
     </row>
     <row r="34" spans="1:34" ht="20.100000000000001" customHeight="1">
+      <c r="A34" s="102"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="3"/>
+      <c r="D34" s="13"/>
       <c r="E34" s="7"/>
       <c r="F34" s="8">
         <f>$B34*Pomocný!$C$12</f>
@@ -5269,10 +5218,10 @@
       <c r="AH34" s="2"/>
     </row>
     <row r="35" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A35" s="99"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
+      <c r="A35" s="104"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
       <c r="E35" s="7"/>
       <c r="F35" s="8">
         <f>$B35*Pomocný!$C$12</f>
@@ -5383,7 +5332,7 @@
       <c r="AH36" s="2"/>
     </row>
     <row r="37" spans="1:34" ht="20.100000000000001" customHeight="1">
-      <c r="A37" s="102"/>
+      <c r="A37" s="101"/>
       <c r="B37" s="11"/>
       <c r="C37" s="13"/>
       <c r="D37" s="3"/>
@@ -5431,7 +5380,7 @@
       <c r="AH37" s="2"/>
     </row>
     <row r="38" spans="1:34" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A38" s="101"/>
+      <c r="A38" s="100"/>
       <c r="B38" s="11"/>
       <c r="C38" s="13"/>
       <c r="D38" s="13"/>
@@ -5475,35 +5424,35 @@
       <c r="AD38" s="69"/>
     </row>
     <row r="39" spans="1:34" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A39" s="139" t="s">
+      <c r="A39" s="137" t="s">
         <v>107</v>
       </c>
-      <c r="B39" s="140"/>
-      <c r="C39" s="140"/>
-      <c r="D39" s="140"/>
-      <c r="E39" s="140"/>
-      <c r="F39" s="140"/>
-      <c r="G39" s="140"/>
-      <c r="H39" s="140"/>
-      <c r="I39" s="140"/>
-      <c r="J39" s="140"/>
-      <c r="K39" s="140"/>
-      <c r="L39" s="140"/>
-      <c r="M39" s="140"/>
-      <c r="N39" s="140"/>
-      <c r="O39" s="140"/>
-      <c r="P39" s="140"/>
-      <c r="Q39" s="140"/>
+      <c r="B39" s="138"/>
+      <c r="C39" s="138"/>
+      <c r="D39" s="138"/>
+      <c r="E39" s="138"/>
+      <c r="F39" s="138"/>
+      <c r="G39" s="138"/>
+      <c r="H39" s="138"/>
+      <c r="I39" s="138"/>
+      <c r="J39" s="138"/>
+      <c r="K39" s="138"/>
+      <c r="L39" s="138"/>
+      <c r="M39" s="138"/>
+      <c r="N39" s="138"/>
+      <c r="O39" s="138"/>
+      <c r="P39" s="138"/>
+      <c r="Q39" s="138"/>
       <c r="R39" s="43" t="s">
         <v>108</v>
       </c>
       <c r="S39" s="30">
         <f>SUM($I$42:$I$49,$T$42:$T$49)</f>
-        <v>27.5</v>
+        <v>0</v>
       </c>
       <c r="T39" s="57">
         <f>S39/$B$5</f>
-        <v>2.75E-2</v>
+        <v>0</v>
       </c>
       <c r="U39" s="70"/>
       <c r="V39" s="84"/>
@@ -5517,28 +5466,28 @@
       <c r="AD39" s="69"/>
     </row>
     <row r="40" spans="1:34" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A40" s="141" t="s">
+      <c r="A40" s="139" t="s">
         <v>109</v>
       </c>
-      <c r="B40" s="142"/>
-      <c r="C40" s="142"/>
-      <c r="D40" s="142"/>
-      <c r="E40" s="142"/>
-      <c r="F40" s="142"/>
-      <c r="G40" s="142"/>
-      <c r="H40" s="142"/>
-      <c r="I40" s="142"/>
-      <c r="J40" s="142"/>
-      <c r="K40" s="142"/>
-      <c r="L40" s="142"/>
-      <c r="M40" s="142"/>
-      <c r="N40" s="142"/>
-      <c r="O40" s="142"/>
-      <c r="P40" s="142"/>
-      <c r="Q40" s="142"/>
-      <c r="R40" s="142"/>
-      <c r="S40" s="142"/>
-      <c r="T40" s="143"/>
+      <c r="B40" s="140"/>
+      <c r="C40" s="140"/>
+      <c r="D40" s="140"/>
+      <c r="E40" s="140"/>
+      <c r="F40" s="140"/>
+      <c r="G40" s="140"/>
+      <c r="H40" s="140"/>
+      <c r="I40" s="140"/>
+      <c r="J40" s="140"/>
+      <c r="K40" s="140"/>
+      <c r="L40" s="140"/>
+      <c r="M40" s="140"/>
+      <c r="N40" s="140"/>
+      <c r="O40" s="140"/>
+      <c r="P40" s="140"/>
+      <c r="Q40" s="140"/>
+      <c r="R40" s="140"/>
+      <c r="S40" s="140"/>
+      <c r="T40" s="159"/>
       <c r="U40" s="70"/>
       <c r="V40" s="84"/>
       <c r="W40" s="69"/>
@@ -5602,11 +5551,11 @@
       <c r="A42" s="165" t="s">
         <v>114</v>
       </c>
-      <c r="B42" s="166"/>
-      <c r="C42" s="166"/>
-      <c r="D42" s="166"/>
-      <c r="E42" s="166"/>
-      <c r="F42" s="166"/>
+      <c r="B42" s="173"/>
+      <c r="C42" s="173"/>
+      <c r="D42" s="173"/>
+      <c r="E42" s="173"/>
+      <c r="F42" s="173"/>
       <c r="G42" s="18"/>
       <c r="H42" s="15">
         <v>30</v>
@@ -5615,19 +5564,17 @@
         <f t="shared" ref="I42:I49" si="0">G42*H42</f>
         <v>0</v>
       </c>
-      <c r="J42" s="167" t="s">
+      <c r="J42" s="148" t="s">
         <v>115</v>
       </c>
-      <c r="K42" s="168"/>
-      <c r="L42" s="168"/>
-      <c r="M42" s="168"/>
-      <c r="N42" s="168"/>
-      <c r="O42" s="168"/>
-      <c r="P42" s="168"/>
-      <c r="Q42" s="169"/>
-      <c r="R42" s="17">
-        <v>2</v>
-      </c>
+      <c r="K42" s="149"/>
+      <c r="L42" s="149"/>
+      <c r="M42" s="149"/>
+      <c r="N42" s="149"/>
+      <c r="O42" s="149"/>
+      <c r="P42" s="149"/>
+      <c r="Q42" s="150"/>
+      <c r="R42" s="17"/>
       <c r="S42" s="17"/>
       <c r="T42" s="20">
         <f t="shared" ref="T42:T47" si="1">R42*S42</f>
@@ -5645,37 +5592,33 @@
       <c r="AD42" s="2"/>
     </row>
     <row r="43" spans="1:34" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A43" s="157" t="s">
+      <c r="A43" s="160" t="s">
         <v>116</v>
       </c>
-      <c r="B43" s="158"/>
-      <c r="C43" s="158"/>
-      <c r="D43" s="158"/>
-      <c r="E43" s="158"/>
-      <c r="F43" s="158"/>
-      <c r="G43" s="17">
-        <v>0.5</v>
-      </c>
+      <c r="B43" s="168"/>
+      <c r="C43" s="168"/>
+      <c r="D43" s="168"/>
+      <c r="E43" s="168"/>
+      <c r="F43" s="168"/>
+      <c r="G43" s="17"/>
       <c r="H43" s="15">
         <v>55</v>
       </c>
       <c r="I43" s="20">
         <f t="shared" si="0"/>
-        <v>27.5</v>
-      </c>
-      <c r="J43" s="159" t="s">
+        <v>0</v>
+      </c>
+      <c r="J43" s="125" t="s">
         <v>117</v>
       </c>
-      <c r="K43" s="160"/>
-      <c r="L43" s="160"/>
-      <c r="M43" s="160"/>
-      <c r="N43" s="160"/>
-      <c r="O43" s="160"/>
-      <c r="P43" s="160"/>
-      <c r="Q43" s="161"/>
-      <c r="R43" s="17">
-        <v>2</v>
-      </c>
+      <c r="K43" s="126"/>
+      <c r="L43" s="126"/>
+      <c r="M43" s="126"/>
+      <c r="N43" s="126"/>
+      <c r="O43" s="126"/>
+      <c r="P43" s="126"/>
+      <c r="Q43" s="127"/>
+      <c r="R43" s="17"/>
       <c r="S43" s="17"/>
       <c r="T43" s="20">
         <f t="shared" si="1"/>
@@ -5693,14 +5636,14 @@
       <c r="AD43" s="2"/>
     </row>
     <row r="44" spans="1:34" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A44" s="157" t="s">
+      <c r="A44" s="160" t="s">
         <v>118</v>
       </c>
-      <c r="B44" s="158"/>
-      <c r="C44" s="158"/>
-      <c r="D44" s="158"/>
-      <c r="E44" s="158"/>
-      <c r="F44" s="158"/>
+      <c r="B44" s="168"/>
+      <c r="C44" s="168"/>
+      <c r="D44" s="168"/>
+      <c r="E44" s="168"/>
+      <c r="F44" s="168"/>
       <c r="G44" s="17"/>
       <c r="H44" s="15">
         <v>35</v>
@@ -5709,16 +5652,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J44" s="159" t="s">
+      <c r="J44" s="125" t="s">
         <v>119</v>
       </c>
-      <c r="K44" s="160"/>
-      <c r="L44" s="160"/>
-      <c r="M44" s="160"/>
-      <c r="N44" s="160"/>
-      <c r="O44" s="160"/>
-      <c r="P44" s="160"/>
-      <c r="Q44" s="161"/>
+      <c r="K44" s="126"/>
+      <c r="L44" s="126"/>
+      <c r="M44" s="126"/>
+      <c r="N44" s="126"/>
+      <c r="O44" s="126"/>
+      <c r="P44" s="126"/>
+      <c r="Q44" s="127"/>
       <c r="R44" s="17"/>
       <c r="S44" s="15">
         <v>0.9</v>
@@ -5739,14 +5682,14 @@
       <c r="AD44" s="2"/>
     </row>
     <row r="45" spans="1:34" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A45" s="157" t="s">
+      <c r="A45" s="160" t="s">
         <v>120</v>
       </c>
-      <c r="B45" s="158"/>
-      <c r="C45" s="158"/>
-      <c r="D45" s="158"/>
-      <c r="E45" s="158"/>
-      <c r="F45" s="158"/>
+      <c r="B45" s="168"/>
+      <c r="C45" s="168"/>
+      <c r="D45" s="168"/>
+      <c r="E45" s="168"/>
+      <c r="F45" s="168"/>
       <c r="G45" s="17"/>
       <c r="H45" s="15">
         <v>60</v>
@@ -5755,16 +5698,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J45" s="159" t="s">
+      <c r="J45" s="125" t="s">
         <v>121</v>
       </c>
-      <c r="K45" s="160"/>
-      <c r="L45" s="160"/>
-      <c r="M45" s="160"/>
-      <c r="N45" s="160"/>
-      <c r="O45" s="160"/>
-      <c r="P45" s="160"/>
-      <c r="Q45" s="161"/>
+      <c r="K45" s="126"/>
+      <c r="L45" s="126"/>
+      <c r="M45" s="126"/>
+      <c r="N45" s="126"/>
+      <c r="O45" s="126"/>
+      <c r="P45" s="126"/>
+      <c r="Q45" s="127"/>
       <c r="R45" s="17"/>
       <c r="S45" s="15">
         <v>1.2</v>
@@ -5785,14 +5728,14 @@
       <c r="AD45" s="2"/>
     </row>
     <row r="46" spans="1:34" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A46" s="157" t="s">
+      <c r="A46" s="160" t="s">
         <v>122</v>
       </c>
-      <c r="B46" s="158"/>
-      <c r="C46" s="158"/>
-      <c r="D46" s="158"/>
-      <c r="E46" s="158"/>
-      <c r="F46" s="158"/>
+      <c r="B46" s="168"/>
+      <c r="C46" s="168"/>
+      <c r="D46" s="168"/>
+      <c r="E46" s="168"/>
+      <c r="F46" s="168"/>
       <c r="G46" s="17"/>
       <c r="H46" s="15">
         <v>10</v>
@@ -5801,16 +5744,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J46" s="159" t="s">
+      <c r="J46" s="125" t="s">
         <v>123</v>
       </c>
-      <c r="K46" s="160"/>
-      <c r="L46" s="160"/>
-      <c r="M46" s="160"/>
-      <c r="N46" s="160"/>
-      <c r="O46" s="160"/>
-      <c r="P46" s="160"/>
-      <c r="Q46" s="161"/>
+      <c r="K46" s="126"/>
+      <c r="L46" s="126"/>
+      <c r="M46" s="126"/>
+      <c r="N46" s="126"/>
+      <c r="O46" s="126"/>
+      <c r="P46" s="126"/>
+      <c r="Q46" s="127"/>
       <c r="R46" s="17"/>
       <c r="S46" s="15">
         <v>0.2</v>
@@ -5831,14 +5774,14 @@
       <c r="AD46" s="2"/>
     </row>
     <row r="47" spans="1:34" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A47" s="157" t="s">
+      <c r="A47" s="160" t="s">
         <v>124</v>
       </c>
-      <c r="B47" s="175"/>
-      <c r="C47" s="175"/>
-      <c r="D47" s="175"/>
-      <c r="E47" s="175"/>
-      <c r="F47" s="175"/>
+      <c r="B47" s="161"/>
+      <c r="C47" s="161"/>
+      <c r="D47" s="161"/>
+      <c r="E47" s="161"/>
+      <c r="F47" s="161"/>
       <c r="G47" s="17"/>
       <c r="H47" s="15">
         <v>1.8</v>
@@ -5847,16 +5790,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J47" s="157" t="s">
+      <c r="J47" s="160" t="s">
         <v>125</v>
       </c>
-      <c r="K47" s="158"/>
-      <c r="L47" s="158"/>
-      <c r="M47" s="158"/>
-      <c r="N47" s="158"/>
-      <c r="O47" s="158"/>
-      <c r="P47" s="158"/>
-      <c r="Q47" s="158"/>
+      <c r="K47" s="168"/>
+      <c r="L47" s="168"/>
+      <c r="M47" s="168"/>
+      <c r="N47" s="168"/>
+      <c r="O47" s="168"/>
+      <c r="P47" s="168"/>
+      <c r="Q47" s="168"/>
       <c r="R47" s="17"/>
       <c r="S47" s="15">
         <v>0.2</v>
@@ -5877,14 +5820,14 @@
       <c r="AD47" s="2"/>
     </row>
     <row r="48" spans="1:34" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A48" s="159" t="s">
+      <c r="A48" s="125" t="s">
         <v>126</v>
       </c>
-      <c r="B48" s="160"/>
-      <c r="C48" s="160"/>
-      <c r="D48" s="160"/>
-      <c r="E48" s="160"/>
-      <c r="F48" s="161"/>
+      <c r="B48" s="126"/>
+      <c r="C48" s="126"/>
+      <c r="D48" s="126"/>
+      <c r="E48" s="126"/>
+      <c r="F48" s="127"/>
       <c r="G48" s="17"/>
       <c r="H48" s="15">
         <v>1.8</v>
@@ -5893,16 +5836,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J48" s="176" t="s">
+      <c r="J48" s="169" t="s">
         <v>127</v>
       </c>
-      <c r="K48" s="177"/>
-      <c r="L48" s="177"/>
-      <c r="M48" s="177"/>
-      <c r="N48" s="177"/>
-      <c r="O48" s="177"/>
-      <c r="P48" s="177"/>
-      <c r="Q48" s="177"/>
+      <c r="K48" s="170"/>
+      <c r="L48" s="170"/>
+      <c r="M48" s="170"/>
+      <c r="N48" s="170"/>
+      <c r="O48" s="170"/>
+      <c r="P48" s="170"/>
+      <c r="Q48" s="170"/>
       <c r="R48" s="17"/>
       <c r="S48" s="15">
         <v>3.6</v>
@@ -5923,14 +5866,14 @@
       <c r="AD48" s="2"/>
     </row>
     <row r="49" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A49" s="178" t="s">
+      <c r="A49" s="131" t="s">
         <v>128</v>
       </c>
-      <c r="B49" s="179"/>
-      <c r="C49" s="179"/>
-      <c r="D49" s="179"/>
-      <c r="E49" s="179"/>
-      <c r="F49" s="179"/>
+      <c r="B49" s="132"/>
+      <c r="C49" s="132"/>
+      <c r="D49" s="132"/>
+      <c r="E49" s="132"/>
+      <c r="F49" s="132"/>
       <c r="G49" s="22"/>
       <c r="H49" s="94">
         <v>1.8</v>
@@ -5939,16 +5882,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="J49" s="180" t="s">
+      <c r="J49" s="171" t="s">
         <v>129</v>
       </c>
-      <c r="K49" s="181"/>
-      <c r="L49" s="181"/>
-      <c r="M49" s="181"/>
-      <c r="N49" s="181"/>
-      <c r="O49" s="181"/>
-      <c r="P49" s="181"/>
-      <c r="Q49" s="181"/>
+      <c r="K49" s="172"/>
+      <c r="L49" s="172"/>
+      <c r="M49" s="172"/>
+      <c r="N49" s="172"/>
+      <c r="O49" s="172"/>
+      <c r="P49" s="172"/>
+      <c r="Q49" s="172"/>
       <c r="R49" s="95"/>
       <c r="S49" s="92">
         <v>7</v>
@@ -5969,25 +5912,25 @@
       <c r="AD49" s="2"/>
     </row>
     <row r="50" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A50" s="139" t="s">
+      <c r="A50" s="137" t="s">
         <v>130</v>
       </c>
-      <c r="B50" s="140"/>
-      <c r="C50" s="140"/>
-      <c r="D50" s="140"/>
-      <c r="E50" s="140"/>
-      <c r="F50" s="140"/>
-      <c r="G50" s="140"/>
-      <c r="H50" s="140"/>
-      <c r="I50" s="140"/>
-      <c r="J50" s="140"/>
-      <c r="K50" s="140"/>
-      <c r="L50" s="140"/>
-      <c r="M50" s="140"/>
-      <c r="N50" s="140"/>
-      <c r="O50" s="140"/>
-      <c r="P50" s="140"/>
-      <c r="Q50" s="170"/>
+      <c r="B50" s="138"/>
+      <c r="C50" s="138"/>
+      <c r="D50" s="138"/>
+      <c r="E50" s="138"/>
+      <c r="F50" s="138"/>
+      <c r="G50" s="138"/>
+      <c r="H50" s="138"/>
+      <c r="I50" s="138"/>
+      <c r="J50" s="138"/>
+      <c r="K50" s="138"/>
+      <c r="L50" s="138"/>
+      <c r="M50" s="138"/>
+      <c r="N50" s="138"/>
+      <c r="O50" s="138"/>
+      <c r="P50" s="138"/>
+      <c r="Q50" s="167"/>
       <c r="R50" s="43" t="s">
         <v>131</v>
       </c>
@@ -6011,25 +5954,25 @@
       <c r="AD50" s="2"/>
     </row>
     <row r="51" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A51" s="141" t="s">
+      <c r="A51" s="139" t="s">
         <v>132</v>
       </c>
-      <c r="B51" s="142"/>
-      <c r="C51" s="142"/>
-      <c r="D51" s="142"/>
-      <c r="E51" s="142"/>
-      <c r="F51" s="142"/>
-      <c r="G51" s="142"/>
-      <c r="H51" s="142"/>
-      <c r="I51" s="142"/>
-      <c r="J51" s="142"/>
-      <c r="K51" s="142"/>
-      <c r="L51" s="142"/>
-      <c r="M51" s="142"/>
-      <c r="N51" s="142"/>
-      <c r="O51" s="142"/>
-      <c r="P51" s="142"/>
-      <c r="Q51" s="171"/>
+      <c r="B51" s="140"/>
+      <c r="C51" s="140"/>
+      <c r="D51" s="140"/>
+      <c r="E51" s="140"/>
+      <c r="F51" s="140"/>
+      <c r="G51" s="140"/>
+      <c r="H51" s="140"/>
+      <c r="I51" s="140"/>
+      <c r="J51" s="140"/>
+      <c r="K51" s="140"/>
+      <c r="L51" s="140"/>
+      <c r="M51" s="140"/>
+      <c r="N51" s="140"/>
+      <c r="O51" s="140"/>
+      <c r="P51" s="140"/>
+      <c r="Q51" s="141"/>
       <c r="R51" s="47" t="s">
         <v>111</v>
       </c>
@@ -6051,25 +5994,25 @@
       <c r="AD51" s="2"/>
     </row>
     <row r="52" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A52" s="172" t="s">
+      <c r="A52" s="110" t="s">
         <v>133</v>
       </c>
-      <c r="B52" s="173"/>
-      <c r="C52" s="173"/>
-      <c r="D52" s="173"/>
-      <c r="E52" s="173"/>
-      <c r="F52" s="173"/>
-      <c r="G52" s="173"/>
-      <c r="H52" s="173"/>
-      <c r="I52" s="173"/>
-      <c r="J52" s="173"/>
-      <c r="K52" s="173"/>
-      <c r="L52" s="173"/>
-      <c r="M52" s="173"/>
-      <c r="N52" s="173"/>
-      <c r="O52" s="173"/>
-      <c r="P52" s="173"/>
-      <c r="Q52" s="174"/>
+      <c r="B52" s="111"/>
+      <c r="C52" s="111"/>
+      <c r="D52" s="111"/>
+      <c r="E52" s="111"/>
+      <c r="F52" s="111"/>
+      <c r="G52" s="111"/>
+      <c r="H52" s="111"/>
+      <c r="I52" s="111"/>
+      <c r="J52" s="111"/>
+      <c r="K52" s="111"/>
+      <c r="L52" s="111"/>
+      <c r="M52" s="111"/>
+      <c r="N52" s="111"/>
+      <c r="O52" s="111"/>
+      <c r="P52" s="111"/>
+      <c r="Q52" s="112"/>
       <c r="R52" s="28"/>
       <c r="S52" s="34"/>
       <c r="T52" s="29">
@@ -6088,25 +6031,25 @@
       <c r="AD52" s="2"/>
     </row>
     <row r="53" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A53" s="147" t="s">
+      <c r="A53" s="145" t="s">
         <v>134</v>
       </c>
-      <c r="B53" s="148"/>
-      <c r="C53" s="148"/>
-      <c r="D53" s="148"/>
-      <c r="E53" s="148"/>
-      <c r="F53" s="148"/>
-      <c r="G53" s="148"/>
-      <c r="H53" s="148"/>
-      <c r="I53" s="148"/>
-      <c r="J53" s="148"/>
-      <c r="K53" s="148"/>
-      <c r="L53" s="148"/>
-      <c r="M53" s="148"/>
-      <c r="N53" s="148"/>
-      <c r="O53" s="148"/>
-      <c r="P53" s="148"/>
-      <c r="Q53" s="148"/>
+      <c r="B53" s="146"/>
+      <c r="C53" s="146"/>
+      <c r="D53" s="146"/>
+      <c r="E53" s="146"/>
+      <c r="F53" s="146"/>
+      <c r="G53" s="146"/>
+      <c r="H53" s="146"/>
+      <c r="I53" s="146"/>
+      <c r="J53" s="146"/>
+      <c r="K53" s="146"/>
+      <c r="L53" s="146"/>
+      <c r="M53" s="146"/>
+      <c r="N53" s="146"/>
+      <c r="O53" s="146"/>
+      <c r="P53" s="146"/>
+      <c r="Q53" s="146"/>
       <c r="R53" s="44" t="s">
         <v>135</v>
       </c>
@@ -6130,25 +6073,25 @@
       <c r="AD53" s="2"/>
     </row>
     <row r="54" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A54" s="139" t="s">
+      <c r="A54" s="137" t="s">
         <v>136</v>
       </c>
-      <c r="B54" s="140"/>
-      <c r="C54" s="140"/>
-      <c r="D54" s="140"/>
-      <c r="E54" s="140"/>
-      <c r="F54" s="140"/>
-      <c r="G54" s="140"/>
-      <c r="H54" s="140"/>
-      <c r="I54" s="140"/>
-      <c r="J54" s="140"/>
-      <c r="K54" s="140"/>
-      <c r="L54" s="140"/>
-      <c r="M54" s="140"/>
-      <c r="N54" s="140"/>
-      <c r="O54" s="140"/>
-      <c r="P54" s="140"/>
-      <c r="Q54" s="140"/>
+      <c r="B54" s="138"/>
+      <c r="C54" s="138"/>
+      <c r="D54" s="138"/>
+      <c r="E54" s="138"/>
+      <c r="F54" s="138"/>
+      <c r="G54" s="138"/>
+      <c r="H54" s="138"/>
+      <c r="I54" s="138"/>
+      <c r="J54" s="138"/>
+      <c r="K54" s="138"/>
+      <c r="L54" s="138"/>
+      <c r="M54" s="138"/>
+      <c r="N54" s="138"/>
+      <c r="O54" s="138"/>
+      <c r="P54" s="138"/>
+      <c r="Q54" s="138"/>
       <c r="R54" s="43" t="s">
         <v>137</v>
       </c>
@@ -6172,28 +6115,28 @@
       <c r="AD54" s="2"/>
     </row>
     <row r="55" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A55" s="141" t="s">
+      <c r="A55" s="139" t="s">
         <v>138</v>
       </c>
-      <c r="B55" s="142"/>
-      <c r="C55" s="142"/>
-      <c r="D55" s="142"/>
-      <c r="E55" s="142"/>
-      <c r="F55" s="142"/>
-      <c r="G55" s="142"/>
-      <c r="H55" s="142"/>
-      <c r="I55" s="142"/>
-      <c r="J55" s="142"/>
-      <c r="K55" s="142"/>
-      <c r="L55" s="142"/>
-      <c r="M55" s="142"/>
-      <c r="N55" s="142"/>
-      <c r="O55" s="142"/>
-      <c r="P55" s="142"/>
-      <c r="Q55" s="142"/>
-      <c r="R55" s="142"/>
-      <c r="S55" s="142"/>
-      <c r="T55" s="143"/>
+      <c r="B55" s="140"/>
+      <c r="C55" s="140"/>
+      <c r="D55" s="140"/>
+      <c r="E55" s="140"/>
+      <c r="F55" s="140"/>
+      <c r="G55" s="140"/>
+      <c r="H55" s="140"/>
+      <c r="I55" s="140"/>
+      <c r="J55" s="140"/>
+      <c r="K55" s="140"/>
+      <c r="L55" s="140"/>
+      <c r="M55" s="140"/>
+      <c r="N55" s="140"/>
+      <c r="O55" s="140"/>
+      <c r="P55" s="140"/>
+      <c r="Q55" s="140"/>
+      <c r="R55" s="140"/>
+      <c r="S55" s="140"/>
+      <c r="T55" s="159"/>
       <c r="U55" s="69"/>
       <c r="V55" s="84"/>
       <c r="W55" s="69"/>
@@ -6257,11 +6200,11 @@
       <c r="A57" s="165" t="s">
         <v>139</v>
       </c>
-      <c r="B57" s="182"/>
-      <c r="C57" s="182"/>
-      <c r="D57" s="182"/>
-      <c r="E57" s="182"/>
-      <c r="F57" s="182"/>
+      <c r="B57" s="166"/>
+      <c r="C57" s="166"/>
+      <c r="D57" s="166"/>
+      <c r="E57" s="166"/>
+      <c r="F57" s="166"/>
       <c r="G57" s="18"/>
       <c r="H57" s="16">
         <v>900</v>
@@ -6273,25 +6216,25 @@
       <c r="J57" s="165" t="s">
         <v>140</v>
       </c>
-      <c r="K57" s="182" t="s">
+      <c r="K57" s="166" t="s">
         <v>141</v>
       </c>
-      <c r="L57" s="182" t="s">
+      <c r="L57" s="166" t="s">
         <v>141</v>
       </c>
-      <c r="M57" s="182" t="s">
+      <c r="M57" s="166" t="s">
         <v>141</v>
       </c>
-      <c r="N57" s="182" t="s">
+      <c r="N57" s="166" t="s">
         <v>141</v>
       </c>
-      <c r="O57" s="182" t="s">
+      <c r="O57" s="166" t="s">
         <v>141</v>
       </c>
-      <c r="P57" s="182" t="s">
+      <c r="P57" s="166" t="s">
         <v>141</v>
       </c>
-      <c r="Q57" s="182" t="s">
+      <c r="Q57" s="166" t="s">
         <v>141</v>
       </c>
       <c r="R57" s="18"/>
@@ -6314,22 +6257,22 @@
       <c r="AD57" s="2"/>
     </row>
     <row r="58" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A58" s="157" t="s">
+      <c r="A58" s="160" t="s">
         <v>142</v>
       </c>
-      <c r="B58" s="175" t="s">
+      <c r="B58" s="161" t="s">
         <v>142</v>
       </c>
-      <c r="C58" s="175" t="s">
+      <c r="C58" s="161" t="s">
         <v>142</v>
       </c>
-      <c r="D58" s="175" t="s">
+      <c r="D58" s="161" t="s">
         <v>142</v>
       </c>
-      <c r="E58" s="175" t="s">
+      <c r="E58" s="161" t="s">
         <v>142</v>
       </c>
-      <c r="F58" s="175" t="s">
+      <c r="F58" s="161" t="s">
         <v>142</v>
       </c>
       <c r="G58" s="17"/>
@@ -6340,28 +6283,28 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J58" s="157" t="s">
+      <c r="J58" s="160" t="s">
         <v>143</v>
       </c>
-      <c r="K58" s="175" t="s">
+      <c r="K58" s="161" t="s">
         <v>144</v>
       </c>
-      <c r="L58" s="175" t="s">
+      <c r="L58" s="161" t="s">
         <v>144</v>
       </c>
-      <c r="M58" s="175" t="s">
+      <c r="M58" s="161" t="s">
         <v>144</v>
       </c>
-      <c r="N58" s="175" t="s">
+      <c r="N58" s="161" t="s">
         <v>144</v>
       </c>
-      <c r="O58" s="175" t="s">
+      <c r="O58" s="161" t="s">
         <v>144</v>
       </c>
-      <c r="P58" s="175" t="s">
+      <c r="P58" s="161" t="s">
         <v>144</v>
       </c>
-      <c r="Q58" s="175" t="s">
+      <c r="Q58" s="161" t="s">
         <v>144</v>
       </c>
       <c r="R58" s="17"/>
@@ -6384,22 +6327,22 @@
       <c r="AD58" s="69"/>
     </row>
     <row r="59" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A59" s="157" t="s">
+      <c r="A59" s="160" t="s">
         <v>145</v>
       </c>
-      <c r="B59" s="175" t="s">
+      <c r="B59" s="161" t="s">
         <v>145</v>
       </c>
-      <c r="C59" s="175" t="s">
+      <c r="C59" s="161" t="s">
         <v>145</v>
       </c>
-      <c r="D59" s="175" t="s">
+      <c r="D59" s="161" t="s">
         <v>145</v>
       </c>
-      <c r="E59" s="175" t="s">
+      <c r="E59" s="161" t="s">
         <v>145</v>
       </c>
-      <c r="F59" s="175" t="s">
+      <c r="F59" s="161" t="s">
         <v>145</v>
       </c>
       <c r="G59" s="17"/>
@@ -6410,28 +6353,28 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J59" s="157" t="s">
+      <c r="J59" s="160" t="s">
         <v>146</v>
       </c>
-      <c r="K59" s="175" t="s">
+      <c r="K59" s="161" t="s">
         <v>146</v>
       </c>
-      <c r="L59" s="175" t="s">
+      <c r="L59" s="161" t="s">
         <v>146</v>
       </c>
-      <c r="M59" s="175" t="s">
+      <c r="M59" s="161" t="s">
         <v>146</v>
       </c>
-      <c r="N59" s="175" t="s">
+      <c r="N59" s="161" t="s">
         <v>146</v>
       </c>
-      <c r="O59" s="175" t="s">
+      <c r="O59" s="161" t="s">
         <v>146</v>
       </c>
-      <c r="P59" s="175" t="s">
+      <c r="P59" s="161" t="s">
         <v>146</v>
       </c>
-      <c r="Q59" s="175" t="s">
+      <c r="Q59" s="161" t="s">
         <v>146</v>
       </c>
       <c r="R59" s="17"/>
@@ -6454,22 +6397,22 @@
       <c r="AD59" s="69"/>
     </row>
     <row r="60" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A60" s="157" t="s">
+      <c r="A60" s="160" t="s">
         <v>147</v>
       </c>
-      <c r="B60" s="175" t="s">
+      <c r="B60" s="161" t="s">
         <v>148</v>
       </c>
-      <c r="C60" s="175" t="s">
+      <c r="C60" s="161" t="s">
         <v>148</v>
       </c>
-      <c r="D60" s="175" t="s">
+      <c r="D60" s="161" t="s">
         <v>148</v>
       </c>
-      <c r="E60" s="175" t="s">
+      <c r="E60" s="161" t="s">
         <v>148</v>
       </c>
-      <c r="F60" s="175" t="s">
+      <c r="F60" s="161" t="s">
         <v>148</v>
       </c>
       <c r="G60" s="17"/>
@@ -6480,28 +6423,28 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J60" s="157" t="s">
+      <c r="J60" s="160" t="s">
         <v>149</v>
       </c>
-      <c r="K60" s="175" t="s">
+      <c r="K60" s="161" t="s">
         <v>149</v>
       </c>
-      <c r="L60" s="175" t="s">
+      <c r="L60" s="161" t="s">
         <v>149</v>
       </c>
-      <c r="M60" s="175" t="s">
+      <c r="M60" s="161" t="s">
         <v>149</v>
       </c>
-      <c r="N60" s="175" t="s">
+      <c r="N60" s="161" t="s">
         <v>149</v>
       </c>
-      <c r="O60" s="175" t="s">
+      <c r="O60" s="161" t="s">
         <v>149</v>
       </c>
-      <c r="P60" s="175" t="s">
+      <c r="P60" s="161" t="s">
         <v>149</v>
       </c>
-      <c r="Q60" s="175" t="s">
+      <c r="Q60" s="161" t="s">
         <v>149</v>
       </c>
       <c r="R60" s="17"/>
@@ -6524,22 +6467,22 @@
       <c r="AD60" s="69"/>
     </row>
     <row r="61" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A61" s="157" t="s">
+      <c r="A61" s="160" t="s">
         <v>150</v>
       </c>
-      <c r="B61" s="175" t="s">
+      <c r="B61" s="161" t="s">
         <v>150</v>
       </c>
-      <c r="C61" s="175" t="s">
+      <c r="C61" s="161" t="s">
         <v>150</v>
       </c>
-      <c r="D61" s="175" t="s">
+      <c r="D61" s="161" t="s">
         <v>150</v>
       </c>
-      <c r="E61" s="175" t="s">
+      <c r="E61" s="161" t="s">
         <v>150</v>
       </c>
-      <c r="F61" s="175" t="s">
+      <c r="F61" s="161" t="s">
         <v>150</v>
       </c>
       <c r="G61" s="17"/>
@@ -6550,16 +6493,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J61" s="159" t="s">
+      <c r="J61" s="125" t="s">
         <v>151</v>
       </c>
-      <c r="K61" s="160"/>
-      <c r="L61" s="160"/>
-      <c r="M61" s="160"/>
-      <c r="N61" s="160"/>
-      <c r="O61" s="160"/>
-      <c r="P61" s="160"/>
-      <c r="Q61" s="161"/>
+      <c r="K61" s="126"/>
+      <c r="L61" s="126"/>
+      <c r="M61" s="126"/>
+      <c r="N61" s="126"/>
+      <c r="O61" s="126"/>
+      <c r="P61" s="126"/>
+      <c r="Q61" s="127"/>
       <c r="R61" s="17"/>
       <c r="S61" s="15">
         <v>1800</v>
@@ -6580,22 +6523,22 @@
       <c r="AD61" s="69"/>
     </row>
     <row r="62" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A62" s="157" t="s">
+      <c r="A62" s="160" t="s">
         <v>152</v>
       </c>
-      <c r="B62" s="175" t="s">
+      <c r="B62" s="161" t="s">
         <v>152</v>
       </c>
-      <c r="C62" s="175" t="s">
+      <c r="C62" s="161" t="s">
         <v>152</v>
       </c>
-      <c r="D62" s="175" t="s">
+      <c r="D62" s="161" t="s">
         <v>152</v>
       </c>
-      <c r="E62" s="175" t="s">
+      <c r="E62" s="161" t="s">
         <v>152</v>
       </c>
-      <c r="F62" s="175" t="s">
+      <c r="F62" s="161" t="s">
         <v>152</v>
       </c>
       <c r="G62" s="17"/>
@@ -6606,16 +6549,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J62" s="187" t="s">
+      <c r="J62" s="128" t="s">
         <v>153</v>
       </c>
-      <c r="K62" s="188"/>
-      <c r="L62" s="188"/>
-      <c r="M62" s="188"/>
-      <c r="N62" s="188"/>
-      <c r="O62" s="188"/>
-      <c r="P62" s="188"/>
-      <c r="Q62" s="189"/>
+      <c r="K62" s="129"/>
+      <c r="L62" s="129"/>
+      <c r="M62" s="129"/>
+      <c r="N62" s="129"/>
+      <c r="O62" s="129"/>
+      <c r="P62" s="129"/>
+      <c r="Q62" s="130"/>
       <c r="R62" s="17"/>
       <c r="S62" s="15">
         <v>900</v>
@@ -6636,22 +6579,22 @@
       <c r="AD62" s="69"/>
     </row>
     <row r="63" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A63" s="157" t="s">
+      <c r="A63" s="160" t="s">
         <v>154</v>
       </c>
-      <c r="B63" s="175" t="s">
+      <c r="B63" s="161" t="s">
         <v>154</v>
       </c>
-      <c r="C63" s="175" t="s">
+      <c r="C63" s="161" t="s">
         <v>154</v>
       </c>
-      <c r="D63" s="175" t="s">
+      <c r="D63" s="161" t="s">
         <v>154</v>
       </c>
-      <c r="E63" s="175" t="s">
+      <c r="E63" s="161" t="s">
         <v>154</v>
       </c>
-      <c r="F63" s="175" t="s">
+      <c r="F63" s="161" t="s">
         <v>154</v>
       </c>
       <c r="G63" s="17"/>
@@ -6662,16 +6605,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J63" s="187" t="s">
+      <c r="J63" s="128" t="s">
         <v>155</v>
       </c>
-      <c r="K63" s="188"/>
-      <c r="L63" s="188"/>
-      <c r="M63" s="188"/>
-      <c r="N63" s="188"/>
-      <c r="O63" s="188"/>
-      <c r="P63" s="188"/>
-      <c r="Q63" s="189"/>
+      <c r="K63" s="129"/>
+      <c r="L63" s="129"/>
+      <c r="M63" s="129"/>
+      <c r="N63" s="129"/>
+      <c r="O63" s="129"/>
+      <c r="P63" s="129"/>
+      <c r="Q63" s="130"/>
       <c r="R63" s="17"/>
       <c r="S63" s="15">
         <v>100</v>
@@ -6692,22 +6635,22 @@
       <c r="AD63" s="69"/>
     </row>
     <row r="64" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A64" s="157" t="s">
+      <c r="A64" s="160" t="s">
         <v>156</v>
       </c>
-      <c r="B64" s="175" t="s">
+      <c r="B64" s="161" t="s">
         <v>157</v>
       </c>
-      <c r="C64" s="175" t="s">
+      <c r="C64" s="161" t="s">
         <v>157</v>
       </c>
-      <c r="D64" s="175" t="s">
+      <c r="D64" s="161" t="s">
         <v>157</v>
       </c>
-      <c r="E64" s="175" t="s">
+      <c r="E64" s="161" t="s">
         <v>157</v>
       </c>
-      <c r="F64" s="175" t="s">
+      <c r="F64" s="161" t="s">
         <v>157</v>
       </c>
       <c r="G64" s="17"/>
@@ -6718,16 +6661,16 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J64" s="187" t="s">
+      <c r="J64" s="128" t="s">
         <v>158</v>
       </c>
-      <c r="K64" s="188"/>
-      <c r="L64" s="188"/>
-      <c r="M64" s="188"/>
-      <c r="N64" s="188"/>
-      <c r="O64" s="188"/>
-      <c r="P64" s="188"/>
-      <c r="Q64" s="189"/>
+      <c r="K64" s="129"/>
+      <c r="L64" s="129"/>
+      <c r="M64" s="129"/>
+      <c r="N64" s="129"/>
+      <c r="O64" s="129"/>
+      <c r="P64" s="129"/>
+      <c r="Q64" s="130"/>
       <c r="R64" s="22"/>
       <c r="S64" s="24">
         <v>100</v>
@@ -6748,22 +6691,22 @@
       <c r="AD64" s="69"/>
     </row>
     <row r="65" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A65" s="178" t="s">
+      <c r="A65" s="131" t="s">
         <v>159</v>
       </c>
-      <c r="B65" s="179" t="s">
+      <c r="B65" s="132" t="s">
         <v>160</v>
       </c>
-      <c r="C65" s="179" t="s">
+      <c r="C65" s="132" t="s">
         <v>160</v>
       </c>
-      <c r="D65" s="179" t="s">
+      <c r="D65" s="132" t="s">
         <v>160</v>
       </c>
-      <c r="E65" s="179" t="s">
+      <c r="E65" s="132" t="s">
         <v>160</v>
       </c>
-      <c r="F65" s="183" t="s">
+      <c r="F65" s="133" t="s">
         <v>160</v>
       </c>
       <c r="G65" s="22"/>
@@ -6774,14 +6717,14 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="J65" s="184"/>
-      <c r="K65" s="185"/>
-      <c r="L65" s="185"/>
-      <c r="M65" s="185"/>
-      <c r="N65" s="185"/>
-      <c r="O65" s="185"/>
-      <c r="P65" s="185"/>
-      <c r="Q65" s="186"/>
+      <c r="J65" s="134"/>
+      <c r="K65" s="135"/>
+      <c r="L65" s="135"/>
+      <c r="M65" s="135"/>
+      <c r="N65" s="135"/>
+      <c r="O65" s="135"/>
+      <c r="P65" s="135"/>
+      <c r="Q65" s="136"/>
       <c r="R65" s="67"/>
       <c r="S65" s="67"/>
       <c r="T65" s="66"/>
@@ -6797,25 +6740,25 @@
       <c r="AD65" s="69"/>
     </row>
     <row r="66" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A66" s="139" t="s">
+      <c r="A66" s="137" t="s">
         <v>161</v>
       </c>
-      <c r="B66" s="140"/>
-      <c r="C66" s="140"/>
-      <c r="D66" s="140"/>
-      <c r="E66" s="140"/>
-      <c r="F66" s="140"/>
-      <c r="G66" s="140"/>
-      <c r="H66" s="140"/>
-      <c r="I66" s="140"/>
-      <c r="J66" s="140"/>
-      <c r="K66" s="140"/>
-      <c r="L66" s="140"/>
-      <c r="M66" s="140"/>
-      <c r="N66" s="140"/>
-      <c r="O66" s="140"/>
-      <c r="P66" s="140"/>
-      <c r="Q66" s="140"/>
+      <c r="B66" s="138"/>
+      <c r="C66" s="138"/>
+      <c r="D66" s="138"/>
+      <c r="E66" s="138"/>
+      <c r="F66" s="138"/>
+      <c r="G66" s="138"/>
+      <c r="H66" s="138"/>
+      <c r="I66" s="138"/>
+      <c r="J66" s="138"/>
+      <c r="K66" s="138"/>
+      <c r="L66" s="138"/>
+      <c r="M66" s="138"/>
+      <c r="N66" s="138"/>
+      <c r="O66" s="138"/>
+      <c r="P66" s="138"/>
+      <c r="Q66" s="138"/>
       <c r="R66" s="43" t="s">
         <v>162</v>
       </c>
@@ -6839,28 +6782,28 @@
       <c r="AD66" s="69"/>
     </row>
     <row r="67" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A67" s="141" t="s">
+      <c r="A67" s="139" t="s">
         <v>163</v>
       </c>
-      <c r="B67" s="142"/>
-      <c r="C67" s="142"/>
-      <c r="D67" s="142"/>
-      <c r="E67" s="142"/>
-      <c r="F67" s="142"/>
-      <c r="G67" s="142"/>
-      <c r="H67" s="142"/>
-      <c r="I67" s="142"/>
-      <c r="J67" s="142"/>
-      <c r="K67" s="142"/>
-      <c r="L67" s="142"/>
-      <c r="M67" s="142"/>
-      <c r="N67" s="142"/>
-      <c r="O67" s="142"/>
-      <c r="P67" s="142"/>
-      <c r="Q67" s="142"/>
-      <c r="R67" s="142"/>
-      <c r="S67" s="142"/>
-      <c r="T67" s="143"/>
+      <c r="B67" s="140"/>
+      <c r="C67" s="140"/>
+      <c r="D67" s="140"/>
+      <c r="E67" s="140"/>
+      <c r="F67" s="140"/>
+      <c r="G67" s="140"/>
+      <c r="H67" s="140"/>
+      <c r="I67" s="140"/>
+      <c r="J67" s="140"/>
+      <c r="K67" s="140"/>
+      <c r="L67" s="140"/>
+      <c r="M67" s="140"/>
+      <c r="N67" s="140"/>
+      <c r="O67" s="140"/>
+      <c r="P67" s="140"/>
+      <c r="Q67" s="140"/>
+      <c r="R67" s="140"/>
+      <c r="S67" s="140"/>
+      <c r="T67" s="159"/>
       <c r="U67" s="69"/>
       <c r="V67" s="84"/>
       <c r="W67" s="69"/>
@@ -6873,11 +6816,11 @@
       <c r="AD67" s="69"/>
     </row>
     <row r="68" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A68" s="141" t="s">
+      <c r="A68" s="139" t="s">
         <v>164</v>
       </c>
-      <c r="B68" s="142"/>
-      <c r="C68" s="171"/>
+      <c r="B68" s="140"/>
+      <c r="C68" s="141"/>
       <c r="D68" s="47" t="s">
         <v>111</v>
       </c>
@@ -6887,12 +6830,12 @@
       <c r="F68" s="48" t="s">
         <v>113</v>
       </c>
-      <c r="G68" s="141" t="s">
+      <c r="G68" s="139" t="s">
         <v>164</v>
       </c>
-      <c r="H68" s="142"/>
-      <c r="I68" s="142"/>
-      <c r="J68" s="171"/>
+      <c r="H68" s="140"/>
+      <c r="I68" s="140"/>
+      <c r="J68" s="141"/>
       <c r="K68" s="47" t="s">
         <v>111</v>
       </c>
@@ -6902,12 +6845,12 @@
       <c r="M68" s="48" t="s">
         <v>113</v>
       </c>
-      <c r="N68" s="141" t="s">
+      <c r="N68" s="139" t="s">
         <v>164</v>
       </c>
-      <c r="O68" s="142"/>
-      <c r="P68" s="142"/>
-      <c r="Q68" s="171"/>
+      <c r="O68" s="140"/>
+      <c r="P68" s="140"/>
+      <c r="Q68" s="141"/>
       <c r="R68" s="47" t="s">
         <v>111</v>
       </c>
@@ -6929,11 +6872,11 @@
       <c r="AD68" s="69"/>
     </row>
     <row r="69" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A69" s="190" t="s">
+      <c r="A69" s="142" t="s">
         <v>165</v>
       </c>
-      <c r="B69" s="191"/>
-      <c r="C69" s="192"/>
+      <c r="B69" s="143"/>
+      <c r="C69" s="144"/>
       <c r="D69" s="18"/>
       <c r="E69" s="16">
         <v>915</v>
@@ -6942,12 +6885,12 @@
         <f>D69*E69</f>
         <v>0</v>
       </c>
-      <c r="G69" s="190" t="s">
+      <c r="G69" s="142" t="s">
         <v>166</v>
       </c>
-      <c r="H69" s="191"/>
-      <c r="I69" s="191"/>
-      <c r="J69" s="192"/>
+      <c r="H69" s="143"/>
+      <c r="I69" s="143"/>
+      <c r="J69" s="144"/>
       <c r="K69" s="18"/>
       <c r="L69" s="16">
         <v>351</v>
@@ -6956,12 +6899,12 @@
         <f>K69*L69</f>
         <v>0</v>
       </c>
-      <c r="N69" s="190" t="s">
+      <c r="N69" s="142" t="s">
         <v>167</v>
       </c>
-      <c r="O69" s="191"/>
-      <c r="P69" s="191"/>
-      <c r="Q69" s="192"/>
+      <c r="O69" s="143"/>
+      <c r="P69" s="143"/>
+      <c r="Q69" s="144"/>
       <c r="R69" s="18"/>
       <c r="S69" s="16">
         <v>130</v>
@@ -6982,11 +6925,11 @@
       <c r="AD69" s="69"/>
     </row>
     <row r="70" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A70" s="159" t="s">
+      <c r="A70" s="125" t="s">
         <v>168</v>
       </c>
-      <c r="B70" s="160"/>
-      <c r="C70" s="161"/>
+      <c r="B70" s="126"/>
+      <c r="C70" s="127"/>
       <c r="D70" s="17"/>
       <c r="E70" s="15">
         <v>777</v>
@@ -6995,12 +6938,12 @@
         <f t="shared" ref="F70:F77" si="4">D70*E70</f>
         <v>0</v>
       </c>
-      <c r="G70" s="159" t="s">
+      <c r="G70" s="125" t="s">
         <v>169</v>
       </c>
-      <c r="H70" s="160"/>
-      <c r="I70" s="160"/>
-      <c r="J70" s="161"/>
+      <c r="H70" s="126"/>
+      <c r="I70" s="126"/>
+      <c r="J70" s="127"/>
       <c r="K70" s="32"/>
       <c r="L70" s="15">
         <v>316</v>
@@ -7009,12 +6952,12 @@
         <f t="shared" ref="M70:M77" si="5">K70*L70</f>
         <v>0</v>
       </c>
-      <c r="N70" s="159" t="s">
+      <c r="N70" s="125" t="s">
         <v>170</v>
       </c>
-      <c r="O70" s="160"/>
-      <c r="P70" s="160"/>
-      <c r="Q70" s="161"/>
+      <c r="O70" s="126"/>
+      <c r="P70" s="126"/>
+      <c r="Q70" s="127"/>
       <c r="R70" s="17"/>
       <c r="S70" s="15">
         <v>120</v>
@@ -7035,11 +6978,11 @@
       <c r="AD70" s="69"/>
     </row>
     <row r="71" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A71" s="159" t="s">
+      <c r="A71" s="125" t="s">
         <v>171</v>
       </c>
-      <c r="B71" s="160"/>
-      <c r="C71" s="161"/>
+      <c r="B71" s="126"/>
+      <c r="C71" s="127"/>
       <c r="D71" s="17"/>
       <c r="E71" s="15">
         <v>630</v>
@@ -7062,12 +7005,12 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N71" s="159" t="s">
+      <c r="N71" s="125" t="s">
         <v>173</v>
       </c>
-      <c r="O71" s="160"/>
-      <c r="P71" s="160"/>
-      <c r="Q71" s="161"/>
+      <c r="O71" s="126"/>
+      <c r="P71" s="126"/>
+      <c r="Q71" s="127"/>
       <c r="R71" s="17"/>
       <c r="S71" s="15">
         <v>95</v>
@@ -7088,11 +7031,11 @@
       <c r="AD71" s="69"/>
     </row>
     <row r="72" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A72" s="159" t="s">
+      <c r="A72" s="125" t="s">
         <v>174</v>
       </c>
-      <c r="B72" s="160"/>
-      <c r="C72" s="161"/>
+      <c r="B72" s="126"/>
+      <c r="C72" s="127"/>
       <c r="D72" s="17"/>
       <c r="E72" s="15">
         <v>573</v>
@@ -7115,12 +7058,12 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N72" s="159" t="s">
+      <c r="N72" s="125" t="s">
         <v>176</v>
       </c>
-      <c r="O72" s="160"/>
-      <c r="P72" s="160"/>
-      <c r="Q72" s="161"/>
+      <c r="O72" s="126"/>
+      <c r="P72" s="126"/>
+      <c r="Q72" s="127"/>
       <c r="R72" s="17"/>
       <c r="S72" s="15">
         <v>85</v>
@@ -7141,11 +7084,11 @@
       <c r="AD72" s="69"/>
     </row>
     <row r="73" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A73" s="159" t="s">
+      <c r="A73" s="125" t="s">
         <v>177</v>
       </c>
-      <c r="B73" s="160"/>
-      <c r="C73" s="161"/>
+      <c r="B73" s="126"/>
+      <c r="C73" s="127"/>
       <c r="D73" s="17"/>
       <c r="E73" s="15">
         <v>522</v>
@@ -7168,12 +7111,12 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N73" s="159" t="s">
+      <c r="N73" s="125" t="s">
         <v>179</v>
       </c>
-      <c r="O73" s="160"/>
-      <c r="P73" s="160"/>
-      <c r="Q73" s="161"/>
+      <c r="O73" s="126"/>
+      <c r="P73" s="126"/>
+      <c r="Q73" s="127"/>
       <c r="R73" s="17"/>
       <c r="S73" s="15">
         <v>80</v>
@@ -7194,11 +7137,11 @@
       <c r="AD73" s="69"/>
     </row>
     <row r="74" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A74" s="159" t="s">
+      <c r="A74" s="125" t="s">
         <v>180</v>
       </c>
-      <c r="B74" s="160"/>
-      <c r="C74" s="161"/>
+      <c r="B74" s="126"/>
+      <c r="C74" s="127"/>
       <c r="D74" s="17"/>
       <c r="E74" s="15">
         <v>414</v>
@@ -7221,12 +7164,12 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N74" s="159" t="s">
+      <c r="N74" s="125" t="s">
         <v>182</v>
       </c>
-      <c r="O74" s="160"/>
-      <c r="P74" s="160"/>
-      <c r="Q74" s="161"/>
+      <c r="O74" s="126"/>
+      <c r="P74" s="126"/>
+      <c r="Q74" s="127"/>
       <c r="R74" s="17"/>
       <c r="S74" s="15">
         <v>60</v>
@@ -7247,11 +7190,11 @@
       <c r="AD74" s="69"/>
     </row>
     <row r="75" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A75" s="159" t="s">
+      <c r="A75" s="125" t="s">
         <v>183</v>
       </c>
-      <c r="B75" s="160"/>
-      <c r="C75" s="161"/>
+      <c r="B75" s="126"/>
+      <c r="C75" s="127"/>
       <c r="D75" s="17"/>
       <c r="E75" s="15">
         <v>381</v>
@@ -7274,12 +7217,12 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N75" s="159" t="s">
+      <c r="N75" s="125" t="s">
         <v>185</v>
       </c>
-      <c r="O75" s="160"/>
-      <c r="P75" s="160"/>
-      <c r="Q75" s="161"/>
+      <c r="O75" s="126"/>
+      <c r="P75" s="126"/>
+      <c r="Q75" s="127"/>
       <c r="R75" s="17"/>
       <c r="S75" s="15">
         <v>50</v>
@@ -7300,11 +7243,11 @@
       <c r="AD75" s="69"/>
     </row>
     <row r="76" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A76" s="159" t="s">
+      <c r="A76" s="125" t="s">
         <v>186</v>
       </c>
-      <c r="B76" s="160"/>
-      <c r="C76" s="161"/>
+      <c r="B76" s="126"/>
+      <c r="C76" s="127"/>
       <c r="D76" s="17"/>
       <c r="E76" s="15">
         <v>270</v>
@@ -7327,12 +7270,12 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N76" s="159" t="s">
+      <c r="N76" s="125" t="s">
         <v>188</v>
       </c>
-      <c r="O76" s="160"/>
-      <c r="P76" s="160"/>
-      <c r="Q76" s="161"/>
+      <c r="O76" s="126"/>
+      <c r="P76" s="126"/>
+      <c r="Q76" s="127"/>
       <c r="R76" s="17"/>
       <c r="S76" s="15">
         <v>45</v>
@@ -7353,11 +7296,11 @@
       <c r="AD76" s="69"/>
     </row>
     <row r="77" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A77" s="178" t="s">
+      <c r="A77" s="131" t="s">
         <v>189</v>
       </c>
-      <c r="B77" s="179"/>
-      <c r="C77" s="183"/>
+      <c r="B77" s="132"/>
+      <c r="C77" s="133"/>
       <c r="D77" s="22"/>
       <c r="E77" s="24">
         <v>291</v>
@@ -7380,12 +7323,12 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N77" s="178" t="s">
+      <c r="N77" s="131" t="s">
         <v>191</v>
       </c>
-      <c r="O77" s="179"/>
-      <c r="P77" s="179"/>
-      <c r="Q77" s="183"/>
+      <c r="O77" s="132"/>
+      <c r="P77" s="132"/>
+      <c r="Q77" s="133"/>
       <c r="R77" s="22"/>
       <c r="S77" s="24">
         <v>40</v>
@@ -7406,25 +7349,25 @@
       <c r="AD77" s="69"/>
     </row>
     <row r="78" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A78" s="139" t="s">
+      <c r="A78" s="137" t="s">
         <v>192</v>
       </c>
-      <c r="B78" s="140"/>
-      <c r="C78" s="140"/>
-      <c r="D78" s="140"/>
-      <c r="E78" s="140"/>
-      <c r="F78" s="140"/>
-      <c r="G78" s="140"/>
-      <c r="H78" s="140"/>
-      <c r="I78" s="140"/>
-      <c r="J78" s="140"/>
-      <c r="K78" s="140"/>
-      <c r="L78" s="140"/>
-      <c r="M78" s="140"/>
-      <c r="N78" s="140"/>
-      <c r="O78" s="140"/>
-      <c r="P78" s="140"/>
-      <c r="Q78" s="140"/>
+      <c r="B78" s="138"/>
+      <c r="C78" s="138"/>
+      <c r="D78" s="138"/>
+      <c r="E78" s="138"/>
+      <c r="F78" s="138"/>
+      <c r="G78" s="138"/>
+      <c r="H78" s="138"/>
+      <c r="I78" s="138"/>
+      <c r="J78" s="138"/>
+      <c r="K78" s="138"/>
+      <c r="L78" s="138"/>
+      <c r="M78" s="138"/>
+      <c r="N78" s="138"/>
+      <c r="O78" s="138"/>
+      <c r="P78" s="138"/>
+      <c r="Q78" s="138"/>
       <c r="R78" s="43" t="s">
         <v>193</v>
       </c>
@@ -7448,14 +7391,14 @@
       <c r="AD78" s="69"/>
     </row>
     <row r="79" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A79" s="141" t="s">
+      <c r="A79" s="139" t="s">
         <v>132</v>
       </c>
-      <c r="B79" s="142"/>
-      <c r="C79" s="142"/>
-      <c r="D79" s="142"/>
-      <c r="E79" s="142"/>
-      <c r="F79" s="171"/>
+      <c r="B79" s="140"/>
+      <c r="C79" s="140"/>
+      <c r="D79" s="140"/>
+      <c r="E79" s="140"/>
+      <c r="F79" s="141"/>
       <c r="G79" s="47" t="s">
         <v>111</v>
       </c>
@@ -7465,16 +7408,16 @@
       <c r="I79" s="48" t="s">
         <v>113</v>
       </c>
-      <c r="J79" s="141" t="s">
+      <c r="J79" s="139" t="s">
         <v>132</v>
       </c>
-      <c r="K79" s="142"/>
-      <c r="L79" s="142"/>
-      <c r="M79" s="142"/>
-      <c r="N79" s="142"/>
-      <c r="O79" s="142"/>
-      <c r="P79" s="142"/>
-      <c r="Q79" s="171"/>
+      <c r="K79" s="140"/>
+      <c r="L79" s="140"/>
+      <c r="M79" s="140"/>
+      <c r="N79" s="140"/>
+      <c r="O79" s="140"/>
+      <c r="P79" s="140"/>
+      <c r="Q79" s="141"/>
       <c r="R79" s="47" t="s">
         <v>111</v>
       </c>
@@ -7496,22 +7439,22 @@
       <c r="AD79" s="69"/>
     </row>
     <row r="80" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A80" s="190" t="s">
+      <c r="A80" s="142" t="s">
         <v>194</v>
       </c>
-      <c r="B80" s="191" t="s">
+      <c r="B80" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="C80" s="191" t="s">
+      <c r="C80" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="D80" s="191" t="s">
+      <c r="D80" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="E80" s="191" t="s">
+      <c r="E80" s="143" t="s">
         <v>194</v>
       </c>
-      <c r="F80" s="192" t="s">
+      <c r="F80" s="144" t="s">
         <v>194</v>
       </c>
       <c r="G80" s="18"/>
@@ -7522,28 +7465,28 @@
         <f t="shared" ref="I80:I88" si="7">G80*H80</f>
         <v>0</v>
       </c>
-      <c r="J80" s="190" t="s">
+      <c r="J80" s="142" t="s">
         <v>195</v>
       </c>
-      <c r="K80" s="191" t="s">
+      <c r="K80" s="143" t="s">
         <v>195</v>
       </c>
-      <c r="L80" s="191" t="s">
+      <c r="L80" s="143" t="s">
         <v>195</v>
       </c>
-      <c r="M80" s="191" t="s">
+      <c r="M80" s="143" t="s">
         <v>195</v>
       </c>
-      <c r="N80" s="191" t="s">
+      <c r="N80" s="143" t="s">
         <v>195</v>
       </c>
-      <c r="O80" s="191" t="s">
+      <c r="O80" s="143" t="s">
         <v>195</v>
       </c>
-      <c r="P80" s="191" t="s">
+      <c r="P80" s="143" t="s">
         <v>195</v>
       </c>
-      <c r="Q80" s="192" t="s">
+      <c r="Q80" s="144" t="s">
         <v>195</v>
       </c>
       <c r="R80" s="18"/>
@@ -7566,22 +7509,22 @@
       <c r="AD80" s="69"/>
     </row>
     <row r="81" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A81" s="159" t="s">
+      <c r="A81" s="125" t="s">
         <v>196</v>
       </c>
-      <c r="B81" s="160" t="s">
+      <c r="B81" s="126" t="s">
         <v>196</v>
       </c>
-      <c r="C81" s="160" t="s">
+      <c r="C81" s="126" t="s">
         <v>196</v>
       </c>
-      <c r="D81" s="160" t="s">
+      <c r="D81" s="126" t="s">
         <v>196</v>
       </c>
-      <c r="E81" s="160" t="s">
+      <c r="E81" s="126" t="s">
         <v>196</v>
       </c>
-      <c r="F81" s="161" t="s">
+      <c r="F81" s="127" t="s">
         <v>196</v>
       </c>
       <c r="G81" s="17"/>
@@ -7592,28 +7535,28 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J81" s="159" t="s">
+      <c r="J81" s="125" t="s">
         <v>197</v>
       </c>
-      <c r="K81" s="160" t="s">
+      <c r="K81" s="126" t="s">
         <v>197</v>
       </c>
-      <c r="L81" s="160" t="s">
+      <c r="L81" s="126" t="s">
         <v>197</v>
       </c>
-      <c r="M81" s="160" t="s">
+      <c r="M81" s="126" t="s">
         <v>197</v>
       </c>
-      <c r="N81" s="160" t="s">
+      <c r="N81" s="126" t="s">
         <v>197</v>
       </c>
-      <c r="O81" s="160" t="s">
+      <c r="O81" s="126" t="s">
         <v>197</v>
       </c>
-      <c r="P81" s="160" t="s">
+      <c r="P81" s="126" t="s">
         <v>197</v>
       </c>
-      <c r="Q81" s="161" t="s">
+      <c r="Q81" s="127" t="s">
         <v>197</v>
       </c>
       <c r="R81" s="17"/>
@@ -7636,22 +7579,22 @@
       <c r="AD81" s="69"/>
     </row>
     <row r="82" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A82" s="159" t="s">
+      <c r="A82" s="125" t="s">
         <v>198</v>
       </c>
-      <c r="B82" s="160" t="s">
+      <c r="B82" s="126" t="s">
         <v>198</v>
       </c>
-      <c r="C82" s="160" t="s">
+      <c r="C82" s="126" t="s">
         <v>198</v>
       </c>
-      <c r="D82" s="160" t="s">
+      <c r="D82" s="126" t="s">
         <v>198</v>
       </c>
-      <c r="E82" s="160" t="s">
+      <c r="E82" s="126" t="s">
         <v>198</v>
       </c>
-      <c r="F82" s="161" t="s">
+      <c r="F82" s="127" t="s">
         <v>198</v>
       </c>
       <c r="G82" s="17"/>
@@ -7662,28 +7605,28 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J82" s="159" t="s">
+      <c r="J82" s="125" t="s">
         <v>199</v>
       </c>
-      <c r="K82" s="160" t="s">
+      <c r="K82" s="126" t="s">
         <v>199</v>
       </c>
-      <c r="L82" s="160" t="s">
+      <c r="L82" s="126" t="s">
         <v>199</v>
       </c>
-      <c r="M82" s="160" t="s">
+      <c r="M82" s="126" t="s">
         <v>199</v>
       </c>
-      <c r="N82" s="160" t="s">
+      <c r="N82" s="126" t="s">
         <v>199</v>
       </c>
-      <c r="O82" s="160" t="s">
+      <c r="O82" s="126" t="s">
         <v>199</v>
       </c>
-      <c r="P82" s="160" t="s">
+      <c r="P82" s="126" t="s">
         <v>199</v>
       </c>
-      <c r="Q82" s="161" t="s">
+      <c r="Q82" s="127" t="s">
         <v>199</v>
       </c>
       <c r="R82" s="17"/>
@@ -7706,22 +7649,22 @@
       <c r="AD82" s="69"/>
     </row>
     <row r="83" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A83" s="159" t="s">
+      <c r="A83" s="125" t="s">
         <v>200</v>
       </c>
-      <c r="B83" s="160" t="s">
+      <c r="B83" s="126" t="s">
         <v>200</v>
       </c>
-      <c r="C83" s="160" t="s">
+      <c r="C83" s="126" t="s">
         <v>200</v>
       </c>
-      <c r="D83" s="160" t="s">
+      <c r="D83" s="126" t="s">
         <v>200</v>
       </c>
-      <c r="E83" s="160" t="s">
+      <c r="E83" s="126" t="s">
         <v>200</v>
       </c>
-      <c r="F83" s="161" t="s">
+      <c r="F83" s="127" t="s">
         <v>200</v>
       </c>
       <c r="G83" s="17"/>
@@ -7732,28 +7675,28 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J83" s="159" t="s">
+      <c r="J83" s="125" t="s">
         <v>201</v>
       </c>
-      <c r="K83" s="160" t="s">
+      <c r="K83" s="126" t="s">
         <v>201</v>
       </c>
-      <c r="L83" s="160" t="s">
+      <c r="L83" s="126" t="s">
         <v>201</v>
       </c>
-      <c r="M83" s="160" t="s">
+      <c r="M83" s="126" t="s">
         <v>201</v>
       </c>
-      <c r="N83" s="160" t="s">
+      <c r="N83" s="126" t="s">
         <v>201</v>
       </c>
-      <c r="O83" s="160" t="s">
+      <c r="O83" s="126" t="s">
         <v>201</v>
       </c>
-      <c r="P83" s="160" t="s">
+      <c r="P83" s="126" t="s">
         <v>201</v>
       </c>
-      <c r="Q83" s="161" t="s">
+      <c r="Q83" s="127" t="s">
         <v>201</v>
       </c>
       <c r="R83" s="17"/>
@@ -7776,22 +7719,22 @@
       <c r="AD83" s="69"/>
     </row>
     <row r="84" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A84" s="159" t="s">
+      <c r="A84" s="125" t="s">
         <v>202</v>
       </c>
-      <c r="B84" s="160" t="s">
+      <c r="B84" s="126" t="s">
         <v>202</v>
       </c>
-      <c r="C84" s="160" t="s">
+      <c r="C84" s="126" t="s">
         <v>202</v>
       </c>
-      <c r="D84" s="160" t="s">
+      <c r="D84" s="126" t="s">
         <v>202</v>
       </c>
-      <c r="E84" s="160" t="s">
+      <c r="E84" s="126" t="s">
         <v>202</v>
       </c>
-      <c r="F84" s="161" t="s">
+      <c r="F84" s="127" t="s">
         <v>202</v>
       </c>
       <c r="G84" s="17"/>
@@ -7802,28 +7745,28 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J84" s="159" t="s">
+      <c r="J84" s="125" t="s">
         <v>203</v>
       </c>
-      <c r="K84" s="160" t="s">
+      <c r="K84" s="126" t="s">
         <v>203</v>
       </c>
-      <c r="L84" s="160" t="s">
+      <c r="L84" s="126" t="s">
         <v>203</v>
       </c>
-      <c r="M84" s="160" t="s">
+      <c r="M84" s="126" t="s">
         <v>203</v>
       </c>
-      <c r="N84" s="160" t="s">
+      <c r="N84" s="126" t="s">
         <v>203</v>
       </c>
-      <c r="O84" s="160" t="s">
+      <c r="O84" s="126" t="s">
         <v>203</v>
       </c>
-      <c r="P84" s="160" t="s">
+      <c r="P84" s="126" t="s">
         <v>203</v>
       </c>
-      <c r="Q84" s="161" t="s">
+      <c r="Q84" s="127" t="s">
         <v>203</v>
       </c>
       <c r="R84" s="17"/>
@@ -7846,22 +7789,22 @@
       <c r="AD84" s="69"/>
     </row>
     <row r="85" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A85" s="159" t="s">
+      <c r="A85" s="125" t="s">
         <v>204</v>
       </c>
-      <c r="B85" s="160" t="s">
+      <c r="B85" s="126" t="s">
         <v>204</v>
       </c>
-      <c r="C85" s="160" t="s">
+      <c r="C85" s="126" t="s">
         <v>204</v>
       </c>
-      <c r="D85" s="160" t="s">
+      <c r="D85" s="126" t="s">
         <v>204</v>
       </c>
-      <c r="E85" s="160" t="s">
+      <c r="E85" s="126" t="s">
         <v>204</v>
       </c>
-      <c r="F85" s="161" t="s">
+      <c r="F85" s="127" t="s">
         <v>204</v>
       </c>
       <c r="G85" s="17"/>
@@ -7872,28 +7815,28 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J85" s="159" t="s">
+      <c r="J85" s="125" t="s">
         <v>205</v>
       </c>
-      <c r="K85" s="160" t="s">
+      <c r="K85" s="126" t="s">
         <v>205</v>
       </c>
-      <c r="L85" s="160" t="s">
+      <c r="L85" s="126" t="s">
         <v>205</v>
       </c>
-      <c r="M85" s="160" t="s">
+      <c r="M85" s="126" t="s">
         <v>205</v>
       </c>
-      <c r="N85" s="160" t="s">
+      <c r="N85" s="126" t="s">
         <v>205</v>
       </c>
-      <c r="O85" s="160" t="s">
+      <c r="O85" s="126" t="s">
         <v>205</v>
       </c>
-      <c r="P85" s="160" t="s">
+      <c r="P85" s="126" t="s">
         <v>205</v>
       </c>
-      <c r="Q85" s="161" t="s">
+      <c r="Q85" s="127" t="s">
         <v>205</v>
       </c>
       <c r="R85" s="17"/>
@@ -7916,22 +7859,22 @@
       <c r="AD85" s="69"/>
     </row>
     <row r="86" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A86" s="159" t="s">
+      <c r="A86" s="125" t="s">
         <v>206</v>
       </c>
-      <c r="B86" s="160" t="s">
+      <c r="B86" s="126" t="s">
         <v>206</v>
       </c>
-      <c r="C86" s="160" t="s">
+      <c r="C86" s="126" t="s">
         <v>206</v>
       </c>
-      <c r="D86" s="160" t="s">
+      <c r="D86" s="126" t="s">
         <v>206</v>
       </c>
-      <c r="E86" s="160" t="s">
+      <c r="E86" s="126" t="s">
         <v>206</v>
       </c>
-      <c r="F86" s="161" t="s">
+      <c r="F86" s="127" t="s">
         <v>206</v>
       </c>
       <c r="G86" s="17"/>
@@ -7942,28 +7885,28 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J86" s="187" t="s">
+      <c r="J86" s="128" t="s">
         <v>207</v>
       </c>
-      <c r="K86" s="188" t="s">
+      <c r="K86" s="129" t="s">
         <v>207</v>
       </c>
-      <c r="L86" s="188" t="s">
+      <c r="L86" s="129" t="s">
         <v>207</v>
       </c>
-      <c r="M86" s="188" t="s">
+      <c r="M86" s="129" t="s">
         <v>207</v>
       </c>
-      <c r="N86" s="188" t="s">
+      <c r="N86" s="129" t="s">
         <v>207</v>
       </c>
-      <c r="O86" s="188" t="s">
+      <c r="O86" s="129" t="s">
         <v>207</v>
       </c>
-      <c r="P86" s="188" t="s">
+      <c r="P86" s="129" t="s">
         <v>207</v>
       </c>
-      <c r="Q86" s="189" t="s">
+      <c r="Q86" s="130" t="s">
         <v>207</v>
       </c>
       <c r="R86" s="17"/>
@@ -7986,22 +7929,22 @@
       <c r="AD86" s="69"/>
     </row>
     <row r="87" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A87" s="159" t="s">
+      <c r="A87" s="125" t="s">
         <v>208</v>
       </c>
-      <c r="B87" s="160" t="s">
+      <c r="B87" s="126" t="s">
         <v>208</v>
       </c>
-      <c r="C87" s="160" t="s">
+      <c r="C87" s="126" t="s">
         <v>208</v>
       </c>
-      <c r="D87" s="160" t="s">
+      <c r="D87" s="126" t="s">
         <v>208</v>
       </c>
-      <c r="E87" s="160" t="s">
+      <c r="E87" s="126" t="s">
         <v>208</v>
       </c>
-      <c r="F87" s="161" t="s">
+      <c r="F87" s="127" t="s">
         <v>208</v>
       </c>
       <c r="G87" s="17"/>
@@ -8012,28 +7955,28 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J87" s="187" t="s">
+      <c r="J87" s="128" t="s">
         <v>209</v>
       </c>
-      <c r="K87" s="188" t="s">
+      <c r="K87" s="129" t="s">
         <v>209</v>
       </c>
-      <c r="L87" s="188" t="s">
+      <c r="L87" s="129" t="s">
         <v>209</v>
       </c>
-      <c r="M87" s="188" t="s">
+      <c r="M87" s="129" t="s">
         <v>209</v>
       </c>
-      <c r="N87" s="188" t="s">
+      <c r="N87" s="129" t="s">
         <v>209</v>
       </c>
-      <c r="O87" s="188" t="s">
+      <c r="O87" s="129" t="s">
         <v>209</v>
       </c>
-      <c r="P87" s="188" t="s">
+      <c r="P87" s="129" t="s">
         <v>209</v>
       </c>
-      <c r="Q87" s="189" t="s">
+      <c r="Q87" s="130" t="s">
         <v>209</v>
       </c>
       <c r="R87" s="17"/>
@@ -8056,14 +7999,14 @@
       <c r="AD87" s="69"/>
     </row>
     <row r="88" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A88" s="196" t="s">
+      <c r="A88" s="154" t="s">
         <v>210</v>
       </c>
-      <c r="B88" s="197"/>
-      <c r="C88" s="197"/>
-      <c r="D88" s="197"/>
-      <c r="E88" s="197"/>
-      <c r="F88" s="197"/>
+      <c r="B88" s="155"/>
+      <c r="C88" s="155"/>
+      <c r="D88" s="155"/>
+      <c r="E88" s="155"/>
+      <c r="F88" s="155"/>
       <c r="G88" s="22"/>
       <c r="H88" s="24">
         <v>5</v>
@@ -8072,28 +8015,28 @@
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="J88" s="198" t="s">
+      <c r="J88" s="156" t="s">
         <v>211</v>
       </c>
-      <c r="K88" s="199" t="s">
+      <c r="K88" s="157" t="s">
         <v>211</v>
       </c>
-      <c r="L88" s="199" t="s">
+      <c r="L88" s="157" t="s">
         <v>211</v>
       </c>
-      <c r="M88" s="199" t="s">
+      <c r="M88" s="157" t="s">
         <v>211</v>
       </c>
-      <c r="N88" s="199" t="s">
+      <c r="N88" s="157" t="s">
         <v>211</v>
       </c>
-      <c r="O88" s="199" t="s">
+      <c r="O88" s="157" t="s">
         <v>211</v>
       </c>
-      <c r="P88" s="199" t="s">
+      <c r="P88" s="157" t="s">
         <v>211</v>
       </c>
-      <c r="Q88" s="200" t="s">
+      <c r="Q88" s="158" t="s">
         <v>211</v>
       </c>
       <c r="R88" s="22"/>
@@ -8116,25 +8059,25 @@
       <c r="AD88" s="69"/>
     </row>
     <row r="89" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A89" s="139" t="s">
+      <c r="A89" s="137" t="s">
         <v>212</v>
       </c>
-      <c r="B89" s="140"/>
-      <c r="C89" s="140"/>
-      <c r="D89" s="140"/>
-      <c r="E89" s="140"/>
-      <c r="F89" s="140"/>
-      <c r="G89" s="140"/>
-      <c r="H89" s="140"/>
-      <c r="I89" s="140"/>
-      <c r="J89" s="140"/>
-      <c r="K89" s="140"/>
-      <c r="L89" s="140"/>
-      <c r="M89" s="140"/>
-      <c r="N89" s="140"/>
-      <c r="O89" s="140"/>
-      <c r="P89" s="140"/>
-      <c r="Q89" s="140"/>
+      <c r="B89" s="138"/>
+      <c r="C89" s="138"/>
+      <c r="D89" s="138"/>
+      <c r="E89" s="138"/>
+      <c r="F89" s="138"/>
+      <c r="G89" s="138"/>
+      <c r="H89" s="138"/>
+      <c r="I89" s="138"/>
+      <c r="J89" s="138"/>
+      <c r="K89" s="138"/>
+      <c r="L89" s="138"/>
+      <c r="M89" s="138"/>
+      <c r="N89" s="138"/>
+      <c r="O89" s="138"/>
+      <c r="P89" s="138"/>
+      <c r="Q89" s="138"/>
       <c r="R89" s="43" t="s">
         <v>213</v>
       </c>
@@ -8158,25 +8101,25 @@
       <c r="AD89" s="69"/>
     </row>
     <row r="90" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A90" s="141" t="s">
+      <c r="A90" s="139" t="s">
         <v>132</v>
       </c>
-      <c r="B90" s="142"/>
-      <c r="C90" s="142"/>
-      <c r="D90" s="142"/>
-      <c r="E90" s="142"/>
-      <c r="F90" s="142"/>
-      <c r="G90" s="142"/>
-      <c r="H90" s="142"/>
-      <c r="I90" s="142"/>
-      <c r="J90" s="142"/>
-      <c r="K90" s="142"/>
-      <c r="L90" s="142"/>
-      <c r="M90" s="142"/>
-      <c r="N90" s="142"/>
-      <c r="O90" s="142"/>
-      <c r="P90" s="142"/>
-      <c r="Q90" s="171"/>
+      <c r="B90" s="140"/>
+      <c r="C90" s="140"/>
+      <c r="D90" s="140"/>
+      <c r="E90" s="140"/>
+      <c r="F90" s="140"/>
+      <c r="G90" s="140"/>
+      <c r="H90" s="140"/>
+      <c r="I90" s="140"/>
+      <c r="J90" s="140"/>
+      <c r="K90" s="140"/>
+      <c r="L90" s="140"/>
+      <c r="M90" s="140"/>
+      <c r="N90" s="140"/>
+      <c r="O90" s="140"/>
+      <c r="P90" s="140"/>
+      <c r="Q90" s="141"/>
       <c r="R90" s="47" t="s">
         <v>111</v>
       </c>
@@ -8198,25 +8141,25 @@
       <c r="AD90" s="69"/>
     </row>
     <row r="91" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A91" s="167" t="s">
+      <c r="A91" s="148" t="s">
         <v>214</v>
       </c>
-      <c r="B91" s="168"/>
-      <c r="C91" s="168"/>
-      <c r="D91" s="168"/>
-      <c r="E91" s="168"/>
-      <c r="F91" s="168"/>
-      <c r="G91" s="168"/>
-      <c r="H91" s="168"/>
-      <c r="I91" s="168"/>
-      <c r="J91" s="168"/>
-      <c r="K91" s="168"/>
-      <c r="L91" s="168"/>
-      <c r="M91" s="168"/>
-      <c r="N91" s="168"/>
-      <c r="O91" s="168"/>
-      <c r="P91" s="168"/>
-      <c r="Q91" s="169"/>
+      <c r="B91" s="149"/>
+      <c r="C91" s="149"/>
+      <c r="D91" s="149"/>
+      <c r="E91" s="149"/>
+      <c r="F91" s="149"/>
+      <c r="G91" s="149"/>
+      <c r="H91" s="149"/>
+      <c r="I91" s="149"/>
+      <c r="J91" s="149"/>
+      <c r="K91" s="149"/>
+      <c r="L91" s="149"/>
+      <c r="M91" s="149"/>
+      <c r="N91" s="149"/>
+      <c r="O91" s="149"/>
+      <c r="P91" s="149"/>
+      <c r="Q91" s="150"/>
       <c r="R91" s="90"/>
       <c r="S91" s="15">
         <v>200</v>
@@ -8237,25 +8180,25 @@
       <c r="AD91" s="69"/>
     </row>
     <row r="92" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A92" s="193" t="s">
+      <c r="A92" s="151" t="s">
         <v>133</v>
       </c>
-      <c r="B92" s="194"/>
-      <c r="C92" s="194"/>
-      <c r="D92" s="194"/>
-      <c r="E92" s="194"/>
-      <c r="F92" s="194"/>
-      <c r="G92" s="194"/>
-      <c r="H92" s="194"/>
-      <c r="I92" s="194"/>
-      <c r="J92" s="194"/>
-      <c r="K92" s="194"/>
-      <c r="L92" s="194"/>
-      <c r="M92" s="194"/>
-      <c r="N92" s="194"/>
-      <c r="O92" s="194"/>
-      <c r="P92" s="194"/>
-      <c r="Q92" s="195"/>
+      <c r="B92" s="152"/>
+      <c r="C92" s="152"/>
+      <c r="D92" s="152"/>
+      <c r="E92" s="152"/>
+      <c r="F92" s="152"/>
+      <c r="G92" s="152"/>
+      <c r="H92" s="152"/>
+      <c r="I92" s="152"/>
+      <c r="J92" s="152"/>
+      <c r="K92" s="152"/>
+      <c r="L92" s="152"/>
+      <c r="M92" s="152"/>
+      <c r="N92" s="152"/>
+      <c r="O92" s="152"/>
+      <c r="P92" s="152"/>
+      <c r="Q92" s="153"/>
       <c r="R92" s="87"/>
       <c r="S92" s="88"/>
       <c r="T92" s="89">
@@ -8274,35 +8217,35 @@
       <c r="AD92" s="69"/>
     </row>
     <row r="93" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A93" s="147" t="s">
+      <c r="A93" s="145" t="s">
         <v>215</v>
       </c>
-      <c r="B93" s="148"/>
-      <c r="C93" s="148"/>
-      <c r="D93" s="148"/>
-      <c r="E93" s="148"/>
-      <c r="F93" s="148"/>
-      <c r="G93" s="148"/>
-      <c r="H93" s="148"/>
-      <c r="I93" s="148"/>
-      <c r="J93" s="148"/>
-      <c r="K93" s="148"/>
-      <c r="L93" s="148"/>
-      <c r="M93" s="148"/>
-      <c r="N93" s="148"/>
-      <c r="O93" s="148"/>
-      <c r="P93" s="148"/>
-      <c r="Q93" s="148"/>
+      <c r="B93" s="146"/>
+      <c r="C93" s="146"/>
+      <c r="D93" s="146"/>
+      <c r="E93" s="146"/>
+      <c r="F93" s="146"/>
+      <c r="G93" s="146"/>
+      <c r="H93" s="146"/>
+      <c r="I93" s="146"/>
+      <c r="J93" s="146"/>
+      <c r="K93" s="146"/>
+      <c r="L93" s="146"/>
+      <c r="M93" s="146"/>
+      <c r="N93" s="146"/>
+      <c r="O93" s="146"/>
+      <c r="P93" s="146"/>
+      <c r="Q93" s="146"/>
       <c r="R93" s="44" t="s">
         <v>216</v>
       </c>
       <c r="S93" s="27">
         <f>(SUM(I95:I110,T95:T109))+T113</f>
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="T93" s="64">
         <f>S93/$B$5</f>
-        <v>7.9000000000000001E-2</v>
+        <v>0</v>
       </c>
       <c r="U93" s="70"/>
       <c r="V93" s="84"/>
@@ -8316,14 +8259,14 @@
       <c r="AD93" s="69"/>
     </row>
     <row r="94" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A94" s="141" t="s">
+      <c r="A94" s="139" t="s">
         <v>132</v>
       </c>
-      <c r="B94" s="142"/>
-      <c r="C94" s="142"/>
-      <c r="D94" s="142"/>
-      <c r="E94" s="142"/>
-      <c r="F94" s="171"/>
+      <c r="B94" s="140"/>
+      <c r="C94" s="140"/>
+      <c r="D94" s="140"/>
+      <c r="E94" s="140"/>
+      <c r="F94" s="141"/>
       <c r="G94" s="47" t="s">
         <v>111</v>
       </c>
@@ -8333,16 +8276,16 @@
       <c r="I94" s="48" t="s">
         <v>113</v>
       </c>
-      <c r="J94" s="141" t="s">
+      <c r="J94" s="139" t="s">
         <v>132</v>
       </c>
-      <c r="K94" s="142"/>
-      <c r="L94" s="142"/>
-      <c r="M94" s="142"/>
-      <c r="N94" s="142"/>
-      <c r="O94" s="142"/>
-      <c r="P94" s="142"/>
-      <c r="Q94" s="171"/>
+      <c r="K94" s="140"/>
+      <c r="L94" s="140"/>
+      <c r="M94" s="140"/>
+      <c r="N94" s="140"/>
+      <c r="O94" s="140"/>
+      <c r="P94" s="140"/>
+      <c r="Q94" s="141"/>
       <c r="R94" s="47" t="s">
         <v>111</v>
       </c>
@@ -8364,22 +8307,22 @@
       <c r="AD94" s="69"/>
     </row>
     <row r="95" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A95" s="190" t="s">
+      <c r="A95" s="142" t="s">
         <v>217</v>
       </c>
-      <c r="B95" s="191" t="s">
+      <c r="B95" s="143" t="s">
         <v>217</v>
       </c>
-      <c r="C95" s="191" t="s">
+      <c r="C95" s="143" t="s">
         <v>217</v>
       </c>
-      <c r="D95" s="191" t="s">
+      <c r="D95" s="143" t="s">
         <v>217</v>
       </c>
-      <c r="E95" s="191" t="s">
+      <c r="E95" s="143" t="s">
         <v>217</v>
       </c>
-      <c r="F95" s="192" t="s">
+      <c r="F95" s="144" t="s">
         <v>217</v>
       </c>
       <c r="G95" s="18"/>
@@ -8390,28 +8333,28 @@
         <f t="shared" ref="I95:I110" si="9">G95*H95</f>
         <v>0</v>
       </c>
-      <c r="J95" s="190" t="s">
+      <c r="J95" s="142" t="s">
         <v>218</v>
       </c>
-      <c r="K95" s="191" t="s">
+      <c r="K95" s="143" t="s">
         <v>218</v>
       </c>
-      <c r="L95" s="191" t="s">
+      <c r="L95" s="143" t="s">
         <v>218</v>
       </c>
-      <c r="M95" s="191" t="s">
+      <c r="M95" s="143" t="s">
         <v>218</v>
       </c>
-      <c r="N95" s="191" t="s">
+      <c r="N95" s="143" t="s">
         <v>218</v>
       </c>
-      <c r="O95" s="191" t="s">
+      <c r="O95" s="143" t="s">
         <v>218</v>
       </c>
-      <c r="P95" s="191" t="s">
+      <c r="P95" s="143" t="s">
         <v>218</v>
       </c>
-      <c r="Q95" s="192" t="s">
+      <c r="Q95" s="144" t="s">
         <v>218</v>
       </c>
       <c r="R95" s="18"/>
@@ -8434,22 +8377,22 @@
       <c r="AD95" s="69"/>
     </row>
     <row r="96" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A96" s="159" t="s">
+      <c r="A96" s="125" t="s">
         <v>219</v>
       </c>
-      <c r="B96" s="160" t="s">
+      <c r="B96" s="126" t="s">
         <v>219</v>
       </c>
-      <c r="C96" s="160" t="s">
+      <c r="C96" s="126" t="s">
         <v>219</v>
       </c>
-      <c r="D96" s="160" t="s">
+      <c r="D96" s="126" t="s">
         <v>219</v>
       </c>
-      <c r="E96" s="160" t="s">
+      <c r="E96" s="126" t="s">
         <v>219</v>
       </c>
-      <c r="F96" s="161" t="s">
+      <c r="F96" s="127" t="s">
         <v>219</v>
       </c>
       <c r="G96" s="17"/>
@@ -8460,28 +8403,28 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J96" s="159" t="s">
+      <c r="J96" s="125" t="s">
         <v>220</v>
       </c>
-      <c r="K96" s="160" t="s">
+      <c r="K96" s="126" t="s">
         <v>220</v>
       </c>
-      <c r="L96" s="160" t="s">
+      <c r="L96" s="126" t="s">
         <v>220</v>
       </c>
-      <c r="M96" s="160" t="s">
+      <c r="M96" s="126" t="s">
         <v>220</v>
       </c>
-      <c r="N96" s="160" t="s">
+      <c r="N96" s="126" t="s">
         <v>220</v>
       </c>
-      <c r="O96" s="160" t="s">
+      <c r="O96" s="126" t="s">
         <v>220</v>
       </c>
-      <c r="P96" s="160" t="s">
+      <c r="P96" s="126" t="s">
         <v>220</v>
       </c>
-      <c r="Q96" s="161" t="s">
+      <c r="Q96" s="127" t="s">
         <v>220</v>
       </c>
       <c r="R96" s="17"/>
@@ -8504,22 +8447,22 @@
       <c r="AD96" s="69"/>
     </row>
     <row r="97" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A97" s="159" t="s">
+      <c r="A97" s="125" t="s">
         <v>221</v>
       </c>
-      <c r="B97" s="160" t="s">
+      <c r="B97" s="126" t="s">
         <v>221</v>
       </c>
-      <c r="C97" s="160" t="s">
+      <c r="C97" s="126" t="s">
         <v>221</v>
       </c>
-      <c r="D97" s="160" t="s">
+      <c r="D97" s="126" t="s">
         <v>221</v>
       </c>
-      <c r="E97" s="160" t="s">
+      <c r="E97" s="126" t="s">
         <v>221</v>
       </c>
-      <c r="F97" s="161" t="s">
+      <c r="F97" s="127" t="s">
         <v>221</v>
       </c>
       <c r="G97" s="17"/>
@@ -8530,28 +8473,28 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J97" s="159" t="s">
+      <c r="J97" s="125" t="s">
         <v>222</v>
       </c>
-      <c r="K97" s="160" t="s">
+      <c r="K97" s="126" t="s">
         <v>222</v>
       </c>
-      <c r="L97" s="160" t="s">
+      <c r="L97" s="126" t="s">
         <v>222</v>
       </c>
-      <c r="M97" s="160" t="s">
+      <c r="M97" s="126" t="s">
         <v>222</v>
       </c>
-      <c r="N97" s="160" t="s">
+      <c r="N97" s="126" t="s">
         <v>222</v>
       </c>
-      <c r="O97" s="160" t="s">
+      <c r="O97" s="126" t="s">
         <v>222</v>
       </c>
-      <c r="P97" s="160" t="s">
+      <c r="P97" s="126" t="s">
         <v>222</v>
       </c>
-      <c r="Q97" s="161" t="s">
+      <c r="Q97" s="127" t="s">
         <v>222</v>
       </c>
       <c r="R97" s="17"/>
@@ -8574,22 +8517,22 @@
       <c r="AD97" s="69"/>
     </row>
     <row r="98" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A98" s="159" t="s">
+      <c r="A98" s="125" t="s">
         <v>223</v>
       </c>
-      <c r="B98" s="160" t="s">
+      <c r="B98" s="126" t="s">
         <v>224</v>
       </c>
-      <c r="C98" s="160" t="s">
+      <c r="C98" s="126" t="s">
         <v>224</v>
       </c>
-      <c r="D98" s="160" t="s">
+      <c r="D98" s="126" t="s">
         <v>224</v>
       </c>
-      <c r="E98" s="160" t="s">
+      <c r="E98" s="126" t="s">
         <v>224</v>
       </c>
-      <c r="F98" s="161" t="s">
+      <c r="F98" s="127" t="s">
         <v>224</v>
       </c>
       <c r="G98" s="17"/>
@@ -8600,28 +8543,28 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J98" s="159" t="s">
+      <c r="J98" s="125" t="s">
         <v>225</v>
       </c>
-      <c r="K98" s="160" t="s">
+      <c r="K98" s="126" t="s">
         <v>225</v>
       </c>
-      <c r="L98" s="160" t="s">
+      <c r="L98" s="126" t="s">
         <v>225</v>
       </c>
-      <c r="M98" s="160" t="s">
+      <c r="M98" s="126" t="s">
         <v>225</v>
       </c>
-      <c r="N98" s="160" t="s">
+      <c r="N98" s="126" t="s">
         <v>225</v>
       </c>
-      <c r="O98" s="160" t="s">
+      <c r="O98" s="126" t="s">
         <v>225</v>
       </c>
-      <c r="P98" s="160" t="s">
+      <c r="P98" s="126" t="s">
         <v>225</v>
       </c>
-      <c r="Q98" s="161" t="s">
+      <c r="Q98" s="127" t="s">
         <v>225</v>
       </c>
       <c r="R98" s="17"/>
@@ -8644,22 +8587,22 @@
       <c r="AD98" s="69"/>
     </row>
     <row r="99" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A99" s="159" t="s">
+      <c r="A99" s="125" t="s">
         <v>226</v>
       </c>
-      <c r="B99" s="160" t="s">
+      <c r="B99" s="126" t="s">
         <v>227</v>
       </c>
-      <c r="C99" s="160" t="s">
+      <c r="C99" s="126" t="s">
         <v>227</v>
       </c>
-      <c r="D99" s="160" t="s">
+      <c r="D99" s="126" t="s">
         <v>227</v>
       </c>
-      <c r="E99" s="160" t="s">
+      <c r="E99" s="126" t="s">
         <v>227</v>
       </c>
-      <c r="F99" s="161" t="s">
+      <c r="F99" s="127" t="s">
         <v>227</v>
       </c>
       <c r="G99" s="17"/>
@@ -8670,28 +8613,28 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J99" s="159" t="s">
+      <c r="J99" s="125" t="s">
         <v>228</v>
       </c>
-      <c r="K99" s="160" t="s">
+      <c r="K99" s="126" t="s">
         <v>228</v>
       </c>
-      <c r="L99" s="160" t="s">
+      <c r="L99" s="126" t="s">
         <v>228</v>
       </c>
-      <c r="M99" s="160" t="s">
+      <c r="M99" s="126" t="s">
         <v>228</v>
       </c>
-      <c r="N99" s="160" t="s">
+      <c r="N99" s="126" t="s">
         <v>228</v>
       </c>
-      <c r="O99" s="160" t="s">
+      <c r="O99" s="126" t="s">
         <v>228</v>
       </c>
-      <c r="P99" s="160" t="s">
+      <c r="P99" s="126" t="s">
         <v>228</v>
       </c>
-      <c r="Q99" s="161" t="s">
+      <c r="Q99" s="127" t="s">
         <v>228</v>
       </c>
       <c r="R99" s="17"/>
@@ -8714,22 +8657,22 @@
       <c r="AD99" s="69"/>
     </row>
     <row r="100" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A100" s="159" t="s">
+      <c r="A100" s="125" t="s">
         <v>229</v>
       </c>
-      <c r="B100" s="160" t="s">
+      <c r="B100" s="126" t="s">
         <v>230</v>
       </c>
-      <c r="C100" s="160" t="s">
+      <c r="C100" s="126" t="s">
         <v>230</v>
       </c>
-      <c r="D100" s="160" t="s">
+      <c r="D100" s="126" t="s">
         <v>230</v>
       </c>
-      <c r="E100" s="160" t="s">
+      <c r="E100" s="126" t="s">
         <v>230</v>
       </c>
-      <c r="F100" s="161" t="s">
+      <c r="F100" s="127" t="s">
         <v>230</v>
       </c>
       <c r="G100" s="17"/>
@@ -8740,28 +8683,28 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J100" s="159" t="s">
+      <c r="J100" s="125" t="s">
         <v>231</v>
       </c>
-      <c r="K100" s="160" t="s">
+      <c r="K100" s="126" t="s">
         <v>231</v>
       </c>
-      <c r="L100" s="160" t="s">
+      <c r="L100" s="126" t="s">
         <v>231</v>
       </c>
-      <c r="M100" s="160" t="s">
+      <c r="M100" s="126" t="s">
         <v>231</v>
       </c>
-      <c r="N100" s="160" t="s">
+      <c r="N100" s="126" t="s">
         <v>231</v>
       </c>
-      <c r="O100" s="160" t="s">
+      <c r="O100" s="126" t="s">
         <v>231</v>
       </c>
-      <c r="P100" s="160" t="s">
+      <c r="P100" s="126" t="s">
         <v>231</v>
       </c>
-      <c r="Q100" s="161" t="s">
+      <c r="Q100" s="127" t="s">
         <v>231</v>
       </c>
       <c r="R100" s="17"/>
@@ -8784,22 +8727,22 @@
       <c r="AD100" s="69"/>
     </row>
     <row r="101" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A101" s="159" t="s">
+      <c r="A101" s="125" t="s">
         <v>232</v>
       </c>
-      <c r="B101" s="160" t="s">
+      <c r="B101" s="126" t="s">
         <v>233</v>
       </c>
-      <c r="C101" s="160" t="s">
+      <c r="C101" s="126" t="s">
         <v>233</v>
       </c>
-      <c r="D101" s="160" t="s">
+      <c r="D101" s="126" t="s">
         <v>233</v>
       </c>
-      <c r="E101" s="160" t="s">
+      <c r="E101" s="126" t="s">
         <v>233</v>
       </c>
-      <c r="F101" s="161" t="s">
+      <c r="F101" s="127" t="s">
         <v>233</v>
       </c>
       <c r="G101" s="17"/>
@@ -8810,28 +8753,28 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J101" s="187" t="s">
+      <c r="J101" s="128" t="s">
         <v>234</v>
       </c>
-      <c r="K101" s="188" t="s">
+      <c r="K101" s="129" t="s">
         <v>234</v>
       </c>
-      <c r="L101" s="188" t="s">
+      <c r="L101" s="129" t="s">
         <v>234</v>
       </c>
-      <c r="M101" s="188" t="s">
+      <c r="M101" s="129" t="s">
         <v>234</v>
       </c>
-      <c r="N101" s="188" t="s">
+      <c r="N101" s="129" t="s">
         <v>234</v>
       </c>
-      <c r="O101" s="188" t="s">
+      <c r="O101" s="129" t="s">
         <v>234</v>
       </c>
-      <c r="P101" s="188" t="s">
+      <c r="P101" s="129" t="s">
         <v>234</v>
       </c>
-      <c r="Q101" s="189" t="s">
+      <c r="Q101" s="130" t="s">
         <v>234</v>
       </c>
       <c r="R101" s="17"/>
@@ -8854,22 +8797,22 @@
       <c r="AD101" s="69"/>
     </row>
     <row r="102" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A102" s="159" t="s">
+      <c r="A102" s="125" t="s">
         <v>235</v>
       </c>
-      <c r="B102" s="160" t="s">
+      <c r="B102" s="126" t="s">
         <v>236</v>
       </c>
-      <c r="C102" s="160" t="s">
+      <c r="C102" s="126" t="s">
         <v>236</v>
       </c>
-      <c r="D102" s="160" t="s">
+      <c r="D102" s="126" t="s">
         <v>236</v>
       </c>
-      <c r="E102" s="160" t="s">
+      <c r="E102" s="126" t="s">
         <v>236</v>
       </c>
-      <c r="F102" s="161" t="s">
+      <c r="F102" s="127" t="s">
         <v>236</v>
       </c>
       <c r="G102" s="17"/>
@@ -8880,28 +8823,28 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J102" s="187" t="s">
+      <c r="J102" s="128" t="s">
         <v>237</v>
       </c>
-      <c r="K102" s="188" t="s">
+      <c r="K102" s="129" t="s">
         <v>237</v>
       </c>
-      <c r="L102" s="188" t="s">
+      <c r="L102" s="129" t="s">
         <v>237</v>
       </c>
-      <c r="M102" s="188" t="s">
+      <c r="M102" s="129" t="s">
         <v>237</v>
       </c>
-      <c r="N102" s="188" t="s">
+      <c r="N102" s="129" t="s">
         <v>237</v>
       </c>
-      <c r="O102" s="188" t="s">
+      <c r="O102" s="129" t="s">
         <v>237</v>
       </c>
-      <c r="P102" s="188" t="s">
+      <c r="P102" s="129" t="s">
         <v>237</v>
       </c>
-      <c r="Q102" s="189" t="s">
+      <c r="Q102" s="130" t="s">
         <v>237</v>
       </c>
       <c r="R102" s="17"/>
@@ -8924,22 +8867,22 @@
       <c r="AD102" s="69"/>
     </row>
     <row r="103" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A103" s="159" t="s">
+      <c r="A103" s="125" t="s">
         <v>238</v>
       </c>
-      <c r="B103" s="160" t="s">
+      <c r="B103" s="126" t="s">
         <v>239</v>
       </c>
-      <c r="C103" s="160" t="s">
+      <c r="C103" s="126" t="s">
         <v>239</v>
       </c>
-      <c r="D103" s="160" t="s">
+      <c r="D103" s="126" t="s">
         <v>239</v>
       </c>
-      <c r="E103" s="160" t="s">
+      <c r="E103" s="126" t="s">
         <v>239</v>
       </c>
-      <c r="F103" s="161" t="s">
+      <c r="F103" s="127" t="s">
         <v>239</v>
       </c>
       <c r="G103" s="17"/>
@@ -8950,28 +8893,28 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J103" s="187" t="s">
+      <c r="J103" s="128" t="s">
         <v>240</v>
       </c>
-      <c r="K103" s="188" t="s">
+      <c r="K103" s="129" t="s">
         <v>240</v>
       </c>
-      <c r="L103" s="188" t="s">
+      <c r="L103" s="129" t="s">
         <v>240</v>
       </c>
-      <c r="M103" s="188" t="s">
+      <c r="M103" s="129" t="s">
         <v>240</v>
       </c>
-      <c r="N103" s="188" t="s">
+      <c r="N103" s="129" t="s">
         <v>240</v>
       </c>
-      <c r="O103" s="188" t="s">
+      <c r="O103" s="129" t="s">
         <v>240</v>
       </c>
-      <c r="P103" s="188" t="s">
+      <c r="P103" s="129" t="s">
         <v>240</v>
       </c>
-      <c r="Q103" s="189" t="s">
+      <c r="Q103" s="130" t="s">
         <v>240</v>
       </c>
       <c r="R103" s="17"/>
@@ -8994,22 +8937,22 @@
       <c r="AD103" s="69"/>
     </row>
     <row r="104" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A104" s="159" t="s">
+      <c r="A104" s="125" t="s">
         <v>241</v>
       </c>
-      <c r="B104" s="160" t="s">
+      <c r="B104" s="126" t="s">
         <v>241</v>
       </c>
-      <c r="C104" s="160" t="s">
+      <c r="C104" s="126" t="s">
         <v>241</v>
       </c>
-      <c r="D104" s="160" t="s">
+      <c r="D104" s="126" t="s">
         <v>241</v>
       </c>
-      <c r="E104" s="160" t="s">
+      <c r="E104" s="126" t="s">
         <v>241</v>
       </c>
-      <c r="F104" s="161" t="s">
+      <c r="F104" s="127" t="s">
         <v>241</v>
       </c>
       <c r="G104" s="17"/>
@@ -9020,28 +8963,28 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J104" s="187" t="s">
+      <c r="J104" s="128" t="s">
         <v>242</v>
       </c>
-      <c r="K104" s="188" t="s">
+      <c r="K104" s="129" t="s">
         <v>242</v>
       </c>
-      <c r="L104" s="188" t="s">
+      <c r="L104" s="129" t="s">
         <v>242</v>
       </c>
-      <c r="M104" s="188" t="s">
+      <c r="M104" s="129" t="s">
         <v>242</v>
       </c>
-      <c r="N104" s="188" t="s">
+      <c r="N104" s="129" t="s">
         <v>242</v>
       </c>
-      <c r="O104" s="188" t="s">
+      <c r="O104" s="129" t="s">
         <v>242</v>
       </c>
-      <c r="P104" s="188" t="s">
+      <c r="P104" s="129" t="s">
         <v>242</v>
       </c>
-      <c r="Q104" s="189" t="s">
+      <c r="Q104" s="130" t="s">
         <v>242</v>
       </c>
       <c r="R104" s="17"/>
@@ -9064,56 +9007,54 @@
       <c r="AD104" s="69"/>
     </row>
     <row r="105" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A105" s="159" t="s">
+      <c r="A105" s="125" t="s">
         <v>243</v>
       </c>
-      <c r="B105" s="160" t="s">
+      <c r="B105" s="126" t="s">
         <v>243</v>
       </c>
-      <c r="C105" s="160" t="s">
+      <c r="C105" s="126" t="s">
         <v>243</v>
       </c>
-      <c r="D105" s="160" t="s">
+      <c r="D105" s="126" t="s">
         <v>243</v>
       </c>
-      <c r="E105" s="160" t="s">
+      <c r="E105" s="126" t="s">
         <v>243</v>
       </c>
-      <c r="F105" s="161" t="s">
+      <c r="F105" s="127" t="s">
         <v>243</v>
       </c>
-      <c r="G105" s="17">
-        <v>1</v>
-      </c>
+      <c r="G105" s="17"/>
       <c r="H105" s="15">
         <v>55</v>
       </c>
       <c r="I105" s="20">
         <f t="shared" si="9"/>
-        <v>55</v>
-      </c>
-      <c r="J105" s="187" t="s">
+        <v>0</v>
+      </c>
+      <c r="J105" s="128" t="s">
         <v>244</v>
       </c>
-      <c r="K105" s="188" t="s">
+      <c r="K105" s="129" t="s">
         <v>244</v>
       </c>
-      <c r="L105" s="188" t="s">
+      <c r="L105" s="129" t="s">
         <v>244</v>
       </c>
-      <c r="M105" s="188" t="s">
+      <c r="M105" s="129" t="s">
         <v>244</v>
       </c>
-      <c r="N105" s="188" t="s">
+      <c r="N105" s="129" t="s">
         <v>244</v>
       </c>
-      <c r="O105" s="188" t="s">
+      <c r="O105" s="129" t="s">
         <v>244</v>
       </c>
-      <c r="P105" s="188" t="s">
+      <c r="P105" s="129" t="s">
         <v>244</v>
       </c>
-      <c r="Q105" s="189" t="s">
+      <c r="Q105" s="130" t="s">
         <v>244</v>
       </c>
       <c r="R105" s="17"/>
@@ -9136,22 +9077,22 @@
       <c r="AD105" s="69"/>
     </row>
     <row r="106" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A106" s="159" t="s">
+      <c r="A106" s="125" t="s">
         <v>245</v>
       </c>
-      <c r="B106" s="160" t="s">
+      <c r="B106" s="126" t="s">
         <v>245</v>
       </c>
-      <c r="C106" s="160" t="s">
+      <c r="C106" s="126" t="s">
         <v>245</v>
       </c>
-      <c r="D106" s="160" t="s">
+      <c r="D106" s="126" t="s">
         <v>245</v>
       </c>
-      <c r="E106" s="160" t="s">
+      <c r="E106" s="126" t="s">
         <v>245</v>
       </c>
-      <c r="F106" s="161" t="s">
+      <c r="F106" s="127" t="s">
         <v>245</v>
       </c>
       <c r="G106" s="17"/>
@@ -9162,28 +9103,28 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J106" s="187" t="s">
+      <c r="J106" s="128" t="s">
         <v>246</v>
       </c>
-      <c r="K106" s="188" t="s">
+      <c r="K106" s="129" t="s">
         <v>247</v>
       </c>
-      <c r="L106" s="188" t="s">
+      <c r="L106" s="129" t="s">
         <v>247</v>
       </c>
-      <c r="M106" s="188" t="s">
+      <c r="M106" s="129" t="s">
         <v>247</v>
       </c>
-      <c r="N106" s="188" t="s">
+      <c r="N106" s="129" t="s">
         <v>247</v>
       </c>
-      <c r="O106" s="188" t="s">
+      <c r="O106" s="129" t="s">
         <v>247</v>
       </c>
-      <c r="P106" s="188" t="s">
+      <c r="P106" s="129" t="s">
         <v>247</v>
       </c>
-      <c r="Q106" s="189" t="s">
+      <c r="Q106" s="130" t="s">
         <v>247</v>
       </c>
       <c r="R106" s="17"/>
@@ -9206,22 +9147,22 @@
       <c r="AD106" s="69"/>
     </row>
     <row r="107" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A107" s="159" t="s">
+      <c r="A107" s="125" t="s">
         <v>248</v>
       </c>
-      <c r="B107" s="160" t="s">
+      <c r="B107" s="126" t="s">
         <v>248</v>
       </c>
-      <c r="C107" s="160" t="s">
+      <c r="C107" s="126" t="s">
         <v>248</v>
       </c>
-      <c r="D107" s="160" t="s">
+      <c r="D107" s="126" t="s">
         <v>248</v>
       </c>
-      <c r="E107" s="160" t="s">
+      <c r="E107" s="126" t="s">
         <v>248</v>
       </c>
-      <c r="F107" s="161" t="s">
+      <c r="F107" s="127" t="s">
         <v>248</v>
       </c>
       <c r="G107" s="17"/>
@@ -9232,39 +9173,37 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J107" s="187" t="s">
+      <c r="J107" s="128" t="s">
         <v>249</v>
       </c>
-      <c r="K107" s="188" t="s">
+      <c r="K107" s="129" t="s">
         <v>250</v>
       </c>
-      <c r="L107" s="188" t="s">
+      <c r="L107" s="129" t="s">
         <v>250</v>
       </c>
-      <c r="M107" s="188" t="s">
+      <c r="M107" s="129" t="s">
         <v>250</v>
       </c>
-      <c r="N107" s="188" t="s">
+      <c r="N107" s="129" t="s">
         <v>250</v>
       </c>
-      <c r="O107" s="188" t="s">
+      <c r="O107" s="129" t="s">
         <v>250</v>
       </c>
-      <c r="P107" s="188" t="s">
+      <c r="P107" s="129" t="s">
         <v>250</v>
       </c>
-      <c r="Q107" s="189" t="s">
+      <c r="Q107" s="130" t="s">
         <v>250</v>
       </c>
-      <c r="R107" s="17">
-        <v>4</v>
-      </c>
+      <c r="R107" s="17"/>
       <c r="S107" s="15">
         <v>6</v>
       </c>
       <c r="T107" s="20">
         <f t="shared" si="11"/>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="U107" s="69"/>
       <c r="V107" s="84"/>
@@ -9278,22 +9217,22 @@
       <c r="AD107" s="69"/>
     </row>
     <row r="108" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A108" s="159" t="s">
+      <c r="A108" s="125" t="s">
         <v>251</v>
       </c>
-      <c r="B108" s="160" t="s">
+      <c r="B108" s="126" t="s">
         <v>251</v>
       </c>
-      <c r="C108" s="160" t="s">
+      <c r="C108" s="126" t="s">
         <v>251</v>
       </c>
-      <c r="D108" s="160" t="s">
+      <c r="D108" s="126" t="s">
         <v>251</v>
       </c>
-      <c r="E108" s="160" t="s">
+      <c r="E108" s="126" t="s">
         <v>251</v>
       </c>
-      <c r="F108" s="161" t="s">
+      <c r="F108" s="127" t="s">
         <v>251</v>
       </c>
       <c r="G108" s="17"/>
@@ -9304,28 +9243,28 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J108" s="187" t="s">
+      <c r="J108" s="128" t="s">
         <v>252</v>
       </c>
-      <c r="K108" s="188" t="s">
+      <c r="K108" s="129" t="s">
         <v>252</v>
       </c>
-      <c r="L108" s="188" t="s">
+      <c r="L108" s="129" t="s">
         <v>252</v>
       </c>
-      <c r="M108" s="188" t="s">
+      <c r="M108" s="129" t="s">
         <v>252</v>
       </c>
-      <c r="N108" s="188" t="s">
+      <c r="N108" s="129" t="s">
         <v>252</v>
       </c>
-      <c r="O108" s="188" t="s">
+      <c r="O108" s="129" t="s">
         <v>252</v>
       </c>
-      <c r="P108" s="188" t="s">
+      <c r="P108" s="129" t="s">
         <v>252</v>
       </c>
-      <c r="Q108" s="189" t="s">
+      <c r="Q108" s="130" t="s">
         <v>252</v>
       </c>
       <c r="R108" s="17"/>
@@ -9348,22 +9287,22 @@
       <c r="AD108" s="69"/>
     </row>
     <row r="109" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A109" s="159" t="s">
+      <c r="A109" s="125" t="s">
         <v>253</v>
       </c>
-      <c r="B109" s="160" t="s">
+      <c r="B109" s="126" t="s">
         <v>253</v>
       </c>
-      <c r="C109" s="160" t="s">
+      <c r="C109" s="126" t="s">
         <v>253</v>
       </c>
-      <c r="D109" s="160" t="s">
+      <c r="D109" s="126" t="s">
         <v>253</v>
       </c>
-      <c r="E109" s="160" t="s">
+      <c r="E109" s="126" t="s">
         <v>253</v>
       </c>
-      <c r="F109" s="161" t="s">
+      <c r="F109" s="127" t="s">
         <v>253</v>
       </c>
       <c r="G109" s="17"/>
@@ -9374,28 +9313,28 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J109" s="187" t="s">
+      <c r="J109" s="128" t="s">
         <v>254</v>
       </c>
-      <c r="K109" s="188" t="s">
+      <c r="K109" s="129" t="s">
         <v>255</v>
       </c>
-      <c r="L109" s="188" t="s">
+      <c r="L109" s="129" t="s">
         <v>255</v>
       </c>
-      <c r="M109" s="188" t="s">
+      <c r="M109" s="129" t="s">
         <v>255</v>
       </c>
-      <c r="N109" s="188" t="s">
+      <c r="N109" s="129" t="s">
         <v>255</v>
       </c>
-      <c r="O109" s="188" t="s">
+      <c r="O109" s="129" t="s">
         <v>255</v>
       </c>
-      <c r="P109" s="188" t="s">
+      <c r="P109" s="129" t="s">
         <v>255</v>
       </c>
-      <c r="Q109" s="189" t="s">
+      <c r="Q109" s="130" t="s">
         <v>255</v>
       </c>
       <c r="R109" s="17"/>
@@ -9418,22 +9357,22 @@
       <c r="AD109" s="69"/>
     </row>
     <row r="110" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A110" s="178" t="s">
+      <c r="A110" s="131" t="s">
         <v>160</v>
       </c>
-      <c r="B110" s="179" t="s">
+      <c r="B110" s="132" t="s">
         <v>160</v>
       </c>
-      <c r="C110" s="179" t="s">
+      <c r="C110" s="132" t="s">
         <v>160</v>
       </c>
-      <c r="D110" s="179" t="s">
+      <c r="D110" s="132" t="s">
         <v>160</v>
       </c>
-      <c r="E110" s="179" t="s">
+      <c r="E110" s="132" t="s">
         <v>160</v>
       </c>
-      <c r="F110" s="183" t="s">
+      <c r="F110" s="133" t="s">
         <v>160</v>
       </c>
       <c r="G110" s="22"/>
@@ -9444,14 +9383,14 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="J110" s="184"/>
-      <c r="K110" s="185"/>
-      <c r="L110" s="185"/>
-      <c r="M110" s="185"/>
-      <c r="N110" s="185"/>
-      <c r="O110" s="185"/>
-      <c r="P110" s="185"/>
-      <c r="Q110" s="186"/>
+      <c r="J110" s="134"/>
+      <c r="K110" s="135"/>
+      <c r="L110" s="135"/>
+      <c r="M110" s="135"/>
+      <c r="N110" s="135"/>
+      <c r="O110" s="135"/>
+      <c r="P110" s="135"/>
+      <c r="Q110" s="136"/>
       <c r="R110" s="67"/>
       <c r="S110" s="67"/>
       <c r="T110" s="66"/>
@@ -9467,25 +9406,25 @@
       <c r="AD110" s="69"/>
     </row>
     <row r="111" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A111" s="139" t="s">
+      <c r="A111" s="137" t="s">
         <v>256</v>
       </c>
-      <c r="B111" s="140"/>
-      <c r="C111" s="140"/>
-      <c r="D111" s="140"/>
-      <c r="E111" s="140"/>
-      <c r="F111" s="140"/>
-      <c r="G111" s="140"/>
-      <c r="H111" s="140"/>
-      <c r="I111" s="140"/>
-      <c r="J111" s="140"/>
-      <c r="K111" s="140"/>
-      <c r="L111" s="140"/>
-      <c r="M111" s="140"/>
-      <c r="N111" s="140"/>
-      <c r="O111" s="140"/>
-      <c r="P111" s="140"/>
-      <c r="Q111" s="140"/>
+      <c r="B111" s="138"/>
+      <c r="C111" s="138"/>
+      <c r="D111" s="138"/>
+      <c r="E111" s="138"/>
+      <c r="F111" s="138"/>
+      <c r="G111" s="138"/>
+      <c r="H111" s="138"/>
+      <c r="I111" s="138"/>
+      <c r="J111" s="138"/>
+      <c r="K111" s="138"/>
+      <c r="L111" s="138"/>
+      <c r="M111" s="138"/>
+      <c r="N111" s="138"/>
+      <c r="O111" s="138"/>
+      <c r="P111" s="138"/>
+      <c r="Q111" s="138"/>
       <c r="R111" s="43" t="s">
         <v>257</v>
       </c>
@@ -9509,25 +9448,25 @@
       <c r="AD111" s="69"/>
     </row>
     <row r="112" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A112" s="141" t="s">
+      <c r="A112" s="139" t="s">
         <v>132</v>
       </c>
-      <c r="B112" s="142"/>
-      <c r="C112" s="142"/>
-      <c r="D112" s="142"/>
-      <c r="E112" s="142"/>
-      <c r="F112" s="142"/>
-      <c r="G112" s="142"/>
-      <c r="H112" s="142"/>
-      <c r="I112" s="142"/>
-      <c r="J112" s="142"/>
-      <c r="K112" s="142"/>
-      <c r="L112" s="142"/>
-      <c r="M112" s="142"/>
-      <c r="N112" s="142"/>
-      <c r="O112" s="142"/>
-      <c r="P112" s="142"/>
-      <c r="Q112" s="171"/>
+      <c r="B112" s="140"/>
+      <c r="C112" s="140"/>
+      <c r="D112" s="140"/>
+      <c r="E112" s="140"/>
+      <c r="F112" s="140"/>
+      <c r="G112" s="140"/>
+      <c r="H112" s="140"/>
+      <c r="I112" s="140"/>
+      <c r="J112" s="140"/>
+      <c r="K112" s="140"/>
+      <c r="L112" s="140"/>
+      <c r="M112" s="140"/>
+      <c r="N112" s="140"/>
+      <c r="O112" s="140"/>
+      <c r="P112" s="140"/>
+      <c r="Q112" s="141"/>
       <c r="R112" s="47" t="s">
         <v>111</v>
       </c>
@@ -9549,25 +9488,25 @@
       <c r="AD112" s="69"/>
     </row>
     <row r="113" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A113" s="172" t="s">
+      <c r="A113" s="110" t="s">
         <v>133</v>
       </c>
-      <c r="B113" s="173"/>
-      <c r="C113" s="173"/>
-      <c r="D113" s="173"/>
-      <c r="E113" s="173"/>
-      <c r="F113" s="173"/>
-      <c r="G113" s="173"/>
-      <c r="H113" s="173"/>
-      <c r="I113" s="173"/>
-      <c r="J113" s="173"/>
-      <c r="K113" s="173"/>
-      <c r="L113" s="173"/>
-      <c r="M113" s="173"/>
-      <c r="N113" s="173"/>
-      <c r="O113" s="173"/>
-      <c r="P113" s="173"/>
-      <c r="Q113" s="174"/>
+      <c r="B113" s="111"/>
+      <c r="C113" s="111"/>
+      <c r="D113" s="111"/>
+      <c r="E113" s="111"/>
+      <c r="F113" s="111"/>
+      <c r="G113" s="111"/>
+      <c r="H113" s="111"/>
+      <c r="I113" s="111"/>
+      <c r="J113" s="111"/>
+      <c r="K113" s="111"/>
+      <c r="L113" s="111"/>
+      <c r="M113" s="111"/>
+      <c r="N113" s="111"/>
+      <c r="O113" s="111"/>
+      <c r="P113" s="111"/>
+      <c r="Q113" s="112"/>
       <c r="R113" s="28"/>
       <c r="S113" s="34"/>
       <c r="T113" s="29">
@@ -9586,25 +9525,25 @@
       <c r="AD113" s="69"/>
     </row>
     <row r="114" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A114" s="147" t="s">
+      <c r="A114" s="145" t="s">
         <v>258</v>
       </c>
-      <c r="B114" s="148"/>
-      <c r="C114" s="148"/>
-      <c r="D114" s="148"/>
-      <c r="E114" s="148"/>
-      <c r="F114" s="148"/>
-      <c r="G114" s="148"/>
-      <c r="H114" s="148"/>
-      <c r="I114" s="148"/>
-      <c r="J114" s="148"/>
-      <c r="K114" s="148"/>
-      <c r="L114" s="148"/>
-      <c r="M114" s="148"/>
-      <c r="N114" s="148"/>
-      <c r="O114" s="148"/>
-      <c r="P114" s="148"/>
-      <c r="Q114" s="201"/>
+      <c r="B114" s="146"/>
+      <c r="C114" s="146"/>
+      <c r="D114" s="146"/>
+      <c r="E114" s="146"/>
+      <c r="F114" s="146"/>
+      <c r="G114" s="146"/>
+      <c r="H114" s="146"/>
+      <c r="I114" s="146"/>
+      <c r="J114" s="146"/>
+      <c r="K114" s="146"/>
+      <c r="L114" s="146"/>
+      <c r="M114" s="146"/>
+      <c r="N114" s="146"/>
+      <c r="O114" s="146"/>
+      <c r="P114" s="146"/>
+      <c r="Q114" s="147"/>
       <c r="R114" s="25" t="s">
         <v>259</v>
       </c>
@@ -9628,14 +9567,14 @@
       <c r="AD114" s="69"/>
     </row>
     <row r="115" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A115" s="141" t="s">
+      <c r="A115" s="139" t="s">
         <v>132</v>
       </c>
-      <c r="B115" s="142"/>
-      <c r="C115" s="142"/>
-      <c r="D115" s="142"/>
-      <c r="E115" s="142"/>
-      <c r="F115" s="171"/>
+      <c r="B115" s="140"/>
+      <c r="C115" s="140"/>
+      <c r="D115" s="140"/>
+      <c r="E115" s="140"/>
+      <c r="F115" s="141"/>
       <c r="G115" s="47" t="s">
         <v>111</v>
       </c>
@@ -9645,16 +9584,16 @@
       <c r="I115" s="48" t="s">
         <v>113</v>
       </c>
-      <c r="J115" s="141" t="s">
+      <c r="J115" s="139" t="s">
         <v>132</v>
       </c>
-      <c r="K115" s="142"/>
-      <c r="L115" s="142"/>
-      <c r="M115" s="142"/>
-      <c r="N115" s="142"/>
-      <c r="O115" s="142"/>
-      <c r="P115" s="142"/>
-      <c r="Q115" s="171"/>
+      <c r="K115" s="140"/>
+      <c r="L115" s="140"/>
+      <c r="M115" s="140"/>
+      <c r="N115" s="140"/>
+      <c r="O115" s="140"/>
+      <c r="P115" s="140"/>
+      <c r="Q115" s="141"/>
       <c r="R115" s="47" t="s">
         <v>111</v>
       </c>
@@ -9676,22 +9615,22 @@
       <c r="AD115" s="69"/>
     </row>
     <row r="116" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A116" s="190" t="s">
+      <c r="A116" s="142" t="s">
         <v>260</v>
       </c>
-      <c r="B116" s="191" t="s">
+      <c r="B116" s="143" t="s">
         <v>261</v>
       </c>
-      <c r="C116" s="191" t="s">
+      <c r="C116" s="143" t="s">
         <v>261</v>
       </c>
-      <c r="D116" s="191" t="s">
+      <c r="D116" s="143" t="s">
         <v>261</v>
       </c>
-      <c r="E116" s="191" t="s">
+      <c r="E116" s="143" t="s">
         <v>261</v>
       </c>
-      <c r="F116" s="192" t="s">
+      <c r="F116" s="144" t="s">
         <v>261</v>
       </c>
       <c r="G116" s="18"/>
@@ -9702,28 +9641,28 @@
         <f t="shared" ref="I116:I123" si="12">G116*H116</f>
         <v>0</v>
       </c>
-      <c r="J116" s="190" t="s">
+      <c r="J116" s="142" t="s">
         <v>262</v>
       </c>
-      <c r="K116" s="191" t="s">
+      <c r="K116" s="143" t="s">
         <v>262</v>
       </c>
-      <c r="L116" s="191" t="s">
+      <c r="L116" s="143" t="s">
         <v>262</v>
       </c>
-      <c r="M116" s="191" t="s">
+      <c r="M116" s="143" t="s">
         <v>262</v>
       </c>
-      <c r="N116" s="191" t="s">
+      <c r="N116" s="143" t="s">
         <v>262</v>
       </c>
-      <c r="O116" s="191" t="s">
+      <c r="O116" s="143" t="s">
         <v>262</v>
       </c>
-      <c r="P116" s="191" t="s">
+      <c r="P116" s="143" t="s">
         <v>262</v>
       </c>
-      <c r="Q116" s="192" t="s">
+      <c r="Q116" s="144" t="s">
         <v>262</v>
       </c>
       <c r="R116" s="18"/>
@@ -9746,22 +9685,22 @@
       <c r="AD116" s="69"/>
     </row>
     <row r="117" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A117" s="159" t="s">
+      <c r="A117" s="125" t="s">
         <v>263</v>
       </c>
-      <c r="B117" s="160" t="s">
+      <c r="B117" s="126" t="s">
         <v>264</v>
       </c>
-      <c r="C117" s="160" t="s">
+      <c r="C117" s="126" t="s">
         <v>264</v>
       </c>
-      <c r="D117" s="160" t="s">
+      <c r="D117" s="126" t="s">
         <v>264</v>
       </c>
-      <c r="E117" s="160" t="s">
+      <c r="E117" s="126" t="s">
         <v>264</v>
       </c>
-      <c r="F117" s="161" t="s">
+      <c r="F117" s="127" t="s">
         <v>264</v>
       </c>
       <c r="G117" s="17"/>
@@ -9772,28 +9711,28 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="J117" s="159" t="s">
+      <c r="J117" s="125" t="s">
         <v>265</v>
       </c>
-      <c r="K117" s="160" t="s">
+      <c r="K117" s="126" t="s">
         <v>265</v>
       </c>
-      <c r="L117" s="160" t="s">
+      <c r="L117" s="126" t="s">
         <v>265</v>
       </c>
-      <c r="M117" s="160" t="s">
+      <c r="M117" s="126" t="s">
         <v>265</v>
       </c>
-      <c r="N117" s="160" t="s">
+      <c r="N117" s="126" t="s">
         <v>265</v>
       </c>
-      <c r="O117" s="160" t="s">
+      <c r="O117" s="126" t="s">
         <v>265</v>
       </c>
-      <c r="P117" s="160" t="s">
+      <c r="P117" s="126" t="s">
         <v>265</v>
       </c>
-      <c r="Q117" s="161" t="s">
+      <c r="Q117" s="127" t="s">
         <v>265</v>
       </c>
       <c r="R117" s="17"/>
@@ -9816,22 +9755,22 @@
       <c r="AD117" s="69"/>
     </row>
     <row r="118" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A118" s="159" t="s">
+      <c r="A118" s="125" t="s">
         <v>266</v>
       </c>
-      <c r="B118" s="160" t="s">
+      <c r="B118" s="126" t="s">
         <v>267</v>
       </c>
-      <c r="C118" s="160" t="s">
+      <c r="C118" s="126" t="s">
         <v>267</v>
       </c>
-      <c r="D118" s="160" t="s">
+      <c r="D118" s="126" t="s">
         <v>267</v>
       </c>
-      <c r="E118" s="160" t="s">
+      <c r="E118" s="126" t="s">
         <v>267</v>
       </c>
-      <c r="F118" s="161" t="s">
+      <c r="F118" s="127" t="s">
         <v>267</v>
       </c>
       <c r="G118" s="17"/>
@@ -9842,28 +9781,28 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="J118" s="159" t="s">
+      <c r="J118" s="125" t="s">
         <v>268</v>
       </c>
-      <c r="K118" s="160" t="s">
+      <c r="K118" s="126" t="s">
         <v>268</v>
       </c>
-      <c r="L118" s="160" t="s">
+      <c r="L118" s="126" t="s">
         <v>268</v>
       </c>
-      <c r="M118" s="160" t="s">
+      <c r="M118" s="126" t="s">
         <v>268</v>
       </c>
-      <c r="N118" s="160" t="s">
+      <c r="N118" s="126" t="s">
         <v>268</v>
       </c>
-      <c r="O118" s="160" t="s">
+      <c r="O118" s="126" t="s">
         <v>268</v>
       </c>
-      <c r="P118" s="160" t="s">
+      <c r="P118" s="126" t="s">
         <v>268</v>
       </c>
-      <c r="Q118" s="161" t="s">
+      <c r="Q118" s="127" t="s">
         <v>268</v>
       </c>
       <c r="R118" s="17"/>
@@ -9886,22 +9825,22 @@
       <c r="AD118" s="69"/>
     </row>
     <row r="119" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A119" s="159" t="s">
+      <c r="A119" s="125" t="s">
         <v>269</v>
       </c>
-      <c r="B119" s="160" t="s">
+      <c r="B119" s="126" t="s">
         <v>270</v>
       </c>
-      <c r="C119" s="160" t="s">
+      <c r="C119" s="126" t="s">
         <v>270</v>
       </c>
-      <c r="D119" s="160" t="s">
+      <c r="D119" s="126" t="s">
         <v>270</v>
       </c>
-      <c r="E119" s="160" t="s">
+      <c r="E119" s="126" t="s">
         <v>270</v>
       </c>
-      <c r="F119" s="161" t="s">
+      <c r="F119" s="127" t="s">
         <v>270</v>
       </c>
       <c r="G119" s="17"/>
@@ -9912,28 +9851,28 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="J119" s="159" t="s">
+      <c r="J119" s="125" t="s">
         <v>271</v>
       </c>
-      <c r="K119" s="160" t="s">
+      <c r="K119" s="126" t="s">
         <v>271</v>
       </c>
-      <c r="L119" s="160" t="s">
+      <c r="L119" s="126" t="s">
         <v>271</v>
       </c>
-      <c r="M119" s="160" t="s">
+      <c r="M119" s="126" t="s">
         <v>271</v>
       </c>
-      <c r="N119" s="160" t="s">
+      <c r="N119" s="126" t="s">
         <v>271</v>
       </c>
-      <c r="O119" s="160" t="s">
+      <c r="O119" s="126" t="s">
         <v>271</v>
       </c>
-      <c r="P119" s="160" t="s">
+      <c r="P119" s="126" t="s">
         <v>271</v>
       </c>
-      <c r="Q119" s="161" t="s">
+      <c r="Q119" s="127" t="s">
         <v>271</v>
       </c>
       <c r="R119" s="17"/>
@@ -9956,22 +9895,22 @@
       <c r="AD119" s="69"/>
     </row>
     <row r="120" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A120" s="159" t="s">
+      <c r="A120" s="125" t="s">
         <v>272</v>
       </c>
-      <c r="B120" s="160" t="s">
+      <c r="B120" s="126" t="s">
         <v>273</v>
       </c>
-      <c r="C120" s="160" t="s">
+      <c r="C120" s="126" t="s">
         <v>273</v>
       </c>
-      <c r="D120" s="160" t="s">
+      <c r="D120" s="126" t="s">
         <v>273</v>
       </c>
-      <c r="E120" s="160" t="s">
+      <c r="E120" s="126" t="s">
         <v>273</v>
       </c>
-      <c r="F120" s="161" t="s">
+      <c r="F120" s="127" t="s">
         <v>273</v>
       </c>
       <c r="G120" s="17"/>
@@ -9982,28 +9921,28 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="J120" s="159" t="s">
+      <c r="J120" s="125" t="s">
         <v>274</v>
       </c>
-      <c r="K120" s="160" t="s">
+      <c r="K120" s="126" t="s">
         <v>275</v>
       </c>
-      <c r="L120" s="160" t="s">
+      <c r="L120" s="126" t="s">
         <v>275</v>
       </c>
-      <c r="M120" s="160" t="s">
+      <c r="M120" s="126" t="s">
         <v>275</v>
       </c>
-      <c r="N120" s="160" t="s">
+      <c r="N120" s="126" t="s">
         <v>275</v>
       </c>
-      <c r="O120" s="160" t="s">
+      <c r="O120" s="126" t="s">
         <v>275</v>
       </c>
-      <c r="P120" s="160" t="s">
+      <c r="P120" s="126" t="s">
         <v>275</v>
       </c>
-      <c r="Q120" s="161" t="s">
+      <c r="Q120" s="127" t="s">
         <v>275</v>
       </c>
       <c r="R120" s="17"/>
@@ -10026,22 +9965,22 @@
       <c r="AD120" s="69"/>
     </row>
     <row r="121" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A121" s="159" t="s">
+      <c r="A121" s="125" t="s">
         <v>276</v>
       </c>
-      <c r="B121" s="160" t="s">
+      <c r="B121" s="126" t="s">
         <v>277</v>
       </c>
-      <c r="C121" s="160" t="s">
+      <c r="C121" s="126" t="s">
         <v>277</v>
       </c>
-      <c r="D121" s="160" t="s">
+      <c r="D121" s="126" t="s">
         <v>277</v>
       </c>
-      <c r="E121" s="160" t="s">
+      <c r="E121" s="126" t="s">
         <v>277</v>
       </c>
-      <c r="F121" s="161" t="s">
+      <c r="F121" s="127" t="s">
         <v>277</v>
       </c>
       <c r="G121" s="17"/>
@@ -10052,28 +9991,28 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="J121" s="159" t="s">
+      <c r="J121" s="125" t="s">
         <v>278</v>
       </c>
-      <c r="K121" s="160" t="s">
+      <c r="K121" s="126" t="s">
         <v>279</v>
       </c>
-      <c r="L121" s="160" t="s">
+      <c r="L121" s="126" t="s">
         <v>279</v>
       </c>
-      <c r="M121" s="160" t="s">
+      <c r="M121" s="126" t="s">
         <v>279</v>
       </c>
-      <c r="N121" s="160" t="s">
+      <c r="N121" s="126" t="s">
         <v>279</v>
       </c>
-      <c r="O121" s="160" t="s">
+      <c r="O121" s="126" t="s">
         <v>279</v>
       </c>
-      <c r="P121" s="160" t="s">
+      <c r="P121" s="126" t="s">
         <v>279</v>
       </c>
-      <c r="Q121" s="161" t="s">
+      <c r="Q121" s="127" t="s">
         <v>279</v>
       </c>
       <c r="R121" s="17"/>
@@ -10096,22 +10035,22 @@
       <c r="AD121" s="69"/>
     </row>
     <row r="122" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1">
-      <c r="A122" s="159" t="s">
+      <c r="A122" s="125" t="s">
         <v>280</v>
       </c>
-      <c r="B122" s="160" t="s">
+      <c r="B122" s="126" t="s">
         <v>281</v>
       </c>
-      <c r="C122" s="160" t="s">
+      <c r="C122" s="126" t="s">
         <v>281</v>
       </c>
-      <c r="D122" s="160" t="s">
+      <c r="D122" s="126" t="s">
         <v>281</v>
       </c>
-      <c r="E122" s="160" t="s">
+      <c r="E122" s="126" t="s">
         <v>281</v>
       </c>
-      <c r="F122" s="161" t="s">
+      <c r="F122" s="127" t="s">
         <v>281</v>
       </c>
       <c r="G122" s="17"/>
@@ -10122,28 +10061,28 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="J122" s="187" t="s">
+      <c r="J122" s="128" t="s">
         <v>282</v>
       </c>
-      <c r="K122" s="188" t="s">
+      <c r="K122" s="129" t="s">
         <v>283</v>
       </c>
-      <c r="L122" s="188" t="s">
+      <c r="L122" s="129" t="s">
         <v>283</v>
       </c>
-      <c r="M122" s="188" t="s">
+      <c r="M122" s="129" t="s">
         <v>283</v>
       </c>
-      <c r="N122" s="188" t="s">
+      <c r="N122" s="129" t="s">
         <v>283</v>
       </c>
-      <c r="O122" s="188" t="s">
+      <c r="O122" s="129" t="s">
         <v>283</v>
       </c>
-      <c r="P122" s="188" t="s">
+      <c r="P122" s="129" t="s">
         <v>283</v>
       </c>
-      <c r="Q122" s="189" t="s">
+      <c r="Q122" s="130" t="s">
         <v>283</v>
       </c>
       <c r="R122" s="17"/>
@@ -10166,22 +10105,22 @@
       <c r="AD122" s="69"/>
     </row>
     <row r="123" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A123" s="178" t="s">
+      <c r="A123" s="131" t="s">
         <v>284</v>
       </c>
-      <c r="B123" s="179" t="s">
+      <c r="B123" s="132" t="s">
         <v>284</v>
       </c>
-      <c r="C123" s="179" t="s">
+      <c r="C123" s="132" t="s">
         <v>284</v>
       </c>
-      <c r="D123" s="179" t="s">
+      <c r="D123" s="132" t="s">
         <v>284</v>
       </c>
-      <c r="E123" s="179" t="s">
+      <c r="E123" s="132" t="s">
         <v>284</v>
       </c>
-      <c r="F123" s="183" t="s">
+      <c r="F123" s="133" t="s">
         <v>284</v>
       </c>
       <c r="G123" s="22"/>
@@ -10192,14 +10131,14 @@
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="J123" s="184"/>
-      <c r="K123" s="185"/>
-      <c r="L123" s="185"/>
-      <c r="M123" s="185"/>
-      <c r="N123" s="185"/>
-      <c r="O123" s="185"/>
-      <c r="P123" s="185"/>
-      <c r="Q123" s="186"/>
+      <c r="J123" s="134"/>
+      <c r="K123" s="135"/>
+      <c r="L123" s="135"/>
+      <c r="M123" s="135"/>
+      <c r="N123" s="135"/>
+      <c r="O123" s="135"/>
+      <c r="P123" s="135"/>
+      <c r="Q123" s="136"/>
       <c r="R123" s="67"/>
       <c r="S123" s="67"/>
       <c r="T123" s="66"/>
@@ -10215,25 +10154,25 @@
       <c r="AD123" s="69"/>
     </row>
     <row r="124" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A124" s="139" t="s">
+      <c r="A124" s="137" t="s">
         <v>285</v>
       </c>
-      <c r="B124" s="140"/>
-      <c r="C124" s="140"/>
-      <c r="D124" s="140"/>
-      <c r="E124" s="140"/>
-      <c r="F124" s="140"/>
-      <c r="G124" s="140"/>
-      <c r="H124" s="140"/>
-      <c r="I124" s="140"/>
-      <c r="J124" s="140"/>
-      <c r="K124" s="140"/>
-      <c r="L124" s="140"/>
-      <c r="M124" s="140"/>
-      <c r="N124" s="140"/>
-      <c r="O124" s="140"/>
-      <c r="P124" s="140"/>
-      <c r="Q124" s="140"/>
+      <c r="B124" s="138"/>
+      <c r="C124" s="138"/>
+      <c r="D124" s="138"/>
+      <c r="E124" s="138"/>
+      <c r="F124" s="138"/>
+      <c r="G124" s="138"/>
+      <c r="H124" s="138"/>
+      <c r="I124" s="138"/>
+      <c r="J124" s="138"/>
+      <c r="K124" s="138"/>
+      <c r="L124" s="138"/>
+      <c r="M124" s="138"/>
+      <c r="N124" s="138"/>
+      <c r="O124" s="138"/>
+      <c r="P124" s="138"/>
+      <c r="Q124" s="138"/>
       <c r="R124" s="43" t="s">
         <v>286</v>
       </c>
@@ -10257,25 +10196,25 @@
       <c r="AD124" s="69"/>
     </row>
     <row r="125" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A125" s="141" t="s">
+      <c r="A125" s="139" t="s">
         <v>132</v>
       </c>
-      <c r="B125" s="142"/>
-      <c r="C125" s="142"/>
-      <c r="D125" s="142"/>
-      <c r="E125" s="142"/>
-      <c r="F125" s="142"/>
-      <c r="G125" s="142"/>
-      <c r="H125" s="142"/>
-      <c r="I125" s="142"/>
-      <c r="J125" s="142"/>
-      <c r="K125" s="142"/>
-      <c r="L125" s="142"/>
-      <c r="M125" s="142"/>
-      <c r="N125" s="142"/>
-      <c r="O125" s="142"/>
-      <c r="P125" s="142"/>
-      <c r="Q125" s="171"/>
+      <c r="B125" s="140"/>
+      <c r="C125" s="140"/>
+      <c r="D125" s="140"/>
+      <c r="E125" s="140"/>
+      <c r="F125" s="140"/>
+      <c r="G125" s="140"/>
+      <c r="H125" s="140"/>
+      <c r="I125" s="140"/>
+      <c r="J125" s="140"/>
+      <c r="K125" s="140"/>
+      <c r="L125" s="140"/>
+      <c r="M125" s="140"/>
+      <c r="N125" s="140"/>
+      <c r="O125" s="140"/>
+      <c r="P125" s="140"/>
+      <c r="Q125" s="141"/>
       <c r="R125" s="47" t="s">
         <v>111</v>
       </c>
@@ -10297,25 +10236,25 @@
       <c r="AD125" s="69"/>
     </row>
     <row r="126" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A126" s="172" t="s">
+      <c r="A126" s="110" t="s">
         <v>133</v>
       </c>
-      <c r="B126" s="173"/>
-      <c r="C126" s="173"/>
-      <c r="D126" s="173"/>
-      <c r="E126" s="173"/>
-      <c r="F126" s="173"/>
-      <c r="G126" s="173"/>
-      <c r="H126" s="173"/>
-      <c r="I126" s="173"/>
-      <c r="J126" s="173"/>
-      <c r="K126" s="173"/>
-      <c r="L126" s="173"/>
-      <c r="M126" s="173"/>
-      <c r="N126" s="173"/>
-      <c r="O126" s="173"/>
-      <c r="P126" s="173"/>
-      <c r="Q126" s="174"/>
+      <c r="B126" s="111"/>
+      <c r="C126" s="111"/>
+      <c r="D126" s="111"/>
+      <c r="E126" s="111"/>
+      <c r="F126" s="111"/>
+      <c r="G126" s="111"/>
+      <c r="H126" s="111"/>
+      <c r="I126" s="111"/>
+      <c r="J126" s="111"/>
+      <c r="K126" s="111"/>
+      <c r="L126" s="111"/>
+      <c r="M126" s="111"/>
+      <c r="N126" s="111"/>
+      <c r="O126" s="111"/>
+      <c r="P126" s="111"/>
+      <c r="Q126" s="112"/>
       <c r="R126" s="28"/>
       <c r="S126" s="34"/>
       <c r="T126" s="29">
@@ -10334,26 +10273,26 @@
       <c r="AD126" s="69"/>
     </row>
     <row r="127" spans="1:30" s="98" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1">
-      <c r="A127" s="202"/>
-      <c r="B127" s="203"/>
-      <c r="C127" s="203"/>
-      <c r="D127" s="203"/>
-      <c r="E127" s="203"/>
-      <c r="F127" s="203"/>
-      <c r="G127" s="203"/>
-      <c r="H127" s="203"/>
-      <c r="I127" s="203"/>
-      <c r="J127" s="203"/>
-      <c r="K127" s="203"/>
-      <c r="L127" s="203"/>
-      <c r="M127" s="203"/>
-      <c r="N127" s="203"/>
-      <c r="O127" s="203"/>
-      <c r="P127" s="203"/>
-      <c r="Q127" s="203"/>
-      <c r="R127" s="203"/>
-      <c r="S127" s="203"/>
-      <c r="T127" s="204"/>
+      <c r="A127" s="113"/>
+      <c r="B127" s="114"/>
+      <c r="C127" s="114"/>
+      <c r="D127" s="114"/>
+      <c r="E127" s="114"/>
+      <c r="F127" s="114"/>
+      <c r="G127" s="114"/>
+      <c r="H127" s="114"/>
+      <c r="I127" s="114"/>
+      <c r="J127" s="114"/>
+      <c r="K127" s="114"/>
+      <c r="L127" s="114"/>
+      <c r="M127" s="114"/>
+      <c r="N127" s="114"/>
+      <c r="O127" s="114"/>
+      <c r="P127" s="114"/>
+      <c r="Q127" s="114"/>
+      <c r="R127" s="114"/>
+      <c r="S127" s="114"/>
+      <c r="T127" s="115"/>
       <c r="U127" s="69"/>
       <c r="V127" s="86"/>
       <c r="W127" s="69"/>
@@ -10369,30 +10308,30 @@
       <c r="A128" s="96" t="s">
         <v>287</v>
       </c>
-      <c r="B128" s="205">
+      <c r="B128" s="116">
         <f ca="1">NOW()</f>
-        <v>45806.877604745372</v>
-      </c>
-      <c r="C128" s="206"/>
-      <c r="D128" s="206"/>
-      <c r="E128" s="207"/>
-      <c r="F128" s="208"/>
-      <c r="G128" s="209"/>
-      <c r="H128" s="209"/>
-      <c r="I128" s="209"/>
-      <c r="J128" s="209"/>
-      <c r="K128" s="209"/>
-      <c r="L128" s="209"/>
-      <c r="M128" s="209"/>
-      <c r="N128" s="209"/>
-      <c r="O128" s="209"/>
-      <c r="P128" s="210"/>
-      <c r="Q128" s="211" t="s">
+        <v>46166.772225578701</v>
+      </c>
+      <c r="C128" s="117"/>
+      <c r="D128" s="117"/>
+      <c r="E128" s="118"/>
+      <c r="F128" s="119"/>
+      <c r="G128" s="120"/>
+      <c r="H128" s="120"/>
+      <c r="I128" s="120"/>
+      <c r="J128" s="120"/>
+      <c r="K128" s="120"/>
+      <c r="L128" s="120"/>
+      <c r="M128" s="120"/>
+      <c r="N128" s="120"/>
+      <c r="O128" s="120"/>
+      <c r="P128" s="121"/>
+      <c r="Q128" s="122" t="s">
         <v>288</v>
       </c>
-      <c r="R128" s="212"/>
-      <c r="S128" s="212"/>
-      <c r="T128" s="213"/>
+      <c r="R128" s="123"/>
+      <c r="S128" s="123"/>
+      <c r="T128" s="124"/>
       <c r="U128" s="2"/>
       <c r="V128" s="2"/>
       <c r="W128" s="2"/>
@@ -10439,65 +10378,124 @@
   </sheetData>
   <sheetProtection formatRows="0" insertRows="0"/>
   <mergeCells count="190">
-    <mergeCell ref="A126:Q126"/>
-    <mergeCell ref="A127:T127"/>
-    <mergeCell ref="B128:E128"/>
-    <mergeCell ref="F128:P128"/>
-    <mergeCell ref="Q128:T128"/>
-    <mergeCell ref="A122:F122"/>
-    <mergeCell ref="J122:Q122"/>
-    <mergeCell ref="A123:F123"/>
-    <mergeCell ref="J123:Q123"/>
-    <mergeCell ref="A124:Q124"/>
-    <mergeCell ref="A125:Q125"/>
-    <mergeCell ref="A119:F119"/>
-    <mergeCell ref="J119:Q119"/>
-    <mergeCell ref="A120:F120"/>
-    <mergeCell ref="J120:Q120"/>
-    <mergeCell ref="A121:F121"/>
-    <mergeCell ref="J121:Q121"/>
-    <mergeCell ref="A116:F116"/>
-    <mergeCell ref="J116:Q116"/>
-    <mergeCell ref="A117:F117"/>
-    <mergeCell ref="J117:Q117"/>
-    <mergeCell ref="A118:F118"/>
-    <mergeCell ref="J118:Q118"/>
-    <mergeCell ref="A111:Q111"/>
-    <mergeCell ref="A112:Q112"/>
-    <mergeCell ref="A113:Q113"/>
-    <mergeCell ref="A114:Q114"/>
-    <mergeCell ref="A115:F115"/>
-    <mergeCell ref="J115:Q115"/>
-    <mergeCell ref="A108:F108"/>
-    <mergeCell ref="J108:Q108"/>
-    <mergeCell ref="A109:F109"/>
-    <mergeCell ref="J109:Q109"/>
-    <mergeCell ref="A110:F110"/>
-    <mergeCell ref="J110:Q110"/>
-    <mergeCell ref="A105:F105"/>
-    <mergeCell ref="J105:Q105"/>
-    <mergeCell ref="A106:F106"/>
-    <mergeCell ref="J106:Q106"/>
-    <mergeCell ref="A107:F107"/>
-    <mergeCell ref="J107:Q107"/>
-    <mergeCell ref="A102:F102"/>
-    <mergeCell ref="J102:Q102"/>
-    <mergeCell ref="A103:F103"/>
-    <mergeCell ref="J103:Q103"/>
-    <mergeCell ref="A104:F104"/>
-    <mergeCell ref="J104:Q104"/>
-    <mergeCell ref="A99:F99"/>
-    <mergeCell ref="J99:Q99"/>
-    <mergeCell ref="A100:F100"/>
-    <mergeCell ref="J100:Q100"/>
-    <mergeCell ref="A101:F101"/>
-    <mergeCell ref="J101:Q101"/>
-    <mergeCell ref="A96:F96"/>
-    <mergeCell ref="J96:Q96"/>
-    <mergeCell ref="A97:F97"/>
-    <mergeCell ref="J97:Q97"/>
-    <mergeCell ref="A98:F98"/>
-    <mergeCell ref="J98:Q98"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="X1:AD1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="L2:T2"/>
+    <mergeCell ref="B3:M3"/>
+    <mergeCell ref="N3:R3"/>
+    <mergeCell ref="S3:T3"/>
+    <mergeCell ref="B4:I4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="N4:R4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="G5:L5"/>
+    <mergeCell ref="N5:R5"/>
+    <mergeCell ref="S5:T5"/>
+    <mergeCell ref="A23:Q23"/>
+    <mergeCell ref="A24:T24"/>
+    <mergeCell ref="B25:E25"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="A39:Q39"/>
+    <mergeCell ref="A40:T40"/>
+    <mergeCell ref="A6:Q6"/>
+    <mergeCell ref="A7:Q7"/>
+    <mergeCell ref="A8:T8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:H9"/>
+    <mergeCell ref="I9:L9"/>
+    <mergeCell ref="M9:P9"/>
+    <mergeCell ref="A44:F44"/>
+    <mergeCell ref="J44:Q44"/>
+    <mergeCell ref="A45:F45"/>
+    <mergeCell ref="J45:Q45"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="J46:Q46"/>
+    <mergeCell ref="A41:F41"/>
+    <mergeCell ref="J41:Q41"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="J42:Q42"/>
+    <mergeCell ref="A43:F43"/>
+    <mergeCell ref="J43:Q43"/>
+    <mergeCell ref="A50:Q50"/>
+    <mergeCell ref="A51:Q51"/>
+    <mergeCell ref="A52:Q52"/>
+    <mergeCell ref="A53:Q53"/>
+    <mergeCell ref="A54:Q54"/>
+    <mergeCell ref="A55:T55"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="J47:Q47"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="J48:Q48"/>
+    <mergeCell ref="A49:F49"/>
+    <mergeCell ref="J49:Q49"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="J59:Q59"/>
+    <mergeCell ref="A60:F60"/>
+    <mergeCell ref="J60:Q60"/>
+    <mergeCell ref="A61:F61"/>
+    <mergeCell ref="J61:Q61"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="J56:Q56"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="J57:Q57"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="J58:Q58"/>
+    <mergeCell ref="A65:F65"/>
+    <mergeCell ref="J65:Q65"/>
+    <mergeCell ref="A66:Q66"/>
+    <mergeCell ref="A67:T67"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="G68:J68"/>
+    <mergeCell ref="N68:Q68"/>
+    <mergeCell ref="A62:F62"/>
+    <mergeCell ref="J62:Q62"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="J63:Q63"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="J64:Q64"/>
+    <mergeCell ref="A71:C71"/>
+    <mergeCell ref="N71:Q71"/>
+    <mergeCell ref="A72:C72"/>
+    <mergeCell ref="N72:Q72"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="N73:Q73"/>
+    <mergeCell ref="A69:C69"/>
+    <mergeCell ref="G69:J69"/>
+    <mergeCell ref="N69:Q69"/>
+    <mergeCell ref="A70:C70"/>
+    <mergeCell ref="G70:J70"/>
+    <mergeCell ref="N70:Q70"/>
+    <mergeCell ref="A77:C77"/>
+    <mergeCell ref="N77:Q77"/>
+    <mergeCell ref="A78:Q78"/>
+    <mergeCell ref="A79:F79"/>
+    <mergeCell ref="J79:Q79"/>
+    <mergeCell ref="A80:F80"/>
+    <mergeCell ref="J80:Q80"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="N74:Q74"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="N75:Q75"/>
+    <mergeCell ref="A76:C76"/>
+    <mergeCell ref="N76:Q76"/>
+    <mergeCell ref="A84:F84"/>
+    <mergeCell ref="J84:Q84"/>
+    <mergeCell ref="A85:F85"/>
+    <mergeCell ref="J85:Q85"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="J86:Q86"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="J81:Q81"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="J82:Q82"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="J83:Q83"/>
     <mergeCell ref="A91:Q91"/>
     <mergeCell ref="A92:Q92"/>
     <mergeCell ref="A93:Q93"/>
@@ -10511,124 +10509,65 @@
     <mergeCell ref="J88:Q88"/>
     <mergeCell ref="A89:Q89"/>
     <mergeCell ref="A90:Q90"/>
-    <mergeCell ref="A84:F84"/>
-    <mergeCell ref="J84:Q84"/>
-    <mergeCell ref="A85:F85"/>
-    <mergeCell ref="J85:Q85"/>
-    <mergeCell ref="A86:F86"/>
-    <mergeCell ref="J86:Q86"/>
-    <mergeCell ref="A81:F81"/>
-    <mergeCell ref="J81:Q81"/>
-    <mergeCell ref="A82:F82"/>
-    <mergeCell ref="J82:Q82"/>
-    <mergeCell ref="A83:F83"/>
-    <mergeCell ref="J83:Q83"/>
-    <mergeCell ref="A77:C77"/>
-    <mergeCell ref="N77:Q77"/>
-    <mergeCell ref="A78:Q78"/>
-    <mergeCell ref="A79:F79"/>
-    <mergeCell ref="J79:Q79"/>
-    <mergeCell ref="A80:F80"/>
-    <mergeCell ref="J80:Q80"/>
-    <mergeCell ref="A74:C74"/>
-    <mergeCell ref="N74:Q74"/>
-    <mergeCell ref="A75:C75"/>
-    <mergeCell ref="N75:Q75"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="N76:Q76"/>
-    <mergeCell ref="A71:C71"/>
-    <mergeCell ref="N71:Q71"/>
-    <mergeCell ref="A72:C72"/>
-    <mergeCell ref="N72:Q72"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="N73:Q73"/>
-    <mergeCell ref="A69:C69"/>
-    <mergeCell ref="G69:J69"/>
-    <mergeCell ref="N69:Q69"/>
-    <mergeCell ref="A70:C70"/>
-    <mergeCell ref="G70:J70"/>
-    <mergeCell ref="N70:Q70"/>
-    <mergeCell ref="A65:F65"/>
-    <mergeCell ref="J65:Q65"/>
-    <mergeCell ref="A66:Q66"/>
-    <mergeCell ref="A67:T67"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="G68:J68"/>
-    <mergeCell ref="N68:Q68"/>
-    <mergeCell ref="A62:F62"/>
-    <mergeCell ref="J62:Q62"/>
-    <mergeCell ref="A63:F63"/>
-    <mergeCell ref="J63:Q63"/>
-    <mergeCell ref="A64:F64"/>
-    <mergeCell ref="J64:Q64"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="J59:Q59"/>
-    <mergeCell ref="A60:F60"/>
-    <mergeCell ref="J60:Q60"/>
-    <mergeCell ref="A61:F61"/>
-    <mergeCell ref="J61:Q61"/>
-    <mergeCell ref="A56:F56"/>
-    <mergeCell ref="J56:Q56"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="J57:Q57"/>
-    <mergeCell ref="A58:F58"/>
-    <mergeCell ref="J58:Q58"/>
-    <mergeCell ref="A50:Q50"/>
-    <mergeCell ref="A51:Q51"/>
-    <mergeCell ref="A52:Q52"/>
-    <mergeCell ref="A53:Q53"/>
-    <mergeCell ref="A54:Q54"/>
-    <mergeCell ref="A55:T55"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="J47:Q47"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="J48:Q48"/>
-    <mergeCell ref="A49:F49"/>
-    <mergeCell ref="J49:Q49"/>
-    <mergeCell ref="A44:F44"/>
-    <mergeCell ref="J44:Q44"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="J45:Q45"/>
-    <mergeCell ref="A46:F46"/>
-    <mergeCell ref="J46:Q46"/>
-    <mergeCell ref="A41:F41"/>
-    <mergeCell ref="J41:Q41"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="J42:Q42"/>
-    <mergeCell ref="A43:F43"/>
-    <mergeCell ref="J43:Q43"/>
-    <mergeCell ref="A39:Q39"/>
-    <mergeCell ref="A40:T40"/>
-    <mergeCell ref="A6:Q6"/>
-    <mergeCell ref="A7:Q7"/>
-    <mergeCell ref="A8:T8"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:H9"/>
-    <mergeCell ref="I9:L9"/>
-    <mergeCell ref="M9:P9"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="G5:L5"/>
-    <mergeCell ref="N5:R5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="A23:Q23"/>
-    <mergeCell ref="A24:T24"/>
-    <mergeCell ref="B25:E25"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="A1:T1"/>
-    <mergeCell ref="X1:AD1"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="L2:T2"/>
-    <mergeCell ref="B3:M3"/>
-    <mergeCell ref="N3:R3"/>
-    <mergeCell ref="S3:T3"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:R4"/>
-    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="J99:Q99"/>
+    <mergeCell ref="A100:F100"/>
+    <mergeCell ref="J100:Q100"/>
+    <mergeCell ref="A101:F101"/>
+    <mergeCell ref="J101:Q101"/>
+    <mergeCell ref="A96:F96"/>
+    <mergeCell ref="J96:Q96"/>
+    <mergeCell ref="A97:F97"/>
+    <mergeCell ref="J97:Q97"/>
+    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="J98:Q98"/>
+    <mergeCell ref="A105:F105"/>
+    <mergeCell ref="J105:Q105"/>
+    <mergeCell ref="A106:F106"/>
+    <mergeCell ref="J106:Q106"/>
+    <mergeCell ref="A107:F107"/>
+    <mergeCell ref="J107:Q107"/>
+    <mergeCell ref="A102:F102"/>
+    <mergeCell ref="J102:Q102"/>
+    <mergeCell ref="A103:F103"/>
+    <mergeCell ref="J103:Q103"/>
+    <mergeCell ref="A104:F104"/>
+    <mergeCell ref="J104:Q104"/>
+    <mergeCell ref="A111:Q111"/>
+    <mergeCell ref="A112:Q112"/>
+    <mergeCell ref="A113:Q113"/>
+    <mergeCell ref="A114:Q114"/>
+    <mergeCell ref="A115:F115"/>
+    <mergeCell ref="J115:Q115"/>
+    <mergeCell ref="A108:F108"/>
+    <mergeCell ref="J108:Q108"/>
+    <mergeCell ref="A109:F109"/>
+    <mergeCell ref="J109:Q109"/>
+    <mergeCell ref="A110:F110"/>
+    <mergeCell ref="J110:Q110"/>
+    <mergeCell ref="A119:F119"/>
+    <mergeCell ref="J119:Q119"/>
+    <mergeCell ref="A120:F120"/>
+    <mergeCell ref="J120:Q120"/>
+    <mergeCell ref="A121:F121"/>
+    <mergeCell ref="J121:Q121"/>
+    <mergeCell ref="A116:F116"/>
+    <mergeCell ref="J116:Q116"/>
+    <mergeCell ref="A117:F117"/>
+    <mergeCell ref="J117:Q117"/>
+    <mergeCell ref="A118:F118"/>
+    <mergeCell ref="J118:Q118"/>
+    <mergeCell ref="A126:Q126"/>
+    <mergeCell ref="A127:T127"/>
+    <mergeCell ref="B128:E128"/>
+    <mergeCell ref="F128:P128"/>
+    <mergeCell ref="Q128:T128"/>
+    <mergeCell ref="A122:F122"/>
+    <mergeCell ref="J122:Q122"/>
+    <mergeCell ref="A123:F123"/>
+    <mergeCell ref="J123:Q123"/>
+    <mergeCell ref="A124:Q124"/>
+    <mergeCell ref="A125:Q125"/>
   </mergeCells>
   <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M5" xr:uid="{00000000-0002-0000-0C00-000000000000}">
@@ -10652,16 +10591,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F0E95D0-608B-4BAB-A7C3-8F78F2162880}">
   <dimension ref="A2:P19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <sheetData>
     <row r="2" spans="2:16">
       <c r="B2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="2:16">
       <c r="B3" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="2:16">
@@ -10680,11 +10619,11 @@
       <c r="F5" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="H5" s="100" t="s">
-        <v>297</v>
+      <c r="H5" s="99" t="s">
+        <v>290</v>
       </c>
       <c r="M5" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6" spans="2:16">
@@ -10703,16 +10642,16 @@
       <c r="F6" s="81">
         <v>1.5</v>
       </c>
-      <c r="H6" s="100">
+      <c r="H6" s="99">
         <v>1.8</v>
       </c>
-      <c r="I6" s="100">
+      <c r="I6" s="99">
         <v>1.2</v>
       </c>
-      <c r="J6" s="100">
+      <c r="J6" s="99">
         <v>1.2</v>
       </c>
-      <c r="K6" s="100">
+      <c r="K6" s="99">
         <v>1.2</v>
       </c>
       <c r="M6" s="81">
@@ -10742,13 +10681,13 @@
         <v>2.25</v>
       </c>
       <c r="F7" s="81"/>
-      <c r="H7" s="100">
+      <c r="H7" s="99">
         <v>2.4</v>
       </c>
-      <c r="I7" s="100">
+      <c r="I7" s="99">
         <v>1.8</v>
       </c>
-      <c r="J7" s="100">
+      <c r="J7" s="99">
         <v>1.8</v>
       </c>
       <c r="M7" s="81">
@@ -10842,7 +10781,7 @@
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>
